--- a/YamyProject/Uploads/Subcontractors-city.xlsx
+++ b/YamyProject/Uploads/Subcontractors-city.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27628"/>
-  <workbookPr defaultThemeVersion="166925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mahmoud\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5F01F7B3-7C67-44CE-B602-52E955C7D8B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{2C0711B4-3165-4259-A02E-98F936D839B5}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576"/>
   </bookViews>
   <sheets>
     <sheet name="Upload" sheetId="1" r:id="rId1"/>
@@ -35,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5860" uniqueCount="1521">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5862" uniqueCount="1523">
   <si>
     <t>Date</t>
   </si>
@@ -4598,12 +4597,18 @@
   </si>
   <si>
     <t>دمج البيانات من نوبل الى نظام يامى -رقم الفاتورة- 652-الخدمة -خصم مكتسب-التفاصيل-تركيب حجر سادة وطبات الحجر للنوافذ والبربت لموقع سالم على المهيرى المزروعى</t>
+  </si>
+  <si>
+    <t>Invoice</t>
+  </si>
+  <si>
+    <t>Retention Amount</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="3">
     <font>
       <sz val="10"/>
@@ -4746,7 +4751,18 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -5055,15 +5071,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65965A3D-9942-4C6A-9AF5-BC5D4680572B}">
-  <dimension ref="B2:M1303"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B2:P1303"/>
   <sheetFormatPr defaultRowHeight="13.2"/>
   <cols>
     <col min="2" max="3" width="7.6640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="119.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:13" ht="19.2">
+    <row r="2" spans="2:16" ht="19.2">
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
@@ -5100,8 +5116,14 @@
       <c r="M2" s="4" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="3" spans="2:13" ht="19.8">
+      <c r="O2" s="3" t="s">
+        <v>1521</v>
+      </c>
+      <c r="P2" s="4" t="s">
+        <v>1522</v>
+      </c>
+    </row>
+    <row r="3" spans="2:16" ht="19.8">
       <c r="B3" s="5">
         <v>44927</v>
       </c>
@@ -5138,8 +5160,14 @@
       <c r="M3" s="11">
         <v>4320</v>
       </c>
-    </row>
-    <row r="4" spans="2:13" ht="19.8">
+      <c r="O3" s="10">
+        <v>15</v>
+      </c>
+      <c r="P3" s="11">
+        <v>3267</v>
+      </c>
+    </row>
+    <row r="4" spans="2:16" ht="19.8">
       <c r="B4" s="5">
         <v>44927</v>
       </c>
@@ -5176,8 +5204,14 @@
       <c r="M4" s="11">
         <v>28350</v>
       </c>
-    </row>
-    <row r="5" spans="2:13" ht="19.8">
+      <c r="O4" s="10">
+        <v>16</v>
+      </c>
+      <c r="P4" s="10">
+        <v>981</v>
+      </c>
+    </row>
+    <row r="5" spans="2:16" ht="19.8">
       <c r="B5" s="5">
         <v>44927</v>
       </c>
@@ -5210,8 +5244,14 @@
       <c r="M5" s="10">
         <v>-3</v>
       </c>
-    </row>
-    <row r="6" spans="2:13" ht="19.8">
+      <c r="O5" s="10">
+        <v>17</v>
+      </c>
+      <c r="P5" s="11">
+        <v>2104.1999999999998</v>
+      </c>
+    </row>
+    <row r="6" spans="2:16" ht="19.8">
       <c r="B6" s="5">
         <v>44927</v>
       </c>
@@ -5248,8 +5288,14 @@
       <c r="M6" s="10">
         <v>810</v>
       </c>
-    </row>
-    <row r="7" spans="2:13" ht="19.8">
+      <c r="O6" s="10">
+        <v>18</v>
+      </c>
+      <c r="P6" s="10">
+        <v>572.9</v>
+      </c>
+    </row>
+    <row r="7" spans="2:16" ht="19.8">
       <c r="B7" s="5">
         <v>44927</v>
       </c>
@@ -5286,8 +5332,14 @@
       <c r="M7" s="11">
         <v>9000</v>
       </c>
-    </row>
-    <row r="8" spans="2:13" ht="19.8">
+      <c r="O7" s="10">
+        <v>19</v>
+      </c>
+      <c r="P7" s="10">
+        <v>729.5</v>
+      </c>
+    </row>
+    <row r="8" spans="2:16" ht="19.8">
       <c r="B8" s="5">
         <v>44927</v>
       </c>
@@ -5320,8 +5372,14 @@
       <c r="M8" s="10">
         <v>-29</v>
       </c>
-    </row>
-    <row r="9" spans="2:13" ht="19.8">
+      <c r="O8" s="10">
+        <v>77</v>
+      </c>
+      <c r="P8" s="11">
+        <v>1836</v>
+      </c>
+    </row>
+    <row r="9" spans="2:16" ht="19.8">
       <c r="B9" s="5">
         <v>44927</v>
       </c>
@@ -5358,8 +5416,14 @@
       <c r="M9" s="10">
         <v>792</v>
       </c>
-    </row>
-    <row r="10" spans="2:13" ht="19.8">
+      <c r="O9" s="10">
+        <v>4</v>
+      </c>
+      <c r="P9" s="10">
+        <v>547.5</v>
+      </c>
+    </row>
+    <row r="10" spans="2:16" ht="19.8">
       <c r="B10" s="5">
         <v>44927</v>
       </c>
@@ -5396,8 +5460,14 @@
       <c r="M10" s="11">
         <v>20250</v>
       </c>
-    </row>
-    <row r="11" spans="2:13" ht="19.8">
+      <c r="O10" s="10">
+        <v>5</v>
+      </c>
+      <c r="P10" s="11">
+        <v>1209</v>
+      </c>
+    </row>
+    <row r="11" spans="2:16" ht="19.8">
       <c r="B11" s="5">
         <v>44927</v>
       </c>
@@ -5430,8 +5500,14 @@
       <c r="M11" s="10">
         <v>-37.799999999999997</v>
       </c>
-    </row>
-    <row r="12" spans="2:13" ht="19.8">
+      <c r="O11" s="10">
+        <v>6</v>
+      </c>
+      <c r="P11" s="11">
+        <v>1595.4</v>
+      </c>
+    </row>
+    <row r="12" spans="2:16" ht="19.8">
       <c r="B12" s="5">
         <v>44927</v>
       </c>
@@ -5468,8 +5544,14 @@
       <c r="M12" s="11">
         <v>5729</v>
       </c>
-    </row>
-    <row r="13" spans="2:13" ht="19.8">
+      <c r="O12" s="10">
+        <v>7</v>
+      </c>
+      <c r="P12" s="10">
+        <v>292.39999999999998</v>
+      </c>
+    </row>
+    <row r="13" spans="2:16" ht="19.8">
       <c r="B13" s="5">
         <v>44927</v>
       </c>
@@ -5502,8 +5584,14 @@
       <c r="M13" s="10">
         <v>-56.1</v>
       </c>
-    </row>
-    <row r="14" spans="2:13" ht="19.8">
+      <c r="O13" s="10">
+        <v>8</v>
+      </c>
+      <c r="P13" s="10">
+        <v>222.7</v>
+      </c>
+    </row>
+    <row r="14" spans="2:16" ht="19.8">
       <c r="B14" s="5">
         <v>44927</v>
       </c>
@@ -5540,8 +5628,14 @@
       <c r="M14" s="11">
         <v>6480</v>
       </c>
-    </row>
-    <row r="15" spans="2:13" ht="19.8">
+      <c r="O14" s="10">
+        <v>9</v>
+      </c>
+      <c r="P14" s="10">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="15" spans="2:16" ht="19.8">
       <c r="B15" s="5">
         <v>44927</v>
       </c>
@@ -5578,8 +5672,14 @@
       <c r="M15" s="10">
         <v>815</v>
       </c>
-    </row>
-    <row r="16" spans="2:13" ht="19.8">
+      <c r="O15" s="10">
+        <v>12</v>
+      </c>
+      <c r="P15" s="10">
+        <v>684.5</v>
+      </c>
+    </row>
+    <row r="16" spans="2:16" ht="19.8">
       <c r="B16" s="5">
         <v>44927</v>
       </c>
@@ -5612,8 +5712,14 @@
       <c r="M16" s="10">
         <v>-65.5</v>
       </c>
-    </row>
-    <row r="17" spans="2:13" ht="19.8">
+      <c r="O16" s="10">
+        <v>13</v>
+      </c>
+      <c r="P16" s="10">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="17" spans="2:16" ht="19.8">
       <c r="B17" s="12" t="s">
         <v>34</v>
       </c>
@@ -5650,8 +5756,14 @@
       <c r="M17" s="11">
         <v>18360</v>
       </c>
-    </row>
-    <row r="18" spans="2:13" ht="19.8">
+      <c r="O17" s="10">
+        <v>22</v>
+      </c>
+      <c r="P17" s="10">
+        <v>974</v>
+      </c>
+    </row>
+    <row r="18" spans="2:16" ht="19.8">
       <c r="B18" s="12" t="s">
         <v>34</v>
       </c>
@@ -5684,8 +5796,14 @@
       <c r="M18" s="10">
         <v>-24</v>
       </c>
-    </row>
-    <row r="19" spans="2:13" ht="19.8">
+      <c r="O18" s="10">
+        <v>23</v>
+      </c>
+      <c r="P18" s="10">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="19" spans="2:16" ht="19.8">
       <c r="B19" s="12" t="s">
         <v>39</v>
       </c>
@@ -5722,8 +5840,14 @@
       <c r="M19" s="11">
         <v>1149.54</v>
       </c>
-    </row>
-    <row r="20" spans="2:13" ht="19.8">
+      <c r="O19" s="10">
+        <v>24</v>
+      </c>
+      <c r="P19" s="10">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="20" spans="2:16" ht="19.8">
       <c r="B20" s="12" t="s">
         <v>39</v>
       </c>
@@ -5760,8 +5884,14 @@
       <c r="M20" s="10">
         <v>300</v>
       </c>
-    </row>
-    <row r="21" spans="2:13" ht="19.8">
+      <c r="O20" s="10">
+        <v>25</v>
+      </c>
+      <c r="P20" s="10">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="21" spans="2:16" ht="19.8">
       <c r="B21" s="12" t="s">
         <v>39</v>
       </c>
@@ -5798,8 +5928,14 @@
       <c r="M21" s="10">
         <v>120</v>
       </c>
-    </row>
-    <row r="22" spans="2:13" ht="19.8">
+      <c r="O21" s="10">
+        <v>26</v>
+      </c>
+      <c r="P21" s="11">
+        <v>2574</v>
+      </c>
+    </row>
+    <row r="22" spans="2:16" ht="19.8">
       <c r="B22" s="12" t="s">
         <v>39</v>
       </c>
@@ -5836,8 +5972,14 @@
       <c r="M22" s="11">
         <v>1445</v>
       </c>
-    </row>
-    <row r="23" spans="2:13" ht="19.8">
+      <c r="O22" s="10">
+        <v>27</v>
+      </c>
+      <c r="P22" s="10">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="23" spans="2:16" ht="19.8">
       <c r="B23" s="12" t="s">
         <v>39</v>
       </c>
@@ -5874,8 +6016,14 @@
       <c r="M23" s="11">
         <v>1836</v>
       </c>
-    </row>
-    <row r="24" spans="2:13" ht="19.8">
+      <c r="O23" s="10">
+        <v>28</v>
+      </c>
+      <c r="P23" s="10">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="24" spans="2:16" ht="19.8">
       <c r="B24" s="12" t="s">
         <v>39</v>
       </c>
@@ -5912,8 +6060,14 @@
       <c r="M24" s="10">
         <v>374</v>
       </c>
-    </row>
-    <row r="25" spans="2:13" ht="19.8">
+      <c r="O24" s="10">
+        <v>34</v>
+      </c>
+      <c r="P24" s="10">
+        <v>286.8</v>
+      </c>
+    </row>
+    <row r="25" spans="2:16" ht="19.8">
       <c r="B25" s="12" t="s">
         <v>39</v>
       </c>
@@ -5950,8 +6104,14 @@
       <c r="M25" s="11">
         <v>1700</v>
       </c>
-    </row>
-    <row r="26" spans="2:13" ht="19.8">
+      <c r="O25" s="10">
+        <v>55</v>
+      </c>
+      <c r="P25" s="11">
+        <v>1114</v>
+      </c>
+    </row>
+    <row r="26" spans="2:16" ht="19.8">
       <c r="B26" s="12" t="s">
         <v>39</v>
       </c>
@@ -5984,8 +6144,14 @@
       <c r="M26" s="10">
         <v>-27.5</v>
       </c>
-    </row>
-    <row r="27" spans="2:13" ht="19.8">
+      <c r="O26" s="10">
+        <v>90</v>
+      </c>
+      <c r="P26" s="11">
+        <v>1734</v>
+      </c>
+    </row>
+    <row r="27" spans="2:16" ht="19.8">
       <c r="B27" s="12" t="s">
         <v>39</v>
       </c>
@@ -6022,8 +6188,14 @@
       <c r="M27" s="11">
         <v>10575</v>
       </c>
-    </row>
-    <row r="28" spans="2:13" ht="19.8">
+      <c r="O27" s="10">
+        <v>1</v>
+      </c>
+      <c r="P27" s="11">
+        <v>1458</v>
+      </c>
+    </row>
+    <row r="28" spans="2:16" ht="19.8">
       <c r="B28" s="12" t="s">
         <v>39</v>
       </c>
@@ -6060,8 +6232,14 @@
       <c r="M28" s="11">
         <v>1520</v>
       </c>
-    </row>
-    <row r="29" spans="2:13" ht="19.8">
+      <c r="O28" s="10">
+        <v>14</v>
+      </c>
+      <c r="P28" s="10">
+        <v>264.79000000000002</v>
+      </c>
+    </row>
+    <row r="29" spans="2:16" ht="19.8">
       <c r="B29" s="12" t="s">
         <v>39</v>
       </c>
@@ -6094,8 +6272,14 @@
       <c r="M29" s="10">
         <v>-86</v>
       </c>
-    </row>
-    <row r="30" spans="2:13" ht="19.8">
+      <c r="O29" s="10">
+        <v>29</v>
+      </c>
+      <c r="P29" s="10">
+        <v>918</v>
+      </c>
+    </row>
+    <row r="30" spans="2:16" ht="19.8">
       <c r="B30" s="12" t="s">
         <v>39</v>
       </c>
@@ -6132,8 +6316,14 @@
       <c r="M30" s="11">
         <v>14850</v>
       </c>
-    </row>
-    <row r="31" spans="2:13" ht="19.8">
+      <c r="O30" s="10">
+        <v>30</v>
+      </c>
+      <c r="P30" s="11">
+        <v>2214</v>
+      </c>
+    </row>
+    <row r="31" spans="2:16" ht="19.8">
       <c r="B31" s="12" t="s">
         <v>39</v>
       </c>
@@ -6170,8 +6360,14 @@
       <c r="M31" s="11">
         <v>1104</v>
       </c>
-    </row>
-    <row r="32" spans="2:13" ht="19.8">
+      <c r="O31" s="10">
+        <v>31</v>
+      </c>
+      <c r="P31" s="11">
+        <v>2268</v>
+      </c>
+    </row>
+    <row r="32" spans="2:16" ht="19.8">
       <c r="B32" s="12" t="s">
         <v>39</v>
       </c>
@@ -6204,8 +6400,14 @@
       <c r="M32" s="10">
         <v>-58.6</v>
       </c>
-    </row>
-    <row r="33" spans="2:13" ht="19.8">
+      <c r="O32" s="10">
+        <v>32</v>
+      </c>
+      <c r="P32" s="10">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="33" spans="2:16" ht="19.8">
       <c r="B33" s="12" t="s">
         <v>39</v>
       </c>
@@ -6242,8 +6444,14 @@
       <c r="M33" s="11">
         <v>2600</v>
       </c>
-    </row>
-    <row r="34" spans="2:13" ht="19.8">
+      <c r="O33" s="10">
+        <v>36</v>
+      </c>
+      <c r="P33" s="11">
+        <v>1787</v>
+      </c>
+    </row>
+    <row r="34" spans="2:16" ht="19.8">
       <c r="B34" s="12" t="s">
         <v>39</v>
       </c>
@@ -6280,8 +6488,14 @@
       <c r="M34" s="10">
         <v>324</v>
       </c>
-    </row>
-    <row r="35" spans="2:13" ht="19.8">
+      <c r="O34" s="10">
+        <v>39</v>
+      </c>
+      <c r="P34" s="10">
+        <v>573.1</v>
+      </c>
+    </row>
+    <row r="35" spans="2:16" ht="19.8">
       <c r="B35" s="12" t="s">
         <v>39</v>
       </c>
@@ -6314,8 +6528,14 @@
       <c r="M35" s="10">
         <v>-31.6</v>
       </c>
-    </row>
-    <row r="36" spans="2:13" ht="19.8">
+      <c r="O35" s="10">
+        <v>40</v>
+      </c>
+      <c r="P35" s="10">
+        <v>797.5</v>
+      </c>
+    </row>
+    <row r="36" spans="2:16" ht="19.8">
       <c r="B36" s="12" t="s">
         <v>39</v>
       </c>
@@ -6352,8 +6572,14 @@
       <c r="M36" s="11">
         <v>2227</v>
       </c>
-    </row>
-    <row r="37" spans="2:13" ht="19.8">
+      <c r="O36" s="10">
+        <v>73</v>
+      </c>
+      <c r="P36" s="11">
+        <v>1598</v>
+      </c>
+    </row>
+    <row r="37" spans="2:16" ht="19.8">
       <c r="B37" s="12" t="s">
         <v>39</v>
       </c>
@@ -6386,8 +6612,14 @@
       <c r="M37" s="10">
         <v>-4.3</v>
       </c>
-    </row>
-    <row r="38" spans="2:13" ht="19.8">
+      <c r="O37" s="10">
+        <v>78</v>
+      </c>
+      <c r="P37" s="10">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="38" spans="2:16" ht="19.8">
       <c r="B38" s="12" t="s">
         <v>39</v>
       </c>
@@ -6424,8 +6656,14 @@
       <c r="M38" s="11">
         <v>2550</v>
       </c>
-    </row>
-    <row r="39" spans="2:13" ht="19.8">
+      <c r="O38" s="10">
+        <v>33</v>
+      </c>
+      <c r="P38" s="10">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="39" spans="2:16" ht="19.8">
       <c r="B39" s="12" t="s">
         <v>39</v>
       </c>
@@ -6458,8 +6696,14 @@
       <c r="M39" s="10">
         <v>-95</v>
       </c>
-    </row>
-    <row r="40" spans="2:13" ht="19.8">
+      <c r="O39" s="10">
+        <v>35</v>
+      </c>
+      <c r="P39" s="10">
+        <v>208.6</v>
+      </c>
+    </row>
+    <row r="40" spans="2:16" ht="19.8">
       <c r="B40" s="12" t="s">
         <v>39</v>
       </c>
@@ -6496,8 +6740,14 @@
       <c r="M40" s="11">
         <v>6045</v>
       </c>
-    </row>
-    <row r="41" spans="2:13" ht="19.8">
+      <c r="O40" s="10">
+        <v>41</v>
+      </c>
+      <c r="P40" s="10">
+        <v>925.2</v>
+      </c>
+    </row>
+    <row r="41" spans="2:16" ht="19.8">
       <c r="B41" s="12" t="s">
         <v>39</v>
       </c>
@@ -6534,8 +6784,14 @@
       <c r="M41" s="10">
         <v>800</v>
       </c>
-    </row>
-    <row r="42" spans="2:13" ht="19.8">
+      <c r="O41" s="10">
+        <v>44</v>
+      </c>
+      <c r="P41" s="11">
+        <v>5703</v>
+      </c>
+    </row>
+    <row r="42" spans="2:16" ht="19.8">
       <c r="B42" s="12" t="s">
         <v>39</v>
       </c>
@@ -6568,8 +6824,14 @@
       <c r="M42" s="10">
         <v>-60.5</v>
       </c>
-    </row>
-    <row r="43" spans="2:13" ht="19.8">
+      <c r="O42" s="10">
+        <v>45</v>
+      </c>
+      <c r="P42" s="10">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="43" spans="2:16" ht="19.8">
       <c r="B43" s="12" t="s">
         <v>39</v>
       </c>
@@ -6606,8 +6868,14 @@
       <c r="M43" s="11">
         <v>5500</v>
       </c>
-    </row>
-    <row r="44" spans="2:13">
+      <c r="O43" s="10">
+        <v>46</v>
+      </c>
+      <c r="P43" s="11">
+        <v>6109.5</v>
+      </c>
+    </row>
+    <row r="44" spans="2:16">
       <c r="B44" s="12" t="s">
         <v>39</v>
       </c>
@@ -6640,8 +6908,14 @@
       <c r="M44" s="10">
         <v>-50</v>
       </c>
-    </row>
-    <row r="45" spans="2:13" ht="19.8">
+      <c r="O44" s="10">
+        <v>47</v>
+      </c>
+      <c r="P44" s="11">
+        <v>3245</v>
+      </c>
+    </row>
+    <row r="45" spans="2:16" ht="19.8">
       <c r="B45" s="12" t="s">
         <v>39</v>
       </c>
@@ -6678,8 +6952,14 @@
       <c r="M45" s="11">
         <v>9744</v>
       </c>
-    </row>
-    <row r="46" spans="2:13" ht="19.8">
+      <c r="O45" s="10">
+        <v>48</v>
+      </c>
+      <c r="P45" s="11">
+        <v>3001</v>
+      </c>
+    </row>
+    <row r="46" spans="2:16" ht="19.8">
       <c r="B46" s="12" t="s">
         <v>39</v>
       </c>
@@ -6712,8 +6992,14 @@
       <c r="M46" s="10">
         <v>-70</v>
       </c>
-    </row>
-    <row r="47" spans="2:13" ht="19.8">
+      <c r="O46" s="10">
+        <v>49</v>
+      </c>
+      <c r="P46" s="11">
+        <v>2070</v>
+      </c>
+    </row>
+    <row r="47" spans="2:16" ht="19.8">
       <c r="B47" s="12" t="s">
         <v>39</v>
       </c>
@@ -6750,8 +7036,14 @@
       <c r="M47" s="11">
         <v>6160</v>
       </c>
-    </row>
-    <row r="48" spans="2:13" ht="19.8">
+      <c r="O47" s="10">
+        <v>50</v>
+      </c>
+      <c r="P47" s="10">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="48" spans="2:16" ht="19.8">
       <c r="B48" s="12" t="s">
         <v>39</v>
       </c>
@@ -6784,8 +7076,14 @@
       <c r="M48" s="10">
         <v>-44</v>
       </c>
-    </row>
-    <row r="49" spans="2:13" ht="19.8">
+      <c r="O48" s="10">
+        <v>51</v>
+      </c>
+      <c r="P48" s="11">
+        <v>1926</v>
+      </c>
+    </row>
+    <row r="49" spans="2:16" ht="19.8">
       <c r="B49" s="12" t="s">
         <v>39</v>
       </c>
@@ -6822,8 +7120,14 @@
       <c r="M49" s="11">
         <v>3160</v>
       </c>
-    </row>
-    <row r="50" spans="2:13" ht="19.8">
+      <c r="O49" s="10">
+        <v>53</v>
+      </c>
+      <c r="P49" s="10">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="50" spans="2:16" ht="19.8">
       <c r="B50" s="12" t="s">
         <v>39</v>
       </c>
@@ -6856,8 +7160,14 @@
       <c r="M50" s="10">
         <v>-44</v>
       </c>
-    </row>
-    <row r="51" spans="2:13" ht="19.8">
+      <c r="O50" s="10">
+        <v>54</v>
+      </c>
+      <c r="P50" s="11">
+        <v>1854</v>
+      </c>
+    </row>
+    <row r="51" spans="2:16" ht="19.8">
       <c r="B51" s="12" t="s">
         <v>39</v>
       </c>
@@ -6894,8 +7204,14 @@
       <c r="M51" s="11">
         <v>1080</v>
       </c>
-    </row>
-    <row r="52" spans="2:13" ht="19.8">
+      <c r="O51" s="10">
+        <v>56</v>
+      </c>
+      <c r="P51" s="10">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="52" spans="2:16" ht="19.8">
       <c r="B52" s="12" t="s">
         <v>39</v>
       </c>
@@ -6928,8 +7244,14 @@
       <c r="M52" s="10">
         <v>-22</v>
       </c>
-    </row>
-    <row r="53" spans="2:13" ht="19.8">
+      <c r="O52" s="10">
+        <v>66</v>
+      </c>
+      <c r="P52" s="11">
+        <v>1323</v>
+      </c>
+    </row>
+    <row r="53" spans="2:16" ht="19.8">
       <c r="B53" s="12" t="s">
         <v>39</v>
       </c>
@@ -6966,8 +7288,14 @@
       <c r="M53" s="11">
         <v>25740</v>
       </c>
-    </row>
-    <row r="54" spans="2:13" ht="19.8">
+      <c r="O53" s="10">
+        <v>69</v>
+      </c>
+      <c r="P53" s="11">
+        <v>3915</v>
+      </c>
+    </row>
+    <row r="54" spans="2:16" ht="19.8">
       <c r="B54" s="12" t="s">
         <v>39</v>
       </c>
@@ -7000,8 +7328,14 @@
       <c r="M54" s="10">
         <v>-166</v>
       </c>
-    </row>
-    <row r="55" spans="2:13" ht="19.8">
+      <c r="O54" s="10">
+        <v>75</v>
+      </c>
+      <c r="P54" s="11">
+        <v>2635</v>
+      </c>
+    </row>
+    <row r="55" spans="2:16" ht="19.8">
       <c r="B55" s="12" t="s">
         <v>39</v>
       </c>
@@ -7038,8 +7372,14 @@
       <c r="M55" s="11">
         <v>6480</v>
       </c>
-    </row>
-    <row r="56" spans="2:13" ht="19.8">
+      <c r="O55" s="10">
+        <v>37</v>
+      </c>
+      <c r="P55" s="10">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="56" spans="2:16" ht="19.8">
       <c r="B56" s="12" t="s">
         <v>39</v>
       </c>
@@ -7072,8 +7412,14 @@
       <c r="M56" s="10">
         <v>-32</v>
       </c>
-    </row>
-    <row r="57" spans="2:13" ht="19.8">
+      <c r="O56" s="10">
+        <v>38</v>
+      </c>
+      <c r="P56" s="10">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="57" spans="2:16" ht="19.8">
       <c r="B57" s="12" t="s">
         <v>39</v>
       </c>
@@ -7110,8 +7456,14 @@
       <c r="M57" s="11">
         <v>2340</v>
       </c>
-    </row>
-    <row r="58" spans="2:13" ht="19.8">
+      <c r="O57" s="10">
+        <v>52</v>
+      </c>
+      <c r="P57" s="10">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="58" spans="2:16" ht="19.8">
       <c r="B58" s="12" t="s">
         <v>39</v>
       </c>
@@ -7144,8 +7496,14 @@
       <c r="M58" s="10">
         <v>-106</v>
       </c>
-    </row>
-    <row r="59" spans="2:13" ht="19.8">
+      <c r="O58" s="10">
+        <v>57</v>
+      </c>
+      <c r="P58" s="11">
+        <v>2685</v>
+      </c>
+    </row>
+    <row r="59" spans="2:16" ht="19.8">
       <c r="B59" s="12" t="s">
         <v>39</v>
       </c>
@@ -7182,8 +7540,14 @@
       <c r="M59" s="11">
         <v>2100</v>
       </c>
-    </row>
-    <row r="60" spans="2:13" ht="19.8">
+      <c r="O59" s="10">
+        <v>61</v>
+      </c>
+      <c r="P59" s="11">
+        <v>1230</v>
+      </c>
+    </row>
+    <row r="60" spans="2:16" ht="19.8">
       <c r="B60" s="12" t="s">
         <v>39</v>
       </c>
@@ -7220,8 +7584,14 @@
       <c r="M60" s="10">
         <v>272</v>
       </c>
-    </row>
-    <row r="61" spans="2:13" ht="19.8">
+      <c r="O60" s="10">
+        <v>62</v>
+      </c>
+      <c r="P60" s="10">
+        <v>662.5</v>
+      </c>
+    </row>
+    <row r="61" spans="2:16" ht="19.8">
       <c r="B61" s="12" t="s">
         <v>39</v>
       </c>
@@ -7258,8 +7628,14 @@
       <c r="M61" s="10">
         <v>496</v>
       </c>
-    </row>
-    <row r="62" spans="2:13" ht="19.8">
+      <c r="O61" s="10">
+        <v>65</v>
+      </c>
+      <c r="P61" s="10">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="62" spans="2:16" ht="19.8">
       <c r="B62" s="12" t="s">
         <v>39</v>
       </c>
@@ -7294,8 +7670,14 @@
       <c r="M62" s="10">
         <v>-81.2</v>
       </c>
-    </row>
-    <row r="63" spans="2:13" ht="19.8">
+      <c r="O62" s="10">
+        <v>67</v>
+      </c>
+      <c r="P62" s="11">
+        <v>1836</v>
+      </c>
+    </row>
+    <row r="63" spans="2:16" ht="19.8">
       <c r="B63" s="12" t="s">
         <v>39</v>
       </c>
@@ -7332,8 +7714,14 @@
       <c r="M63" s="11">
         <v>6856</v>
       </c>
-    </row>
-    <row r="64" spans="2:13" ht="19.8">
+      <c r="O63" s="10">
+        <v>68</v>
+      </c>
+      <c r="P63" s="11">
+        <v>4779</v>
+      </c>
+    </row>
+    <row r="64" spans="2:16" ht="19.8">
       <c r="B64" s="12" t="s">
         <v>39</v>
       </c>
@@ -7370,8 +7758,14 @@
       <c r="M64" s="11">
         <v>1824</v>
       </c>
-    </row>
-    <row r="65" spans="2:13" ht="19.8">
+      <c r="O64" s="10">
+        <v>70</v>
+      </c>
+      <c r="P64" s="10">
+        <v>962</v>
+      </c>
+    </row>
+    <row r="65" spans="2:16" ht="19.8">
       <c r="B65" s="12" t="s">
         <v>39</v>
       </c>
@@ -7408,8 +7802,14 @@
       <c r="M65" s="11">
         <v>1600</v>
       </c>
-    </row>
-    <row r="66" spans="2:13">
+      <c r="O65" s="10">
+        <v>71</v>
+      </c>
+      <c r="P65" s="11">
+        <v>1026</v>
+      </c>
+    </row>
+    <row r="66" spans="2:16">
       <c r="B66" s="12" t="s">
         <v>39</v>
       </c>
@@ -7442,8 +7842,14 @@
       <c r="M66" s="10">
         <v>-80</v>
       </c>
-    </row>
-    <row r="67" spans="2:13" ht="19.8">
+      <c r="O66" s="10">
+        <v>72</v>
+      </c>
+      <c r="P66" s="10">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="67" spans="2:16" ht="19.8">
       <c r="B67" s="12" t="s">
         <v>39</v>
       </c>
@@ -7480,8 +7886,14 @@
       <c r="M67" s="10">
         <v>460</v>
       </c>
-    </row>
-    <row r="68" spans="2:13" ht="19.8">
+      <c r="O67" s="10">
+        <v>74</v>
+      </c>
+      <c r="P67" s="11">
+        <v>2431</v>
+      </c>
+    </row>
+    <row r="68" spans="2:16" ht="19.8">
       <c r="B68" s="12" t="s">
         <v>39</v>
       </c>
@@ -7518,8 +7930,14 @@
       <c r="M68" s="10">
         <v>480</v>
       </c>
-    </row>
-    <row r="69" spans="2:13">
+      <c r="O68" s="10">
+        <v>76</v>
+      </c>
+      <c r="P68" s="11">
+        <v>2329</v>
+      </c>
+    </row>
+    <row r="69" spans="2:16">
       <c r="B69" s="12" t="s">
         <v>39</v>
       </c>
@@ -7552,8 +7970,14 @@
       <c r="M69" s="10">
         <v>-26</v>
       </c>
-    </row>
-    <row r="70" spans="2:13" ht="19.8">
+      <c r="O69" s="10">
+        <v>89</v>
+      </c>
+      <c r="P69" s="10">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="70" spans="2:16" ht="19.8">
       <c r="B70" s="12" t="s">
         <v>39</v>
       </c>
@@ -7590,8 +8014,14 @@
       <c r="M70" s="11">
         <v>17340</v>
       </c>
-    </row>
-    <row r="71" spans="2:13" ht="19.8">
+      <c r="O70" s="10">
+        <v>91</v>
+      </c>
+      <c r="P70" s="11">
+        <v>2574</v>
+      </c>
+    </row>
+    <row r="71" spans="2:16" ht="19.8">
       <c r="B71" s="12" t="s">
         <v>39</v>
       </c>
@@ -7624,8 +8054,14 @@
       <c r="M71" s="10">
         <v>-6</v>
       </c>
-    </row>
-    <row r="72" spans="2:13" ht="19.8">
+      <c r="O71" s="10">
+        <v>92</v>
+      </c>
+      <c r="P71" s="10">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="72" spans="2:16" ht="19.8">
       <c r="B72" s="5">
         <v>44959</v>
       </c>
@@ -7662,8 +8098,14 @@
       <c r="M72" s="11">
         <v>10880</v>
       </c>
-    </row>
-    <row r="73" spans="2:13" ht="19.8">
+      <c r="O72" s="10">
+        <v>155</v>
+      </c>
+      <c r="P72" s="10">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="73" spans="2:16" ht="19.8">
       <c r="B73" s="5">
         <v>44959</v>
       </c>
@@ -7700,8 +8142,14 @@
       <c r="M73" s="10">
         <v>580</v>
       </c>
-    </row>
-    <row r="74" spans="2:13" ht="19.8">
+      <c r="O73" s="10">
+        <v>58</v>
+      </c>
+      <c r="P73" s="10">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="74" spans="2:16" ht="19.8">
       <c r="B74" s="5">
         <v>44959</v>
       </c>
@@ -7738,8 +8186,14 @@
       <c r="M74" s="11">
         <v>1792</v>
       </c>
-    </row>
-    <row r="75" spans="2:13" ht="19.8">
+      <c r="O74" s="10">
+        <v>59</v>
+      </c>
+      <c r="P74" s="11">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="75" spans="2:16" ht="19.8">
       <c r="B75" s="5">
         <v>44959</v>
       </c>
@@ -7776,8 +8230,14 @@
       <c r="M75" s="11">
         <v>1328</v>
       </c>
-    </row>
-    <row r="76" spans="2:13" ht="19.8">
+      <c r="O75" s="10">
+        <v>60</v>
+      </c>
+      <c r="P75" s="11">
+        <v>3438</v>
+      </c>
+    </row>
+    <row r="76" spans="2:16" ht="19.8">
       <c r="B76" s="5">
         <v>44959</v>
       </c>
@@ -7810,8 +8270,14 @@
       <c r="M76" s="10">
         <v>-22</v>
       </c>
-    </row>
-    <row r="77" spans="2:13" ht="19.8">
+      <c r="O76" s="10">
+        <v>64</v>
+      </c>
+      <c r="P76" s="10">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="77" spans="2:16" ht="19.8">
       <c r="B77" s="5">
         <v>45018</v>
       </c>
@@ -7848,8 +8314,14 @@
       <c r="M77" s="11">
         <v>4320</v>
       </c>
-    </row>
-    <row r="78" spans="2:13" ht="19.8">
+      <c r="O77" s="10">
+        <v>83</v>
+      </c>
+      <c r="P77" s="11">
+        <v>1180</v>
+      </c>
+    </row>
+    <row r="78" spans="2:16" ht="19.8">
       <c r="B78" s="5">
         <v>45018</v>
       </c>
@@ -7886,8 +8358,14 @@
       <c r="M78" s="10">
         <v>400</v>
       </c>
-    </row>
-    <row r="79" spans="2:13" ht="19.8">
+      <c r="O78" s="10">
+        <v>84</v>
+      </c>
+      <c r="P78" s="10">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="79" spans="2:16" ht="19.8">
       <c r="B79" s="5">
         <v>45018</v>
       </c>
@@ -7924,8 +8402,14 @@
       <c r="M79" s="10">
         <v>664.8</v>
       </c>
-    </row>
-    <row r="80" spans="2:13" ht="19.8">
+      <c r="O79" s="10">
+        <v>87</v>
+      </c>
+      <c r="P79" s="10">
+        <v>513.9</v>
+      </c>
+    </row>
+    <row r="80" spans="2:16" ht="19.8">
       <c r="B80" s="5">
         <v>45109</v>
       </c>
@@ -7962,8 +8446,14 @@
       <c r="M80" s="11">
         <v>25000</v>
       </c>
-    </row>
-    <row r="81" spans="2:13" ht="19.8">
+      <c r="O80" s="10">
+        <v>102</v>
+      </c>
+      <c r="P80" s="11">
+        <v>1566</v>
+      </c>
+    </row>
+    <row r="81" spans="2:16" ht="19.8">
       <c r="B81" s="5">
         <v>45109</v>
       </c>
@@ -8000,8 +8490,14 @@
       <c r="M81" s="11">
         <v>15000</v>
       </c>
-    </row>
-    <row r="82" spans="2:13" ht="19.8">
+      <c r="O81" s="10">
+        <v>103</v>
+      </c>
+      <c r="P81" s="10">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="82" spans="2:16" ht="19.8">
       <c r="B82" s="12" t="s">
         <v>122</v>
       </c>
@@ -8038,8 +8534,14 @@
       <c r="M82" s="11">
         <v>2340</v>
       </c>
-    </row>
-    <row r="83" spans="2:13" ht="19.8">
+      <c r="O82" s="10">
+        <v>106</v>
+      </c>
+      <c r="P82" s="10">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="83" spans="2:16" ht="19.8">
       <c r="B83" s="12" t="s">
         <v>122</v>
       </c>
@@ -8076,8 +8578,14 @@
       <c r="M83" s="11">
         <v>5040</v>
       </c>
-    </row>
-    <row r="84" spans="2:13" ht="19.8">
+      <c r="O83" s="10">
+        <v>107</v>
+      </c>
+      <c r="P83" s="10">
+        <v>90.5</v>
+      </c>
+    </row>
+    <row r="84" spans="2:16" ht="19.8">
       <c r="B84" s="12" t="s">
         <v>122</v>
       </c>
@@ -8114,8 +8622,14 @@
       <c r="M84" s="11">
         <v>1800</v>
       </c>
-    </row>
-    <row r="85" spans="2:13" ht="19.8">
+      <c r="O84" s="10">
+        <v>108</v>
+      </c>
+      <c r="P84" s="11">
+        <v>1438.5</v>
+      </c>
+    </row>
+    <row r="85" spans="2:16" ht="19.8">
       <c r="B85" s="12" t="s">
         <v>122</v>
       </c>
@@ -8148,8 +8662,14 @@
       <c r="M85" s="10">
         <v>-62</v>
       </c>
-    </row>
-    <row r="86" spans="2:13" ht="19.8">
+      <c r="O85" s="10">
+        <v>113</v>
+      </c>
+      <c r="P85" s="10">
+        <v>421.2</v>
+      </c>
+    </row>
+    <row r="86" spans="2:16" ht="19.8">
       <c r="B86" s="12" t="s">
         <v>122</v>
       </c>
@@ -8186,8 +8706,14 @@
       <c r="M86" s="11">
         <v>10620</v>
       </c>
-    </row>
-    <row r="87" spans="2:13" ht="19.8">
+      <c r="O86" s="10">
+        <v>154</v>
+      </c>
+      <c r="P86" s="11">
+        <v>1207</v>
+      </c>
+    </row>
+    <row r="87" spans="2:16" ht="19.8">
       <c r="B87" s="12" t="s">
         <v>122</v>
       </c>
@@ -8224,8 +8750,14 @@
       <c r="M87" s="11">
         <v>11520</v>
       </c>
-    </row>
-    <row r="88" spans="2:13" ht="19.8">
+      <c r="O87" s="10">
+        <v>93</v>
+      </c>
+      <c r="P87" s="10">
+        <v>757.8</v>
+      </c>
+    </row>
+    <row r="88" spans="2:16" ht="19.8">
       <c r="B88" s="12" t="s">
         <v>122</v>
       </c>
@@ -8258,8 +8790,14 @@
       <c r="M88" s="10">
         <v>-26</v>
       </c>
-    </row>
-    <row r="89" spans="2:13" ht="19.8">
+      <c r="O88" s="10">
+        <v>94</v>
+      </c>
+      <c r="P88" s="11">
+        <v>1602</v>
+      </c>
+    </row>
+    <row r="89" spans="2:16" ht="19.8">
       <c r="B89" s="12" t="s">
         <v>122</v>
       </c>
@@ -8296,8 +8834,14 @@
       <c r="M89" s="11">
         <v>20160</v>
       </c>
-    </row>
-    <row r="90" spans="2:13" ht="19.8">
+      <c r="O89" s="10">
+        <v>95</v>
+      </c>
+      <c r="P89" s="11">
+        <v>1439.9</v>
+      </c>
+    </row>
+    <row r="90" spans="2:16" ht="19.8">
       <c r="B90" s="12" t="s">
         <v>122</v>
       </c>
@@ -8334,8 +8878,14 @@
       <c r="M90" s="11">
         <v>2520</v>
       </c>
-    </row>
-    <row r="91" spans="2:13" ht="19.8">
+      <c r="O90" s="10">
+        <v>96</v>
+      </c>
+      <c r="P90" s="11">
+        <v>3600</v>
+      </c>
+    </row>
+    <row r="91" spans="2:16" ht="19.8">
       <c r="B91" s="12" t="s">
         <v>122</v>
       </c>
@@ -8368,8 +8918,14 @@
       <c r="M91" s="10">
         <v>-12</v>
       </c>
-    </row>
-    <row r="92" spans="2:13" ht="19.8">
+      <c r="O91" s="10">
+        <v>97</v>
+      </c>
+      <c r="P91" s="11">
+        <v>4023</v>
+      </c>
+    </row>
+    <row r="92" spans="2:16" ht="19.8">
       <c r="B92" s="12" t="s">
         <v>122</v>
       </c>
@@ -8406,8 +8962,14 @@
       <c r="M92" s="11">
         <v>5220</v>
       </c>
-    </row>
-    <row r="93" spans="2:13" ht="19.8">
+      <c r="O92" s="10">
+        <v>98</v>
+      </c>
+      <c r="P92" s="10">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="93" spans="2:16" ht="19.8">
       <c r="B93" s="12" t="s">
         <v>122</v>
       </c>
@@ -8444,8 +9006,14 @@
       <c r="M93" s="10">
         <v>720</v>
       </c>
-    </row>
-    <row r="94" spans="2:13" ht="19.8">
+      <c r="O93" s="10">
+        <v>100</v>
+      </c>
+      <c r="P93" s="10">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="94" spans="2:16" ht="19.8">
       <c r="B94" s="12" t="s">
         <v>122</v>
       </c>
@@ -8478,8 +9046,14 @@
       <c r="M94" s="10">
         <v>-46</v>
       </c>
-    </row>
-    <row r="95" spans="2:13" ht="19.8">
+      <c r="O94" s="10">
+        <v>101</v>
+      </c>
+      <c r="P94" s="11">
+        <v>4212</v>
+      </c>
+    </row>
+    <row r="95" spans="2:16" ht="19.8">
       <c r="B95" s="12" t="s">
         <v>122</v>
       </c>
@@ -8516,8 +9090,14 @@
       <c r="M95" s="11">
         <v>13910</v>
       </c>
-    </row>
-    <row r="96" spans="2:13" ht="19.8">
+      <c r="O95" s="10">
+        <v>142</v>
+      </c>
+      <c r="P95" s="10">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="96" spans="2:16" ht="19.8">
       <c r="B96" s="12" t="s">
         <v>122</v>
       </c>
@@ -8554,8 +9134,14 @@
       <c r="M96" s="11">
         <v>3960</v>
       </c>
-    </row>
-    <row r="97" spans="2:13">
+      <c r="O96" s="10">
+        <v>135</v>
+      </c>
+      <c r="P96" s="11">
+        <v>1635.4</v>
+      </c>
+    </row>
+    <row r="97" spans="2:16">
       <c r="B97" s="12" t="s">
         <v>122</v>
       </c>
@@ -8588,8 +9174,14 @@
       <c r="M97" s="10">
         <v>-83</v>
       </c>
-    </row>
-    <row r="98" spans="2:13" ht="19.8">
+      <c r="O97" s="10">
+        <v>99</v>
+      </c>
+      <c r="P97" s="11">
+        <v>2673</v>
+      </c>
+    </row>
+    <row r="98" spans="2:16" ht="19.8">
       <c r="B98" s="12" t="s">
         <v>122</v>
       </c>
@@ -8626,8 +9218,14 @@
       <c r="M98" s="11">
         <v>5731</v>
       </c>
-    </row>
-    <row r="99" spans="2:13" ht="19.8">
+      <c r="O98" s="10">
+        <v>104</v>
+      </c>
+      <c r="P98" s="11">
+        <v>1276.5</v>
+      </c>
+    </row>
+    <row r="99" spans="2:16" ht="19.8">
       <c r="B99" s="12" t="s">
         <v>122</v>
       </c>
@@ -8660,8 +9258,14 @@
       <c r="M99" s="10">
         <v>-57.9</v>
       </c>
-    </row>
-    <row r="100" spans="2:13" ht="19.8">
+      <c r="O99" s="10">
+        <v>105</v>
+      </c>
+      <c r="P99" s="10">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="100" spans="2:16" ht="19.8">
       <c r="B100" s="12" t="s">
         <v>122</v>
       </c>
@@ -8698,8 +9302,14 @@
       <c r="M100" s="11">
         <v>7975</v>
       </c>
-    </row>
-    <row r="101" spans="2:13" ht="19.8">
+      <c r="O100" s="10">
+        <v>109</v>
+      </c>
+      <c r="P100" s="10">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="101" spans="2:16" ht="19.8">
       <c r="B101" s="12" t="s">
         <v>122</v>
       </c>
@@ -8732,8 +9342,14 @@
       <c r="M101" s="10">
         <v>-77.5</v>
       </c>
-    </row>
-    <row r="102" spans="2:13" ht="19.8">
+      <c r="O101" s="10">
+        <v>110</v>
+      </c>
+      <c r="P101" s="10">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="102" spans="2:16" ht="19.8">
       <c r="B102" s="12" t="s">
         <v>122</v>
       </c>
@@ -8770,8 +9386,14 @@
       <c r="M102" s="11">
         <v>15980</v>
       </c>
-    </row>
-    <row r="103" spans="2:13" ht="19.8">
+      <c r="O102" s="10">
+        <v>111</v>
+      </c>
+      <c r="P102" s="10">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="103" spans="2:16" ht="19.8">
       <c r="B103" s="12" t="s">
         <v>122</v>
       </c>
@@ -8804,8 +9426,14 @@
       <c r="M103" s="10">
         <v>-82</v>
       </c>
-    </row>
-    <row r="104" spans="2:13" ht="19.8">
+      <c r="O103" s="10">
+        <v>112</v>
+      </c>
+      <c r="P103" s="10">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="104" spans="2:16" ht="19.8">
       <c r="B104" s="12" t="s">
         <v>122</v>
       </c>
@@ -8842,8 +9470,14 @@
       <c r="M104" s="11">
         <v>9690</v>
       </c>
-    </row>
-    <row r="105" spans="2:13" ht="19.8">
+      <c r="O104" s="10">
+        <v>115</v>
+      </c>
+      <c r="P104" s="10">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="105" spans="2:16" ht="19.8">
       <c r="B105" s="12" t="s">
         <v>122</v>
       </c>
@@ -8876,8 +9510,14 @@
       <c r="M105" s="10">
         <v>-21</v>
       </c>
-    </row>
-    <row r="106" spans="2:13" ht="19.8">
+      <c r="O105" s="10">
+        <v>116</v>
+      </c>
+      <c r="P105" s="11">
+        <v>2448</v>
+      </c>
+    </row>
+    <row r="106" spans="2:16" ht="19.8">
       <c r="B106" s="12" t="s">
         <v>149</v>
       </c>
@@ -8914,8 +9554,14 @@
       <c r="M106" s="11">
         <v>1020</v>
       </c>
-    </row>
-    <row r="107" spans="2:13" ht="19.8">
+      <c r="O106" s="10">
+        <v>147</v>
+      </c>
+      <c r="P106" s="11">
+        <v>3077</v>
+      </c>
+    </row>
+    <row r="107" spans="2:16" ht="19.8">
       <c r="B107" s="12" t="s">
         <v>149</v>
       </c>
@@ -8952,8 +9598,14 @@
       <c r="M107" s="11">
         <v>1250</v>
       </c>
-    </row>
-    <row r="108" spans="2:13" ht="19.8">
+      <c r="O107" s="10">
+        <v>151</v>
+      </c>
+      <c r="P107" s="11">
+        <v>1819</v>
+      </c>
+    </row>
+    <row r="108" spans="2:16" ht="19.8">
       <c r="B108" s="12" t="s">
         <v>149</v>
       </c>
@@ -8986,8 +9638,14 @@
       <c r="M108" s="10">
         <v>-43</v>
       </c>
-    </row>
-    <row r="109" spans="2:13" ht="19.8">
+      <c r="O108" s="10">
+        <v>153</v>
+      </c>
+      <c r="P108" s="10">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="109" spans="2:16" ht="19.8">
       <c r="B109" s="12" t="s">
         <v>149</v>
       </c>
@@ -9024,8 +9682,14 @@
       <c r="M109" s="11">
         <v>1836</v>
       </c>
-    </row>
-    <row r="110" spans="2:13" ht="19.8">
+      <c r="O109" s="10">
+        <v>159</v>
+      </c>
+      <c r="P109" s="11">
+        <v>3360</v>
+      </c>
+    </row>
+    <row r="110" spans="2:16" ht="19.8">
       <c r="B110" s="12" t="s">
         <v>149</v>
       </c>
@@ -9062,8 +9726,14 @@
       <c r="M110" s="10">
         <v>250</v>
       </c>
-    </row>
-    <row r="111" spans="2:13" ht="19.8">
+      <c r="O110" s="10">
+        <v>117</v>
+      </c>
+      <c r="P110" s="10">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="111" spans="2:16" ht="19.8">
       <c r="B111" s="12" t="s">
         <v>149</v>
       </c>
@@ -9096,8 +9766,14 @@
       <c r="M111" s="10">
         <v>-77.400000000000006</v>
       </c>
-    </row>
-    <row r="112" spans="2:13" ht="19.8">
+      <c r="O111" s="10">
+        <v>123</v>
+      </c>
+      <c r="P111" s="10">
+        <v>574.5</v>
+      </c>
+    </row>
+    <row r="112" spans="2:16" ht="19.8">
       <c r="B112" s="12" t="s">
         <v>149</v>
       </c>
@@ -9134,8 +9810,14 @@
       <c r="M112" s="11">
         <v>9252</v>
       </c>
-    </row>
-    <row r="113" spans="2:13" ht="19.8">
+      <c r="O112" s="10">
+        <v>124</v>
+      </c>
+      <c r="P112" s="10">
+        <v>626.4</v>
+      </c>
+    </row>
+    <row r="113" spans="2:16" ht="19.8">
       <c r="B113" s="12" t="s">
         <v>149</v>
       </c>
@@ -9170,8 +9852,14 @@
       <c r="M113" s="10">
         <v>-26.8</v>
       </c>
-    </row>
-    <row r="114" spans="2:13" ht="19.8">
+      <c r="O113" s="10">
+        <v>131</v>
+      </c>
+      <c r="P113" s="10">
+        <v>87.6</v>
+      </c>
+    </row>
+    <row r="114" spans="2:16" ht="19.8">
       <c r="B114" s="12" t="s">
         <v>149</v>
       </c>
@@ -9208,8 +9896,14 @@
       <c r="M114" s="11">
         <v>57030</v>
       </c>
-    </row>
-    <row r="115" spans="2:13">
+      <c r="O114" s="10">
+        <v>132</v>
+      </c>
+      <c r="P114" s="10">
+        <v>244.8</v>
+      </c>
+    </row>
+    <row r="115" spans="2:16">
       <c r="B115" s="12" t="s">
         <v>149</v>
       </c>
@@ -9242,8 +9936,14 @@
       <c r="M115" s="11">
         <v>-1327</v>
       </c>
-    </row>
-    <row r="116" spans="2:13" ht="19.8">
+      <c r="O115" s="10">
+        <v>146</v>
+      </c>
+      <c r="P115" s="11">
+        <v>2924</v>
+      </c>
+    </row>
+    <row r="116" spans="2:16" ht="19.8">
       <c r="B116" s="12" t="s">
         <v>149</v>
       </c>
@@ -9280,8 +9980,14 @@
       <c r="M116" s="11">
         <v>6880</v>
       </c>
-    </row>
-    <row r="117" spans="2:13">
+      <c r="O116" s="10">
+        <v>160</v>
+      </c>
+      <c r="P116" s="11">
+        <v>9548</v>
+      </c>
+    </row>
+    <row r="117" spans="2:16">
       <c r="B117" s="12" t="s">
         <v>149</v>
       </c>
@@ -9314,8 +10020,14 @@
       <c r="M117" s="10">
         <v>-192</v>
       </c>
-    </row>
-    <row r="118" spans="2:13" ht="19.8">
+      <c r="O117" s="10">
+        <v>176</v>
+      </c>
+      <c r="P117" s="11">
+        <v>1971</v>
+      </c>
+    </row>
+    <row r="118" spans="2:16" ht="19.8">
       <c r="B118" s="12" t="s">
         <v>149</v>
       </c>
@@ -9352,8 +10064,14 @@
       <c r="M118" s="11">
         <v>61095</v>
       </c>
-    </row>
-    <row r="119" spans="2:13">
+      <c r="O118" s="10">
+        <v>177</v>
+      </c>
+      <c r="P118" s="11">
+        <v>5886</v>
+      </c>
+    </row>
+    <row r="119" spans="2:16">
       <c r="B119" s="12" t="s">
         <v>149</v>
       </c>
@@ -9386,8 +10104,14 @@
       <c r="M119" s="10">
         <v>-985.5</v>
       </c>
-    </row>
-    <row r="120" spans="2:13" ht="19.8">
+      <c r="O119" s="10">
+        <v>180</v>
+      </c>
+      <c r="P119" s="10">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="120" spans="2:16" ht="19.8">
       <c r="B120" s="12" t="s">
         <v>149</v>
       </c>
@@ -9424,8 +10148,14 @@
       <c r="M120" s="11">
         <v>32450</v>
       </c>
-    </row>
-    <row r="121" spans="2:13">
+      <c r="O120" s="10">
+        <v>182</v>
+      </c>
+      <c r="P120" s="11">
+        <v>2133</v>
+      </c>
+    </row>
+    <row r="121" spans="2:16">
       <c r="B121" s="12" t="s">
         <v>149</v>
       </c>
@@ -9458,8 +10188,14 @@
       <c r="M121" s="10">
         <v>-205</v>
       </c>
-    </row>
-    <row r="122" spans="2:13" ht="19.8">
+      <c r="O121" s="10">
+        <v>118</v>
+      </c>
+      <c r="P121" s="10">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="122" spans="2:16" ht="19.8">
       <c r="B122" s="12" t="s">
         <v>149</v>
       </c>
@@ -9496,8 +10232,14 @@
       <c r="M122" s="11">
         <v>30010</v>
       </c>
-    </row>
-    <row r="123" spans="2:13">
+      <c r="O122" s="10">
+        <v>119</v>
+      </c>
+      <c r="P122" s="10">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="123" spans="2:16">
       <c r="B123" s="12" t="s">
         <v>149</v>
       </c>
@@ -9530,8 +10272,14 @@
       <c r="M123" s="10">
         <v>-9</v>
       </c>
-    </row>
-    <row r="124" spans="2:13" ht="19.8">
+      <c r="O123" s="10">
+        <v>125</v>
+      </c>
+      <c r="P123" s="10">
+        <v>141.6</v>
+      </c>
+    </row>
+    <row r="124" spans="2:16" ht="19.8">
       <c r="B124" s="12" t="s">
         <v>149</v>
       </c>
@@ -9568,8 +10316,14 @@
       <c r="M124" s="11">
         <v>20700</v>
       </c>
-    </row>
-    <row r="125" spans="2:13">
+      <c r="O124" s="10">
+        <v>150</v>
+      </c>
+      <c r="P124" s="10">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="125" spans="2:16">
       <c r="B125" s="12" t="s">
         <v>149</v>
       </c>
@@ -9602,8 +10356,14 @@
       <c r="M125" s="10">
         <v>-130</v>
       </c>
-    </row>
-    <row r="126" spans="2:13" ht="19.8">
+      <c r="O125" s="10">
+        <v>152</v>
+      </c>
+      <c r="P125" s="11">
+        <v>1938</v>
+      </c>
+    </row>
+    <row r="126" spans="2:16" ht="19.8">
       <c r="B126" s="12" t="s">
         <v>149</v>
       </c>
@@ -9640,8 +10400,14 @@
       <c r="M126" s="11">
         <v>3000</v>
       </c>
-    </row>
-    <row r="127" spans="2:13" ht="19.8">
+      <c r="O126" s="10">
+        <v>114</v>
+      </c>
+      <c r="P126" s="11">
+        <v>1727.1</v>
+      </c>
+    </row>
+    <row r="127" spans="2:16" ht="19.8">
       <c r="B127" s="12" t="s">
         <v>149</v>
       </c>
@@ -9678,8 +10444,14 @@
       <c r="M127" s="11">
         <v>19260</v>
       </c>
-    </row>
-    <row r="128" spans="2:13">
+      <c r="O127" s="10">
+        <v>120</v>
+      </c>
+      <c r="P127" s="10">
+        <v>169.6</v>
+      </c>
+    </row>
+    <row r="128" spans="2:16">
       <c r="B128" s="12" t="s">
         <v>149</v>
       </c>
@@ -9712,8 +10484,14 @@
       <c r="M128" s="10">
         <v>-34</v>
       </c>
-    </row>
-    <row r="129" spans="2:13" ht="19.8">
+      <c r="O128" s="10">
+        <v>121</v>
+      </c>
+      <c r="P128" s="10">
+        <v>952</v>
+      </c>
+    </row>
+    <row r="129" spans="2:16" ht="19.8">
       <c r="B129" s="12" t="s">
         <v>149</v>
       </c>
@@ -9750,8 +10528,14 @@
       <c r="M129" s="11">
         <v>3240</v>
       </c>
-    </row>
-    <row r="130" spans="2:13" ht="19.8">
+      <c r="O129" s="10">
+        <v>134</v>
+      </c>
+      <c r="P129" s="11">
+        <v>1122</v>
+      </c>
+    </row>
+    <row r="130" spans="2:16" ht="19.8">
       <c r="B130" s="12" t="s">
         <v>149</v>
       </c>
@@ -9788,8 +10572,14 @@
       <c r="M130" s="11">
         <v>1260</v>
       </c>
-    </row>
-    <row r="131" spans="2:13" ht="19.8">
+      <c r="O130" s="10">
+        <v>148</v>
+      </c>
+      <c r="P130" s="11">
+        <v>2346</v>
+      </c>
+    </row>
+    <row r="131" spans="2:16" ht="19.8">
       <c r="B131" s="12" t="s">
         <v>149</v>
       </c>
@@ -9822,8 +10612,14 @@
       <c r="M131" s="10">
         <v>-50</v>
       </c>
-    </row>
-    <row r="132" spans="2:13" ht="19.8">
+      <c r="O131" s="10">
+        <v>149</v>
+      </c>
+      <c r="P131" s="11">
+        <v>2091</v>
+      </c>
+    </row>
+    <row r="132" spans="2:16" ht="19.8">
       <c r="B132" s="12" t="s">
         <v>149</v>
       </c>
@@ -9860,8 +10656,14 @@
       <c r="M132" s="10">
         <v>900</v>
       </c>
-    </row>
-    <row r="133" spans="2:13" ht="19.8">
+      <c r="O132" s="10">
+        <v>178</v>
+      </c>
+      <c r="P132" s="11">
+        <v>4428</v>
+      </c>
+    </row>
+    <row r="133" spans="2:16" ht="19.8">
       <c r="B133" s="12" t="s">
         <v>149</v>
       </c>
@@ -9898,8 +10700,14 @@
       <c r="M133" s="11">
         <v>17640</v>
       </c>
-    </row>
-    <row r="134" spans="2:13" ht="19.8">
+      <c r="O133" s="10">
+        <v>179</v>
+      </c>
+      <c r="P133" s="10">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="134" spans="2:16" ht="19.8">
       <c r="B134" s="12" t="s">
         <v>149</v>
       </c>
@@ -9932,8 +10740,14 @@
       <c r="M134" s="10">
         <v>-86</v>
       </c>
-    </row>
-    <row r="135" spans="2:13" ht="19.8">
+      <c r="O134" s="10">
+        <v>122</v>
+      </c>
+      <c r="P134" s="10">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="135" spans="2:16" ht="19.8">
       <c r="B135" s="12" t="s">
         <v>149</v>
       </c>
@@ -9970,8 +10784,14 @@
       <c r="M135" s="11">
         <v>1480</v>
       </c>
-    </row>
-    <row r="136" spans="2:13" ht="19.8">
+      <c r="O135" s="10">
+        <v>126</v>
+      </c>
+      <c r="P135" s="11">
+        <v>1453.7</v>
+      </c>
+    </row>
+    <row r="136" spans="2:16" ht="19.8">
       <c r="B136" s="12" t="s">
         <v>149</v>
       </c>
@@ -10004,8 +10824,14 @@
       <c r="M136" s="10">
         <v>-32</v>
       </c>
-    </row>
-    <row r="137" spans="2:13" ht="19.8">
+      <c r="O136" s="10">
+        <v>127</v>
+      </c>
+      <c r="P136" s="10">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="137" spans="2:16" ht="19.8">
       <c r="B137" s="12" t="s">
         <v>149</v>
       </c>
@@ -10042,8 +10868,14 @@
       <c r="M137" s="11">
         <v>2700</v>
       </c>
-    </row>
-    <row r="138" spans="2:13" ht="19.8">
+      <c r="O137" s="10">
+        <v>128</v>
+      </c>
+      <c r="P137" s="10">
+        <v>911</v>
+      </c>
+    </row>
+    <row r="138" spans="2:16" ht="19.8">
       <c r="B138" s="12" t="s">
         <v>149</v>
       </c>
@@ -10080,8 +10912,14 @@
       <c r="M138" s="11">
         <v>9720</v>
       </c>
-    </row>
-    <row r="139" spans="2:13" ht="19.8">
+      <c r="O138" s="10">
+        <v>129</v>
+      </c>
+      <c r="P138" s="10">
+        <v>903.6</v>
+      </c>
+    </row>
+    <row r="139" spans="2:16" ht="19.8">
       <c r="B139" s="12" t="s">
         <v>149</v>
       </c>
@@ -10118,8 +10956,14 @@
       <c r="M139" s="10">
         <v>810</v>
       </c>
-    </row>
-    <row r="140" spans="2:13">
+      <c r="O139" s="10">
+        <v>136</v>
+      </c>
+      <c r="P139" s="10">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="140" spans="2:16">
       <c r="B140" s="12" t="s">
         <v>149</v>
       </c>
@@ -10152,8 +10996,14 @@
       <c r="M140" s="10">
         <v>-7</v>
       </c>
-    </row>
-    <row r="141" spans="2:13" ht="19.8">
+      <c r="O140" s="10">
+        <v>137</v>
+      </c>
+      <c r="P140" s="10">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="141" spans="2:16" ht="19.8">
       <c r="B141" s="12" t="s">
         <v>149</v>
       </c>
@@ -10190,8 +11040,14 @@
       <c r="M141" s="11">
         <v>39150</v>
       </c>
-    </row>
-    <row r="142" spans="2:13">
+      <c r="O141" s="10">
+        <v>140</v>
+      </c>
+      <c r="P141" s="10">
+        <v>859.2</v>
+      </c>
+    </row>
+    <row r="142" spans="2:16">
       <c r="B142" s="12" t="s">
         <v>149</v>
       </c>
@@ -10224,8 +11080,14 @@
       <c r="M142" s="10">
         <v>-35</v>
       </c>
-    </row>
-    <row r="143" spans="2:13" ht="19.8">
+      <c r="O142" s="10">
+        <v>141</v>
+      </c>
+      <c r="P142" s="10">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="143" spans="2:16" ht="19.8">
       <c r="B143" s="12" t="s">
         <v>149</v>
       </c>
@@ -10262,8 +11124,14 @@
       <c r="M143" s="11">
         <v>26350</v>
       </c>
-    </row>
-    <row r="144" spans="2:13" ht="19.8">
+      <c r="O143" s="10">
+        <v>130</v>
+      </c>
+      <c r="P143" s="10">
+        <v>387.5</v>
+      </c>
+    </row>
+    <row r="144" spans="2:16" ht="19.8">
       <c r="B144" s="12" t="s">
         <v>149</v>
       </c>
@@ -10296,8 +11164,14 @@
       <c r="M144" s="10">
         <v>-15</v>
       </c>
-    </row>
-    <row r="145" spans="2:13" ht="19.8">
+      <c r="O144" s="10">
+        <v>133</v>
+      </c>
+      <c r="P144" s="11">
+        <v>4654</v>
+      </c>
+    </row>
+    <row r="145" spans="2:16" ht="19.8">
       <c r="B145" s="5">
         <v>45264</v>
       </c>
@@ -10334,8 +11208,14 @@
       <c r="M145" s="11">
         <v>2625</v>
       </c>
-    </row>
-    <row r="146" spans="2:13" ht="19.8">
+      <c r="O145" s="10">
+        <v>138</v>
+      </c>
+      <c r="P145" s="10">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="146" spans="2:16" ht="19.8">
       <c r="B146" s="5">
         <v>45264</v>
       </c>
@@ -10368,8 +11248,14 @@
       <c r="M146" s="10">
         <v>-63</v>
       </c>
-    </row>
-    <row r="147" spans="2:13" ht="19.8">
+      <c r="O146" s="10">
+        <v>145</v>
+      </c>
+      <c r="P146" s="11">
+        <v>1792</v>
+      </c>
+    </row>
+    <row r="147" spans="2:16" ht="19.8">
       <c r="B147" s="5">
         <v>45264</v>
       </c>
@@ -10406,8 +11292,14 @@
       <c r="M147" s="11">
         <v>5742</v>
       </c>
-    </row>
-    <row r="148" spans="2:13" ht="19.8">
+      <c r="O147" s="10">
+        <v>161</v>
+      </c>
+      <c r="P147" s="10">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="148" spans="2:16" ht="19.8">
       <c r="B148" s="5">
         <v>45264</v>
       </c>
@@ -10440,8 +11332,14 @@
       <c r="M148" s="10">
         <v>-68</v>
       </c>
-    </row>
-    <row r="149" spans="2:13" ht="19.8">
+      <c r="O148" s="10">
+        <v>162</v>
+      </c>
+      <c r="P148" s="10">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="149" spans="2:16" ht="19.8">
       <c r="B149" s="12" t="s">
         <v>203</v>
       </c>
@@ -10478,8 +11376,14 @@
       <c r="M149" s="11">
         <v>8000</v>
       </c>
-    </row>
-    <row r="150" spans="2:13" ht="19.8">
+      <c r="O149" s="10">
+        <v>169</v>
+      </c>
+      <c r="P149" s="11">
+        <v>1735.5</v>
+      </c>
+    </row>
+    <row r="150" spans="2:16" ht="19.8">
       <c r="B150" s="12" t="s">
         <v>205</v>
       </c>
@@ -10516,8 +11420,14 @@
       <c r="M150" s="11">
         <v>41500</v>
       </c>
-    </row>
-    <row r="151" spans="2:13" ht="19.8">
+      <c r="O150" s="10">
+        <v>181</v>
+      </c>
+      <c r="P150" s="11">
+        <v>2241</v>
+      </c>
+    </row>
+    <row r="151" spans="2:16" ht="19.8">
       <c r="B151" s="12" t="s">
         <v>208</v>
       </c>
@@ -10554,8 +11464,14 @@
       <c r="M151" s="11">
         <v>5220</v>
       </c>
-    </row>
-    <row r="152" spans="2:13" ht="19.8">
+      <c r="O151" s="10">
+        <v>139</v>
+      </c>
+      <c r="P151" s="11">
+        <v>4824</v>
+      </c>
+    </row>
+    <row r="152" spans="2:16" ht="19.8">
       <c r="B152" s="12" t="s">
         <v>208</v>
       </c>
@@ -10588,8 +11504,14 @@
       <c r="M152" s="10">
         <v>-98</v>
       </c>
-    </row>
-    <row r="153" spans="2:13" ht="19.8">
+      <c r="O152" s="10">
+        <v>143</v>
+      </c>
+      <c r="P152" s="10">
+        <v>884</v>
+      </c>
+    </row>
+    <row r="153" spans="2:16" ht="19.8">
       <c r="B153" s="12" t="s">
         <v>211</v>
       </c>
@@ -10626,8 +11548,14 @@
       <c r="M153" s="11">
         <v>24258</v>
       </c>
-    </row>
-    <row r="154" spans="2:13" ht="19.8">
+      <c r="O153" s="10">
+        <v>144</v>
+      </c>
+      <c r="P153" s="10">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="154" spans="2:16" ht="19.8">
       <c r="B154" s="12" t="s">
         <v>211</v>
       </c>
@@ -10664,8 +11592,14 @@
       <c r="M154" s="11">
         <v>2592</v>
       </c>
-    </row>
-    <row r="155" spans="2:13">
+      <c r="O154" s="10">
+        <v>167</v>
+      </c>
+      <c r="P154" s="10">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="155" spans="2:16">
       <c r="B155" s="12" t="s">
         <v>211</v>
       </c>
@@ -10698,8 +11632,14 @@
       <c r="M155" s="10">
         <v>-165</v>
       </c>
-    </row>
-    <row r="156" spans="2:13" ht="19.8">
+      <c r="O155" s="10">
+        <v>168</v>
+      </c>
+      <c r="P155" s="11">
+        <v>1943.5</v>
+      </c>
+    </row>
+    <row r="156" spans="2:16" ht="19.8">
       <c r="B156" s="12" t="s">
         <v>211</v>
       </c>
@@ -10736,8 +11676,14 @@
       <c r="M156" s="11">
         <v>9600</v>
       </c>
-    </row>
-    <row r="157" spans="2:13" ht="19.8">
+      <c r="O156" s="10">
+        <v>156</v>
+      </c>
+      <c r="P156" s="11">
+        <v>2352</v>
+      </c>
+    </row>
+    <row r="157" spans="2:16" ht="19.8">
       <c r="B157" s="12" t="s">
         <v>211</v>
       </c>
@@ -10774,8 +11720,14 @@
       <c r="M157" s="11">
         <v>2700</v>
       </c>
-    </row>
-    <row r="158" spans="2:13" ht="19.8">
+      <c r="O157" s="10">
+        <v>157</v>
+      </c>
+      <c r="P157" s="11">
+        <v>13020</v>
+      </c>
+    </row>
+    <row r="158" spans="2:16" ht="19.8">
       <c r="B158" s="12" t="s">
         <v>211</v>
       </c>
@@ -10808,8 +11760,14 @@
       <c r="M158" s="10">
         <v>-70</v>
       </c>
-    </row>
-    <row r="159" spans="2:13" ht="19.8">
+      <c r="O158" s="10">
+        <v>158</v>
+      </c>
+      <c r="P158" s="11">
+        <v>6076</v>
+      </c>
+    </row>
+    <row r="159" spans="2:16" ht="19.8">
       <c r="B159" s="12" t="s">
         <v>211</v>
       </c>
@@ -10846,8 +11804,14 @@
       <c r="M159" s="11">
         <v>5700</v>
       </c>
-    </row>
-    <row r="160" spans="2:13" ht="19.8">
+      <c r="O159" s="10">
+        <v>163</v>
+      </c>
+      <c r="P159" s="11">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="160" spans="2:16" ht="19.8">
       <c r="B160" s="12" t="s">
         <v>211</v>
       </c>
@@ -10884,8 +11848,14 @@
       <c r="M160" s="10">
         <v>925</v>
       </c>
-    </row>
-    <row r="161" spans="2:13" ht="19.8">
+      <c r="O160" s="10">
+        <v>164</v>
+      </c>
+      <c r="P160" s="10">
+        <v>449.6</v>
+      </c>
+    </row>
+    <row r="161" spans="2:16" ht="19.8">
       <c r="B161" s="12" t="s">
         <v>211</v>
       </c>
@@ -10918,8 +11888,14 @@
       <c r="M161" s="10">
         <v>-62.5</v>
       </c>
-    </row>
-    <row r="162" spans="2:13" ht="19.8">
+      <c r="O161" s="10">
+        <v>165</v>
+      </c>
+      <c r="P161" s="10">
+        <v>246.4</v>
+      </c>
+    </row>
+    <row r="162" spans="2:16" ht="19.8">
       <c r="B162" s="12" t="s">
         <v>211</v>
       </c>
@@ -10956,8 +11932,14 @@
       <c r="M162" s="11">
         <v>3936</v>
       </c>
-    </row>
-    <row r="163" spans="2:13" ht="19.8">
+      <c r="O162" s="10">
+        <v>166</v>
+      </c>
+      <c r="P162" s="10">
+        <v>163.19999999999999</v>
+      </c>
+    </row>
+    <row r="163" spans="2:16" ht="19.8">
       <c r="B163" s="12" t="s">
         <v>211</v>
       </c>
@@ -10994,8 +11976,14 @@
       <c r="M163" s="10">
         <v>495</v>
       </c>
-    </row>
-    <row r="164" spans="2:13" ht="19.8">
+      <c r="O163" s="10">
+        <v>183</v>
+      </c>
+      <c r="P163" s="10">
+        <v>161.5</v>
+      </c>
+    </row>
+    <row r="164" spans="2:16" ht="19.8">
       <c r="B164" s="12" t="s">
         <v>211</v>
       </c>
@@ -11028,8 +12016,14 @@
       <c r="M164" s="10">
         <v>-88</v>
       </c>
-    </row>
-    <row r="165" spans="2:13" ht="19.8">
+      <c r="O164" s="10">
+        <v>184</v>
+      </c>
+      <c r="P164" s="10">
+        <v>756.5</v>
+      </c>
+    </row>
+    <row r="165" spans="2:16" ht="19.8">
       <c r="B165" s="12" t="s">
         <v>211</v>
       </c>
@@ -11066,8 +12060,14 @@
       <c r="M165" s="11">
         <v>18360</v>
       </c>
-    </row>
-    <row r="166" spans="2:13">
+      <c r="O165" s="10">
+        <v>185</v>
+      </c>
+      <c r="P165" s="10">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="166" spans="2:16">
       <c r="B166" s="12" t="s">
         <v>211</v>
       </c>
@@ -11100,8 +12100,14 @@
       <c r="M166" s="10">
         <v>-24</v>
       </c>
-    </row>
-    <row r="167" spans="2:13" ht="19.8">
+      <c r="O166" s="10">
+        <v>186</v>
+      </c>
+      <c r="P166" s="10">
+        <v>332.8</v>
+      </c>
+    </row>
+    <row r="167" spans="2:16" ht="19.8">
       <c r="B167" s="12" t="s">
         <v>211</v>
       </c>
@@ -11138,8 +12144,14 @@
       <c r="M167" s="11">
         <v>47790</v>
       </c>
-    </row>
-    <row r="168" spans="2:13">
+      <c r="O167" s="10">
+        <v>187</v>
+      </c>
+      <c r="P167" s="10">
+        <v>420.8</v>
+      </c>
+    </row>
+    <row r="168" spans="2:16">
       <c r="B168" s="12" t="s">
         <v>211</v>
       </c>
@@ -11172,8 +12184,14 @@
       <c r="M168" s="10">
         <v>-11</v>
       </c>
-    </row>
-    <row r="169" spans="2:13" ht="19.8">
+      <c r="O168" s="10">
+        <v>188</v>
+      </c>
+      <c r="P168" s="11">
+        <v>5670</v>
+      </c>
+    </row>
+    <row r="169" spans="2:16" ht="19.8">
       <c r="B169" s="12" t="s">
         <v>211</v>
       </c>
@@ -11210,8 +12228,14 @@
       <c r="M169" s="11">
         <v>9620</v>
       </c>
-    </row>
-    <row r="170" spans="2:13">
+      <c r="O169" s="10">
+        <v>190</v>
+      </c>
+      <c r="P169" s="10">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="170" spans="2:16">
       <c r="B170" s="12" t="s">
         <v>211</v>
       </c>
@@ -11244,8 +12268,14 @@
       <c r="M170" s="10">
         <v>-58</v>
       </c>
-    </row>
-    <row r="171" spans="2:13" ht="19.8">
+      <c r="O170" s="10">
+        <v>192</v>
+      </c>
+      <c r="P170" s="11">
+        <v>2003</v>
+      </c>
+    </row>
+    <row r="171" spans="2:16" ht="19.8">
       <c r="B171" s="12" t="s">
         <v>211</v>
       </c>
@@ -11282,8 +12312,14 @@
       <c r="M171" s="11">
         <v>10260</v>
       </c>
-    </row>
-    <row r="172" spans="2:13">
+      <c r="O171" s="10">
+        <v>191</v>
+      </c>
+      <c r="P171" s="11">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="172" spans="2:16">
       <c r="B172" s="12" t="s">
         <v>211</v>
       </c>
@@ -11316,8 +12352,14 @@
       <c r="M172" s="10">
         <v>-34</v>
       </c>
-    </row>
-    <row r="173" spans="2:13" ht="19.8">
+      <c r="O172" s="10">
+        <v>194</v>
+      </c>
+      <c r="P172" s="11">
+        <v>1944</v>
+      </c>
+    </row>
+    <row r="173" spans="2:16" ht="19.8">
       <c r="B173" s="12" t="s">
         <v>211</v>
       </c>
@@ -11354,8 +12396,14 @@
       <c r="M173" s="11">
         <v>1870</v>
       </c>
-    </row>
-    <row r="174" spans="2:13" ht="19.8">
+      <c r="O173" s="10">
+        <v>195</v>
+      </c>
+      <c r="P173" s="11">
+        <v>2466.1999999999998</v>
+      </c>
+    </row>
+    <row r="174" spans="2:16" ht="19.8">
       <c r="B174" s="12" t="s">
         <v>211</v>
       </c>
@@ -11388,8 +12436,14 @@
       <c r="M174" s="10">
         <v>-83</v>
       </c>
-    </row>
-    <row r="175" spans="2:13" ht="19.8">
+      <c r="O174" s="10">
+        <v>196</v>
+      </c>
+      <c r="P174" s="10">
+        <v>486.5</v>
+      </c>
+    </row>
+    <row r="175" spans="2:16" ht="19.8">
       <c r="B175" s="12" t="s">
         <v>211</v>
       </c>
@@ -11426,8 +12480,14 @@
       <c r="M175" s="11">
         <v>24310</v>
       </c>
-    </row>
-    <row r="176" spans="2:13" ht="19.8">
+      <c r="O175" s="10">
+        <v>197</v>
+      </c>
+      <c r="P175" s="10">
+        <v>488.8</v>
+      </c>
+    </row>
+    <row r="176" spans="2:16" ht="19.8">
       <c r="B176" s="12" t="s">
         <v>211</v>
       </c>
@@ -11460,8 +12520,14 @@
       <c r="M176" s="10">
         <v>-79</v>
       </c>
-    </row>
-    <row r="177" spans="2:13" ht="19.8">
+      <c r="O176" s="10">
+        <v>198</v>
+      </c>
+      <c r="P176" s="11">
+        <v>2964</v>
+      </c>
+    </row>
+    <row r="177" spans="2:16" ht="19.8">
       <c r="B177" s="12" t="s">
         <v>211</v>
       </c>
@@ -11498,8 +12564,14 @@
       <c r="M177" s="11">
         <v>23290</v>
       </c>
-    </row>
-    <row r="178" spans="2:13" ht="19.8">
+      <c r="O177" s="10">
+        <v>200</v>
+      </c>
+      <c r="P177" s="10">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="178" spans="2:16" ht="19.8">
       <c r="B178" s="12" t="s">
         <v>211</v>
       </c>
@@ -11532,8 +12604,14 @@
       <c r="M178" s="10">
         <v>-61</v>
       </c>
-    </row>
-    <row r="179" spans="2:13" ht="19.8">
+      <c r="O178" s="10">
+        <v>201</v>
+      </c>
+      <c r="P178" s="10">
+        <v>362.4</v>
+      </c>
+    </row>
+    <row r="179" spans="2:16" ht="19.8">
       <c r="B179" s="12" t="s">
         <v>211</v>
       </c>
@@ -11570,8 +12648,14 @@
       <c r="M179" s="11">
         <v>12000</v>
       </c>
-    </row>
-    <row r="180" spans="2:13" ht="19.8">
+      <c r="O179" s="10">
+        <v>202</v>
+      </c>
+      <c r="P179" s="10">
+        <v>511.5</v>
+      </c>
+    </row>
+    <row r="180" spans="2:16" ht="19.8">
       <c r="B180" s="12" t="s">
         <v>211</v>
       </c>
@@ -11608,8 +12692,14 @@
       <c r="M180" s="11">
         <v>10000</v>
       </c>
-    </row>
-    <row r="181" spans="2:13" ht="19.8">
+      <c r="O180" s="10">
+        <v>203</v>
+      </c>
+      <c r="P180" s="11">
+        <v>1779.8</v>
+      </c>
+    </row>
+    <row r="181" spans="2:16" ht="19.8">
       <c r="B181" s="12" t="s">
         <v>211</v>
       </c>
@@ -11646,8 +12736,14 @@
       <c r="M181" s="11">
         <v>9000</v>
       </c>
-    </row>
-    <row r="182" spans="2:13" ht="19.8">
+      <c r="O181" s="10">
+        <v>204</v>
+      </c>
+      <c r="P181" s="10">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="182" spans="2:16" ht="19.8">
       <c r="B182" s="12" t="s">
         <v>211</v>
       </c>
@@ -11684,8 +12780,14 @@
       <c r="M182" s="11">
         <v>20000</v>
       </c>
-    </row>
-    <row r="183" spans="2:13" ht="19.8">
+      <c r="O182" s="10">
+        <v>211</v>
+      </c>
+      <c r="P182" s="11">
+        <v>1030.4000000000001</v>
+      </c>
+    </row>
+    <row r="183" spans="2:16" ht="19.8">
       <c r="B183" s="12" t="s">
         <v>211</v>
       </c>
@@ -11722,8 +12824,14 @@
       <c r="M183" s="11">
         <v>2720</v>
       </c>
-    </row>
-    <row r="184" spans="2:13" ht="19.8">
+      <c r="O183" s="10">
+        <v>214</v>
+      </c>
+      <c r="P183" s="10">
+        <v>863.2</v>
+      </c>
+    </row>
+    <row r="184" spans="2:16" ht="19.8">
       <c r="B184" s="12" t="s">
         <v>211</v>
       </c>
@@ -11756,8 +12864,14 @@
       <c r="M184" s="10">
         <v>-48</v>
       </c>
-    </row>
-    <row r="185" spans="2:13" ht="19.8">
+      <c r="O184" s="10">
+        <v>233</v>
+      </c>
+      <c r="P184" s="11">
+        <v>1294.8</v>
+      </c>
+    </row>
+    <row r="185" spans="2:16" ht="19.8">
       <c r="B185" s="12" t="s">
         <v>211</v>
       </c>
@@ -11794,8 +12908,14 @@
       <c r="M185" s="11">
         <v>25740</v>
       </c>
-    </row>
-    <row r="186" spans="2:13" ht="19.8">
+      <c r="O185" s="10">
+        <v>234</v>
+      </c>
+      <c r="P185" s="11">
+        <v>1396.8</v>
+      </c>
+    </row>
+    <row r="186" spans="2:16" ht="19.8">
       <c r="B186" s="12" t="s">
         <v>211</v>
       </c>
@@ -11828,8 +12948,14 @@
       <c r="M186" s="10">
         <v>-66</v>
       </c>
-    </row>
-    <row r="187" spans="2:13" ht="19.8">
+      <c r="O186" s="10">
+        <v>247</v>
+      </c>
+      <c r="P186" s="11">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="187" spans="2:16" ht="19.8">
       <c r="B187" s="12" t="s">
         <v>211</v>
       </c>
@@ -11866,8 +12992,14 @@
       <c r="M187" s="11">
         <v>1620</v>
       </c>
-    </row>
-    <row r="188" spans="2:13" ht="19.8">
+      <c r="O187" s="10">
+        <v>189</v>
+      </c>
+      <c r="P187" s="11">
+        <v>3610</v>
+      </c>
+    </row>
+    <row r="188" spans="2:16" ht="19.8">
       <c r="B188" s="12" t="s">
         <v>211</v>
       </c>
@@ -11900,8 +13032,14 @@
       <c r="M188" s="10">
         <v>-58</v>
       </c>
-    </row>
-    <row r="189" spans="2:13" ht="19.8">
+      <c r="O188" s="10">
+        <v>193</v>
+      </c>
+      <c r="P188" s="10">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="189" spans="2:16" ht="19.8">
       <c r="B189" s="12" t="s">
         <v>211</v>
       </c>
@@ -11938,8 +13076,14 @@
       <c r="M189" s="11">
         <v>2040</v>
       </c>
-    </row>
-    <row r="190" spans="2:13" ht="19.8">
+      <c r="O189" s="10">
+        <v>199</v>
+      </c>
+      <c r="P189" s="11">
+        <v>1115</v>
+      </c>
+    </row>
+    <row r="190" spans="2:16" ht="19.8">
       <c r="B190" s="12" t="s">
         <v>211</v>
       </c>
@@ -11972,8 +13116,14 @@
       <c r="M190" s="10">
         <v>-36</v>
       </c>
-    </row>
-    <row r="191" spans="2:13" ht="19.8">
+      <c r="O190" s="10">
+        <v>205</v>
+      </c>
+      <c r="P190" s="11">
+        <v>1011</v>
+      </c>
+    </row>
+    <row r="191" spans="2:16" ht="19.8">
       <c r="B191" s="5">
         <v>45204</v>
       </c>
@@ -12010,8 +13160,14 @@
       <c r="M191" s="10">
         <v>500</v>
       </c>
-    </row>
-    <row r="192" spans="2:13" ht="19.8">
+      <c r="O191" s="10">
+        <v>206</v>
+      </c>
+      <c r="P191" s="11">
+        <v>2165.6</v>
+      </c>
+    </row>
+    <row r="192" spans="2:16" ht="19.8">
       <c r="B192" s="5">
         <v>45235</v>
       </c>
@@ -12048,8 +13204,14 @@
       <c r="M192" s="11">
         <v>6773</v>
       </c>
-    </row>
-    <row r="193" spans="2:13" ht="19.8">
+      <c r="O192" s="10">
+        <v>207</v>
+      </c>
+      <c r="P192" s="11">
+        <v>2310</v>
+      </c>
+    </row>
+    <row r="193" spans="2:16" ht="19.8">
       <c r="B193" s="5">
         <v>45235</v>
       </c>
@@ -12086,8 +13248,14 @@
       <c r="M193" s="10">
         <v>468</v>
       </c>
-    </row>
-    <row r="194" spans="2:13" ht="19.8">
+      <c r="O193" s="10">
+        <v>208</v>
+      </c>
+      <c r="P193" s="11">
+        <v>2174</v>
+      </c>
+    </row>
+    <row r="194" spans="2:16" ht="19.8">
       <c r="B194" s="5">
         <v>45235</v>
       </c>
@@ -12124,8 +13292,14 @@
       <c r="M194" s="10">
         <v>125</v>
       </c>
-    </row>
-    <row r="195" spans="2:13">
+      <c r="O194" s="10">
+        <v>209</v>
+      </c>
+      <c r="P194" s="10">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="195" spans="2:16">
       <c r="B195" s="5">
         <v>45235</v>
       </c>
@@ -12158,8 +13332,14 @@
       <c r="M195" s="10">
         <v>-30</v>
       </c>
-    </row>
-    <row r="196" spans="2:13" ht="19.8">
+      <c r="O195" s="10">
+        <v>210</v>
+      </c>
+      <c r="P195" s="10">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="196" spans="2:16" ht="19.8">
       <c r="B196" s="5">
         <v>45235</v>
       </c>
@@ -12196,8 +13376,14 @@
       <c r="M196" s="11">
         <v>10080</v>
       </c>
-    </row>
-    <row r="197" spans="2:13" ht="19.8">
+      <c r="O196" s="10">
+        <v>212</v>
+      </c>
+      <c r="P196" s="10">
+        <v>618.79999999999995</v>
+      </c>
+    </row>
+    <row r="197" spans="2:16" ht="19.8">
       <c r="B197" s="5">
         <v>45235</v>
       </c>
@@ -12230,8 +13416,14 @@
       <c r="M197" s="10">
         <v>-72</v>
       </c>
-    </row>
-    <row r="198" spans="2:13" ht="19.8">
+      <c r="O197" s="10">
+        <v>215</v>
+      </c>
+      <c r="P197" s="11">
+        <v>1045.5999999999999</v>
+      </c>
+    </row>
+    <row r="198" spans="2:16" ht="19.8">
       <c r="B198" s="12" t="s">
         <v>264</v>
       </c>
@@ -12268,8 +13460,14 @@
       <c r="M198" s="11">
         <v>34380</v>
       </c>
-    </row>
-    <row r="199" spans="2:13" ht="19.8">
+      <c r="O198" s="10">
+        <v>216</v>
+      </c>
+      <c r="P198" s="10">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="199" spans="2:16" ht="19.8">
       <c r="B199" s="12" t="s">
         <v>264</v>
       </c>
@@ -12302,8 +13500,14 @@
       <c r="M199" s="10">
         <v>-42</v>
       </c>
-    </row>
-    <row r="200" spans="2:13" ht="19.8">
+      <c r="O199" s="10">
+        <v>217</v>
+      </c>
+      <c r="P199" s="11">
+        <v>1290</v>
+      </c>
+    </row>
+    <row r="200" spans="2:16" ht="19.8">
       <c r="B200" s="12" t="s">
         <v>267</v>
       </c>
@@ -12340,8 +13544,14 @@
       <c r="M200" s="11">
         <v>5040</v>
       </c>
-    </row>
-    <row r="201" spans="2:13" ht="19.8">
+      <c r="O200" s="10">
+        <v>218</v>
+      </c>
+      <c r="P200" s="11">
+        <v>1239</v>
+      </c>
+    </row>
+    <row r="201" spans="2:16" ht="19.8">
       <c r="B201" s="12" t="s">
         <v>267</v>
       </c>
@@ -12378,8 +13588,14 @@
       <c r="M201" s="11">
         <v>2375</v>
       </c>
-    </row>
-    <row r="202" spans="2:13" ht="19.8">
+      <c r="O201" s="10">
+        <v>220</v>
+      </c>
+      <c r="P201" s="10">
+        <v>890.5</v>
+      </c>
+    </row>
+    <row r="202" spans="2:16" ht="19.8">
       <c r="B202" s="12" t="s">
         <v>267</v>
       </c>
@@ -12412,8 +13628,14 @@
       <c r="M202" s="10">
         <v>-73</v>
       </c>
-    </row>
-    <row r="203" spans="2:13" ht="19.8">
+      <c r="O202" s="10">
+        <v>221</v>
+      </c>
+      <c r="P202" s="10">
+        <v>266.8</v>
+      </c>
+    </row>
+    <row r="203" spans="2:16" ht="19.8">
       <c r="B203" s="12" t="s">
         <v>271</v>
       </c>
@@ -12450,8 +13672,14 @@
       <c r="M203" s="11">
         <v>8400</v>
       </c>
-    </row>
-    <row r="204" spans="2:13" ht="19.8">
+      <c r="O203" s="10">
+        <v>222</v>
+      </c>
+      <c r="P203" s="10">
+        <v>181.9</v>
+      </c>
+    </row>
+    <row r="204" spans="2:16" ht="19.8">
       <c r="B204" s="12" t="s">
         <v>271</v>
       </c>
@@ -12488,8 +13716,14 @@
       <c r="M204" s="11">
         <v>3400</v>
       </c>
-    </row>
-    <row r="205" spans="2:13">
+      <c r="O204" s="10">
+        <v>223</v>
+      </c>
+      <c r="P204" s="10">
+        <v>165.4</v>
+      </c>
+    </row>
+    <row r="205" spans="2:16">
       <c r="B205" s="12" t="s">
         <v>271</v>
       </c>
@@ -12522,8 +13756,14 @@
       <c r="M205" s="10">
         <v>-20</v>
       </c>
-    </row>
-    <row r="206" spans="2:13" ht="19.8">
+      <c r="O205" s="10">
+        <v>224</v>
+      </c>
+      <c r="P205" s="10">
+        <v>137.69999999999999</v>
+      </c>
+    </row>
+    <row r="206" spans="2:16" ht="19.8">
       <c r="B206" s="12" t="s">
         <v>271</v>
       </c>
@@ -12560,8 +13800,14 @@
       <c r="M206" s="11">
         <v>7000</v>
       </c>
-    </row>
-    <row r="207" spans="2:13" ht="19.8">
+      <c r="O206" s="10">
+        <v>225</v>
+      </c>
+      <c r="P206" s="10">
+        <v>947</v>
+      </c>
+    </row>
+    <row r="207" spans="2:16" ht="19.8">
       <c r="B207" s="12" t="s">
         <v>271</v>
       </c>
@@ -12598,8 +13844,14 @@
       <c r="M207" s="11">
         <v>3939</v>
       </c>
-    </row>
-    <row r="208" spans="2:13" ht="19.8">
+      <c r="O207" s="10">
+        <v>226</v>
+      </c>
+      <c r="P207" s="10">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="208" spans="2:16" ht="19.8">
       <c r="B208" s="12" t="s">
         <v>271</v>
       </c>
@@ -12636,8 +13888,14 @@
       <c r="M208" s="11">
         <v>1200</v>
       </c>
-    </row>
-    <row r="209" spans="2:13" ht="19.8">
+      <c r="O208" s="10">
+        <v>227</v>
+      </c>
+      <c r="P208" s="10">
+        <v>637.5</v>
+      </c>
+    </row>
+    <row r="209" spans="2:16" ht="19.8">
       <c r="B209" s="12" t="s">
         <v>271</v>
       </c>
@@ -12670,8 +13928,14 @@
       <c r="M209" s="10">
         <v>-25.1</v>
       </c>
-    </row>
-    <row r="210" spans="2:13" ht="19.8">
+      <c r="O209" s="10">
+        <v>228</v>
+      </c>
+      <c r="P209" s="10">
+        <v>713.6</v>
+      </c>
+    </row>
+    <row r="210" spans="2:16" ht="19.8">
       <c r="B210" s="12" t="s">
         <v>271</v>
       </c>
@@ -12708,8 +13972,14 @@
       <c r="M210" s="11">
         <v>15660</v>
       </c>
-    </row>
-    <row r="211" spans="2:13" ht="19.8">
+      <c r="O210" s="10">
+        <v>229</v>
+      </c>
+      <c r="P210" s="10">
+        <v>833.6</v>
+      </c>
+    </row>
+    <row r="211" spans="2:16" ht="19.8">
       <c r="B211" s="12" t="s">
         <v>271</v>
       </c>
@@ -12742,8 +14012,14 @@
       <c r="M211" s="10">
         <v>-94</v>
       </c>
-    </row>
-    <row r="212" spans="2:13" ht="19.8">
+      <c r="O211" s="10">
+        <v>230</v>
+      </c>
+      <c r="P211" s="10">
+        <v>65.099999999999994</v>
+      </c>
+    </row>
+    <row r="212" spans="2:16" ht="19.8">
       <c r="B212" s="12" t="s">
         <v>271</v>
       </c>
@@ -12780,8 +14056,14 @@
       <c r="M212" s="11">
         <v>4140</v>
       </c>
-    </row>
-    <row r="213" spans="2:13" ht="19.8">
+      <c r="O212" s="10">
+        <v>231</v>
+      </c>
+      <c r="P212" s="10">
+        <v>64.400000000000006</v>
+      </c>
+    </row>
+    <row r="213" spans="2:16" ht="19.8">
       <c r="B213" s="12" t="s">
         <v>271</v>
       </c>
@@ -12814,8 +14096,14 @@
       <c r="M213" s="10">
         <v>-26</v>
       </c>
-    </row>
-    <row r="214" spans="2:13" ht="19.8">
+      <c r="O213" s="10">
+        <v>232</v>
+      </c>
+      <c r="P213" s="10">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="214" spans="2:16" ht="19.8">
       <c r="B214" s="12" t="s">
         <v>271</v>
       </c>
@@ -12852,8 +14140,14 @@
       <c r="M214" s="10">
         <v>600</v>
       </c>
-    </row>
-    <row r="215" spans="2:13" ht="19.8">
+      <c r="O214" s="10">
+        <v>235</v>
+      </c>
+      <c r="P214" s="10">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="215" spans="2:16" ht="19.8">
       <c r="B215" s="12" t="s">
         <v>271</v>
       </c>
@@ -12890,8 +14184,14 @@
       <c r="M215" s="10">
         <v>60</v>
       </c>
-    </row>
-    <row r="216" spans="2:13">
+      <c r="O215" s="10">
+        <v>236</v>
+      </c>
+      <c r="P215" s="10">
+        <v>867</v>
+      </c>
+    </row>
+    <row r="216" spans="2:16">
       <c r="B216" s="12" t="s">
         <v>271</v>
       </c>
@@ -12924,8 +14224,14 @@
       <c r="M216" s="10">
         <v>-94</v>
       </c>
-    </row>
-    <row r="217" spans="2:13" ht="19.8">
+      <c r="O216" s="10">
+        <v>238</v>
+      </c>
+      <c r="P216" s="11">
+        <v>1674</v>
+      </c>
+    </row>
+    <row r="217" spans="2:16" ht="19.8">
       <c r="B217" s="12" t="s">
         <v>271</v>
       </c>
@@ -12962,8 +14268,14 @@
       <c r="M217" s="10">
         <v>455</v>
       </c>
-    </row>
-    <row r="218" spans="2:13" ht="19.8">
+      <c r="O217" s="10">
+        <v>239</v>
+      </c>
+      <c r="P217" s="11">
+        <v>5805</v>
+      </c>
+    </row>
+    <row r="218" spans="2:16" ht="19.8">
       <c r="B218" s="12" t="s">
         <v>271</v>
       </c>
@@ -13000,8 +14312,14 @@
       <c r="M218" s="10">
         <v>450</v>
       </c>
-    </row>
-    <row r="219" spans="2:13">
+      <c r="O218" s="10">
+        <v>244</v>
+      </c>
+      <c r="P218" s="10">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="219" spans="2:16">
       <c r="B219" s="12" t="s">
         <v>271</v>
       </c>
@@ -13034,8 +14352,14 @@
       <c r="M219" s="10">
         <v>-14.5</v>
       </c>
-    </row>
-    <row r="220" spans="2:13" ht="19.8">
+      <c r="O219" s="10">
+        <v>245</v>
+      </c>
+      <c r="P219" s="10">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="220" spans="2:16" ht="19.8">
       <c r="B220" s="12" t="s">
         <v>271</v>
       </c>
@@ -13072,8 +14396,14 @@
       <c r="M220" s="11">
         <v>14385</v>
       </c>
-    </row>
-    <row r="221" spans="2:13">
+      <c r="O220" s="10">
+        <v>246</v>
+      </c>
+      <c r="P220" s="10">
+        <v>481.6</v>
+      </c>
+    </row>
+    <row r="221" spans="2:16">
       <c r="B221" s="12" t="s">
         <v>271</v>
       </c>
@@ -13106,8 +14436,14 @@
       <c r="M221" s="10">
         <v>-46.5</v>
       </c>
-    </row>
-    <row r="222" spans="2:13" ht="19.8">
+      <c r="O221" s="10">
+        <v>252</v>
+      </c>
+      <c r="P221" s="11">
+        <v>2148.3000000000002</v>
+      </c>
+    </row>
+    <row r="222" spans="2:16" ht="19.8">
       <c r="B222" s="12" t="s">
         <v>271</v>
       </c>
@@ -13144,8 +14480,14 @@
       <c r="M222" s="11">
         <v>3822</v>
       </c>
-    </row>
-    <row r="223" spans="2:13" ht="19.8">
+      <c r="O222" s="10">
+        <v>259</v>
+      </c>
+      <c r="P222" s="11">
+        <v>1458</v>
+      </c>
+    </row>
+    <row r="223" spans="2:16" ht="19.8">
       <c r="B223" s="12" t="s">
         <v>271</v>
       </c>
@@ -13182,8 +14524,14 @@
       <c r="M223" s="10">
         <v>390</v>
       </c>
-    </row>
-    <row r="224" spans="2:13">
+      <c r="O223" s="10">
+        <v>261</v>
+      </c>
+      <c r="P223" s="11">
+        <v>1692</v>
+      </c>
+    </row>
+    <row r="224" spans="2:16">
       <c r="B224" s="12" t="s">
         <v>271</v>
       </c>
@@ -13216,8 +14564,14 @@
       <c r="M224" s="10">
         <v>-290.8</v>
       </c>
-    </row>
-    <row r="225" spans="2:13" ht="19.8">
+      <c r="O224" s="10">
+        <v>262</v>
+      </c>
+      <c r="P224" s="11">
+        <v>2790</v>
+      </c>
+    </row>
+    <row r="225" spans="2:16" ht="19.8">
       <c r="B225" s="12" t="s">
         <v>271</v>
       </c>
@@ -13254,8 +14608,14 @@
       <c r="M225" s="11">
         <v>12070</v>
       </c>
-    </row>
-    <row r="226" spans="2:13" ht="19.8">
+      <c r="O225" s="10">
+        <v>240</v>
+      </c>
+      <c r="P225" s="10">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="226" spans="2:16" ht="19.8">
       <c r="B226" s="12" t="s">
         <v>271</v>
       </c>
@@ -13288,8 +14648,14 @@
       <c r="M226" s="10">
         <v>-163</v>
       </c>
-    </row>
-    <row r="227" spans="2:13" ht="19.8">
+      <c r="O226" s="10">
+        <v>241</v>
+      </c>
+      <c r="P226" s="10">
+        <v>703.6</v>
+      </c>
+    </row>
+    <row r="227" spans="2:16" ht="19.8">
       <c r="B227" s="12" t="s">
         <v>298</v>
       </c>
@@ -13326,8 +14692,14 @@
       <c r="M227" s="11">
         <v>7578</v>
       </c>
-    </row>
-    <row r="228" spans="2:13">
+      <c r="O227" s="10">
+        <v>248</v>
+      </c>
+      <c r="P227" s="10">
+        <v>801.9</v>
+      </c>
+    </row>
+    <row r="228" spans="2:16">
       <c r="B228" s="12" t="s">
         <v>298</v>
       </c>
@@ -13360,8 +14732,14 @@
       <c r="M228" s="10">
         <v>-20.2</v>
       </c>
-    </row>
-    <row r="229" spans="2:13" ht="19.8">
+      <c r="O228" s="10">
+        <v>249</v>
+      </c>
+      <c r="P228" s="10">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="229" spans="2:16" ht="19.8">
       <c r="B229" s="12" t="s">
         <v>298</v>
       </c>
@@ -13398,8 +14776,14 @@
       <c r="M229" s="11">
         <v>16020</v>
       </c>
-    </row>
-    <row r="230" spans="2:13">
+      <c r="O229" s="10">
+        <v>260</v>
+      </c>
+      <c r="P229" s="11">
+        <v>1692</v>
+      </c>
+    </row>
+    <row r="230" spans="2:16">
       <c r="B230" s="12" t="s">
         <v>298</v>
       </c>
@@ -13432,8 +14816,14 @@
       <c r="M230" s="10">
         <v>-18</v>
       </c>
-    </row>
-    <row r="231" spans="2:13" ht="19.8">
+      <c r="O230" s="10">
+        <v>270</v>
+      </c>
+      <c r="P230" s="10">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="231" spans="2:16" ht="19.8">
       <c r="B231" s="12" t="s">
         <v>298</v>
       </c>
@@ -13470,8 +14860,14 @@
       <c r="M231" s="11">
         <v>14399</v>
       </c>
-    </row>
-    <row r="232" spans="2:13" ht="19.8">
+      <c r="O231" s="10">
+        <v>219</v>
+      </c>
+      <c r="P231" s="10">
+        <v>999.6</v>
+      </c>
+    </row>
+    <row r="232" spans="2:16" ht="19.8">
       <c r="B232" s="12" t="s">
         <v>298</v>
       </c>
@@ -13504,8 +14900,14 @@
       <c r="M232" s="10">
         <v>-59.1</v>
       </c>
-    </row>
-    <row r="233" spans="2:13" ht="19.8">
+      <c r="O232" s="10">
+        <v>237</v>
+      </c>
+      <c r="P232" s="11">
+        <v>2335</v>
+      </c>
+    </row>
+    <row r="233" spans="2:16" ht="19.8">
       <c r="B233" s="12" t="s">
         <v>298</v>
       </c>
@@ -13542,8 +14944,14 @@
       <c r="M233" s="11">
         <v>36000</v>
       </c>
-    </row>
-    <row r="234" spans="2:13" ht="19.8">
+      <c r="O233" s="10">
+        <v>251</v>
+      </c>
+      <c r="P233" s="10">
+        <v>499.2</v>
+      </c>
+    </row>
+    <row r="234" spans="2:16" ht="19.8">
       <c r="B234" s="12" t="s">
         <v>298</v>
       </c>
@@ -13580,8 +14988,14 @@
       <c r="M234" s="11">
         <v>40230</v>
       </c>
-    </row>
-    <row r="235" spans="2:13">
+      <c r="O234" s="10">
+        <v>253</v>
+      </c>
+      <c r="P234" s="11">
+        <v>1991.6</v>
+      </c>
+    </row>
+    <row r="235" spans="2:16">
       <c r="B235" s="12" t="s">
         <v>298</v>
       </c>
@@ -13614,8 +15028,14 @@
       <c r="M235" s="10">
         <v>-7</v>
       </c>
-    </row>
-    <row r="236" spans="2:13" ht="19.8">
+      <c r="O235" s="10">
+        <v>254</v>
+      </c>
+      <c r="P235" s="11">
+        <v>2102.1</v>
+      </c>
+    </row>
+    <row r="236" spans="2:16" ht="19.8">
       <c r="B236" s="12" t="s">
         <v>298</v>
       </c>
@@ -13652,8 +15072,14 @@
       <c r="M236" s="11">
         <v>6210</v>
       </c>
-    </row>
-    <row r="237" spans="2:13">
+      <c r="O236" s="10">
+        <v>255</v>
+      </c>
+      <c r="P236" s="10">
+        <v>816.3</v>
+      </c>
+    </row>
+    <row r="237" spans="2:16">
       <c r="B237" s="12" t="s">
         <v>298</v>
       </c>
@@ -13686,8 +15112,14 @@
       <c r="M237" s="10">
         <v>-89</v>
       </c>
-    </row>
-    <row r="238" spans="2:13" ht="19.8">
+      <c r="O237" s="10">
+        <v>256</v>
+      </c>
+      <c r="P237" s="10">
+        <v>612.9</v>
+      </c>
+    </row>
+    <row r="238" spans="2:16" ht="19.8">
       <c r="B238" s="12" t="s">
         <v>298</v>
       </c>
@@ -13724,8 +15156,14 @@
       <c r="M238" s="11">
         <v>5130</v>
       </c>
-    </row>
-    <row r="239" spans="2:13">
+      <c r="O238" s="10">
+        <v>257</v>
+      </c>
+      <c r="P238" s="10">
+        <v>701.5</v>
+      </c>
+    </row>
+    <row r="239" spans="2:16">
       <c r="B239" s="12" t="s">
         <v>298</v>
       </c>
@@ -13758,8 +15196,14 @@
       <c r="M239" s="10">
         <v>-17</v>
       </c>
-    </row>
-    <row r="240" spans="2:13" ht="19.8">
+      <c r="O239" s="10">
+        <v>258</v>
+      </c>
+      <c r="P239" s="10">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="240" spans="2:16" ht="19.8">
       <c r="B240" s="12" t="s">
         <v>298</v>
       </c>
@@ -13796,8 +15240,14 @@
       <c r="M240" s="11">
         <v>42120</v>
       </c>
-    </row>
-    <row r="241" spans="2:13">
+      <c r="O240" s="10">
+        <v>267</v>
+      </c>
+      <c r="P240" s="10">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="241" spans="2:16">
       <c r="B241" s="12" t="s">
         <v>298</v>
       </c>
@@ -13830,8 +15280,14 @@
       <c r="M241" s="10">
         <v>-108</v>
       </c>
-    </row>
-    <row r="242" spans="2:13" ht="19.8">
+      <c r="O241" s="10">
+        <v>268</v>
+      </c>
+      <c r="P241" s="10">
+        <v>397.8</v>
+      </c>
+    </row>
+    <row r="242" spans="2:16" ht="19.8">
       <c r="B242" s="12" t="s">
         <v>298</v>
       </c>
@@ -13868,8 +15324,14 @@
       <c r="M242" s="11">
         <v>6800</v>
       </c>
-    </row>
-    <row r="243" spans="2:13" ht="19.8">
+      <c r="O242" s="10">
+        <v>269</v>
+      </c>
+      <c r="P242" s="10">
+        <v>664.3</v>
+      </c>
+    </row>
+    <row r="243" spans="2:16" ht="19.8">
       <c r="B243" s="12" t="s">
         <v>298</v>
       </c>
@@ -13902,8 +15364,14 @@
       <c r="M243" s="10">
         <v>-20</v>
       </c>
-    </row>
-    <row r="244" spans="2:13" ht="19.8">
+      <c r="O243" s="10">
+        <v>263</v>
+      </c>
+      <c r="P243" s="11">
+        <v>3816</v>
+      </c>
+    </row>
+    <row r="244" spans="2:16" ht="19.8">
       <c r="B244" s="5">
         <v>44932</v>
       </c>
@@ -13940,8 +15408,14 @@
       <c r="M244" s="11">
         <v>16354</v>
       </c>
-    </row>
-    <row r="245" spans="2:13">
+      <c r="O244" s="10">
+        <v>264</v>
+      </c>
+      <c r="P244" s="11">
+        <v>1074</v>
+      </c>
+    </row>
+    <row r="245" spans="2:16">
       <c r="B245" s="5">
         <v>44932</v>
       </c>
@@ -13974,8 +15448,14 @@
       <c r="M245" s="10">
         <v>-18.600000000000001</v>
       </c>
-    </row>
-    <row r="246" spans="2:13" ht="19.8">
+      <c r="O245" s="10">
+        <v>265</v>
+      </c>
+      <c r="P245" s="11">
+        <v>1385</v>
+      </c>
+    </row>
+    <row r="246" spans="2:16" ht="19.8">
       <c r="B246" s="5">
         <v>45205</v>
       </c>
@@ -14012,8 +15492,14 @@
       <c r="M246" s="11">
         <v>1200</v>
       </c>
-    </row>
-    <row r="247" spans="2:13" ht="19.8">
+      <c r="O246" s="10">
+        <v>266</v>
+      </c>
+      <c r="P246" s="10">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="247" spans="2:16" ht="19.8">
       <c r="B247" s="12" t="s">
         <v>319</v>
       </c>
@@ -14050,8 +15536,14 @@
       <c r="M247" s="11">
         <v>1500</v>
       </c>
-    </row>
-    <row r="248" spans="2:13" ht="19.8">
+      <c r="O247" s="10">
+        <v>273</v>
+      </c>
+      <c r="P247" s="11">
+        <v>1248</v>
+      </c>
+    </row>
+    <row r="248" spans="2:16" ht="19.8">
       <c r="B248" s="12" t="s">
         <v>322</v>
       </c>
@@ -14088,8 +15580,14 @@
       <c r="M248" s="11">
         <v>1200</v>
       </c>
-    </row>
-    <row r="249" spans="2:13" ht="19.8">
+      <c r="O248" s="10">
+        <v>271</v>
+      </c>
+      <c r="P248" s="10">
+        <v>810</v>
+      </c>
+    </row>
+    <row r="249" spans="2:16" ht="19.8">
       <c r="B249" s="12" t="s">
         <v>324</v>
       </c>
@@ -14126,8 +15624,14 @@
       <c r="M249" s="11">
         <v>26730</v>
       </c>
-    </row>
-    <row r="250" spans="2:13">
+      <c r="O249" s="10">
+        <v>272</v>
+      </c>
+      <c r="P249" s="10">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="250" spans="2:16">
       <c r="B250" s="12" t="s">
         <v>324</v>
       </c>
@@ -14160,8 +15664,14 @@
       <c r="M250" s="10">
         <v>-57</v>
       </c>
-    </row>
-    <row r="251" spans="2:13" ht="19.8">
+      <c r="O250" s="10">
+        <v>274</v>
+      </c>
+      <c r="P250" s="10">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="251" spans="2:16" ht="19.8">
       <c r="B251" s="12" t="s">
         <v>324</v>
       </c>
@@ -14198,8 +15708,14 @@
       <c r="M251" s="11">
         <v>12765</v>
       </c>
-    </row>
-    <row r="252" spans="2:13">
+      <c r="O251" s="10">
+        <v>275</v>
+      </c>
+      <c r="P251" s="10">
+        <v>243.3</v>
+      </c>
+    </row>
+    <row r="252" spans="2:16">
       <c r="B252" s="12" t="s">
         <v>324</v>
       </c>
@@ -14232,8 +15748,14 @@
       <c r="M252" s="10">
         <v>-88.5</v>
       </c>
-    </row>
-    <row r="253" spans="2:13" ht="19.8">
+      <c r="O252" s="10">
+        <v>276</v>
+      </c>
+      <c r="P252" s="10">
+        <v>309.39999999999998</v>
+      </c>
+    </row>
+    <row r="253" spans="2:16" ht="19.8">
       <c r="B253" s="12" t="s">
         <v>324</v>
       </c>
@@ -14270,8 +15792,14 @@
       <c r="M253" s="11">
         <v>4290</v>
       </c>
-    </row>
-    <row r="254" spans="2:13" ht="19.8">
+      <c r="O253" s="10">
+        <v>277</v>
+      </c>
+      <c r="P253" s="10">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="254" spans="2:16" ht="19.8">
       <c r="B254" s="12" t="s">
         <v>324</v>
       </c>
@@ -14308,8 +15836,14 @@
       <c r="M254" s="10">
         <v>720</v>
       </c>
-    </row>
-    <row r="255" spans="2:13">
+      <c r="O254" s="10">
+        <v>278</v>
+      </c>
+      <c r="P254" s="10">
+        <v>162.30000000000001</v>
+      </c>
+    </row>
+    <row r="255" spans="2:16">
       <c r="B255" s="12" t="s">
         <v>324</v>
       </c>
@@ -14342,8 +15876,14 @@
       <c r="M255" s="10">
         <v>-9</v>
       </c>
-    </row>
-    <row r="256" spans="2:13" ht="19.8">
+      <c r="O255" s="10">
+        <v>279</v>
+      </c>
+      <c r="P255" s="11">
+        <v>1445</v>
+      </c>
+    </row>
+    <row r="256" spans="2:16" ht="19.8">
       <c r="B256" s="12" t="s">
         <v>324</v>
       </c>
@@ -14380,8 +15920,14 @@
       <c r="M256" s="11">
         <v>4056</v>
       </c>
-    </row>
-    <row r="257" spans="2:13" ht="19.8">
+      <c r="O256" s="10">
+        <v>289</v>
+      </c>
+      <c r="P256" s="11">
+        <v>1314</v>
+      </c>
+    </row>
+    <row r="257" spans="2:16" ht="19.8">
       <c r="B257" s="12" t="s">
         <v>324</v>
       </c>
@@ -14414,8 +15960,14 @@
       <c r="M257" s="10">
         <v>-50</v>
       </c>
-    </row>
-    <row r="258" spans="2:13" ht="19.8">
+      <c r="O257" s="10">
+        <v>290</v>
+      </c>
+      <c r="P257" s="10">
+        <v>954</v>
+      </c>
+    </row>
+    <row r="258" spans="2:16" ht="19.8">
       <c r="B258" s="12" t="s">
         <v>324</v>
       </c>
@@ -14452,8 +16004,14 @@
       <c r="M258" s="11">
         <v>6120</v>
       </c>
-    </row>
-    <row r="259" spans="2:13" ht="19.8">
+      <c r="O258" s="10">
+        <v>288</v>
+      </c>
+      <c r="P258" s="10">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="259" spans="2:16" ht="19.8">
       <c r="B259" s="12" t="s">
         <v>324</v>
       </c>
@@ -14486,8 +16044,14 @@
       <c r="M259" s="10">
         <v>-8</v>
       </c>
-    </row>
-    <row r="260" spans="2:13" ht="19.8">
+      <c r="O259" s="10">
+        <v>280</v>
+      </c>
+      <c r="P259" s="10">
+        <v>961.4</v>
+      </c>
+    </row>
+    <row r="260" spans="2:16" ht="19.8">
       <c r="B260" s="12" t="s">
         <v>324</v>
       </c>
@@ -14524,8 +16088,14 @@
       <c r="M260" s="11">
         <v>1300</v>
       </c>
-    </row>
-    <row r="261" spans="2:13" ht="19.8">
+      <c r="O260" s="10">
+        <v>281</v>
+      </c>
+      <c r="P260" s="11">
+        <v>1164.8</v>
+      </c>
+    </row>
+    <row r="261" spans="2:16" ht="19.8">
       <c r="B261" s="12" t="s">
         <v>324</v>
       </c>
@@ -14562,8 +16132,14 @@
       <c r="M261" s="10">
         <v>75</v>
       </c>
-    </row>
-    <row r="262" spans="2:13" ht="19.8">
+      <c r="O261" s="10">
+        <v>282</v>
+      </c>
+      <c r="P261" s="10">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="262" spans="2:16" ht="19.8">
       <c r="B262" s="12" t="s">
         <v>324</v>
       </c>
@@ -14596,8 +16172,14 @@
       <c r="M262" s="10">
         <v>-37</v>
       </c>
-    </row>
-    <row r="263" spans="2:13" ht="19.8">
+      <c r="O262" s="10">
+        <v>283</v>
+      </c>
+      <c r="P262" s="10">
+        <v>709.8</v>
+      </c>
+    </row>
+    <row r="263" spans="2:16" ht="19.8">
       <c r="B263" s="12" t="s">
         <v>324</v>
       </c>
@@ -14634,8 +16216,14 @@
       <c r="M263" s="11">
         <v>8400</v>
       </c>
-    </row>
-    <row r="264" spans="2:13">
+      <c r="O263" s="10">
+        <v>284</v>
+      </c>
+      <c r="P263" s="11">
+        <v>1389.7</v>
+      </c>
+    </row>
+    <row r="264" spans="2:16">
       <c r="B264" s="12" t="s">
         <v>324</v>
       </c>
@@ -14668,8 +16256,14 @@
       <c r="M264" s="10">
         <v>-60</v>
       </c>
-    </row>
-    <row r="265" spans="2:13" ht="19.8">
+      <c r="O264" s="10">
+        <v>285</v>
+      </c>
+      <c r="P264" s="10">
+        <v>252.8</v>
+      </c>
+    </row>
+    <row r="265" spans="2:16" ht="19.8">
       <c r="B265" s="12" t="s">
         <v>324</v>
       </c>
@@ -14706,8 +16300,14 @@
       <c r="M265" s="11">
         <v>1080</v>
       </c>
-    </row>
-    <row r="266" spans="2:13" ht="19.8">
+      <c r="O265" s="10">
+        <v>286</v>
+      </c>
+      <c r="P265" s="10">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="266" spans="2:16" ht="19.8">
       <c r="B266" s="12" t="s">
         <v>324</v>
       </c>
@@ -14740,8 +16340,14 @@
       <c r="M266" s="10">
         <v>-2</v>
       </c>
-    </row>
-    <row r="267" spans="2:13" ht="19.8">
+      <c r="O266" s="10">
+        <v>287</v>
+      </c>
+      <c r="P266" s="10">
+        <v>205.2</v>
+      </c>
+    </row>
+    <row r="267" spans="2:16" ht="19.8">
       <c r="B267" s="12" t="s">
         <v>324</v>
       </c>
@@ -14778,8 +16384,14 @@
       <c r="M267" s="11">
         <v>24480</v>
       </c>
-    </row>
-    <row r="268" spans="2:13" ht="19.8">
+      <c r="O267" s="10">
+        <v>291</v>
+      </c>
+      <c r="P267" s="10">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="268" spans="2:16" ht="19.8">
       <c r="B268" s="12" t="s">
         <v>324</v>
       </c>
@@ -14812,8 +16424,14 @@
       <c r="M268" s="10">
         <v>-32</v>
       </c>
-    </row>
-    <row r="269" spans="2:13" ht="19.8">
+      <c r="O268" s="10">
+        <v>292</v>
+      </c>
+      <c r="P268" s="11">
+        <v>1476</v>
+      </c>
+    </row>
+    <row r="269" spans="2:16" ht="19.8">
       <c r="B269" s="12" t="s">
         <v>324</v>
       </c>
@@ -14850,8 +16468,14 @@
       <c r="M269" s="11">
         <v>30770</v>
       </c>
-    </row>
-    <row r="270" spans="2:13" ht="19.8">
+      <c r="O269" s="10">
+        <v>293</v>
+      </c>
+      <c r="P269" s="10">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="270" spans="2:16" ht="19.8">
       <c r="B270" s="12" t="s">
         <v>324</v>
       </c>
@@ -14884,8 +16508,14 @@
       <c r="M270" s="10">
         <v>-293</v>
       </c>
-    </row>
-    <row r="271" spans="2:13" ht="19.8">
+      <c r="O270" s="10">
+        <v>294</v>
+      </c>
+      <c r="P270" s="10">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="271" spans="2:16" ht="19.8">
       <c r="B271" s="12" t="s">
         <v>324</v>
       </c>
@@ -14922,8 +16552,14 @@
       <c r="M271" s="11">
         <v>18190</v>
       </c>
-    </row>
-    <row r="272" spans="2:13" ht="19.8">
+      <c r="O271" s="10">
+        <v>298</v>
+      </c>
+      <c r="P271" s="11">
+        <v>1245</v>
+      </c>
+    </row>
+    <row r="272" spans="2:16" ht="19.8">
       <c r="B272" s="12" t="s">
         <v>324</v>
       </c>
@@ -14956,8 +16592,14 @@
       <c r="M272" s="10">
         <v>-71</v>
       </c>
-    </row>
-    <row r="273" spans="2:13" ht="19.8">
+      <c r="O272" s="10">
+        <v>301</v>
+      </c>
+      <c r="P272" s="10">
+        <v>905.1</v>
+      </c>
+    </row>
+    <row r="273" spans="2:16" ht="19.8">
       <c r="B273" s="12" t="s">
         <v>324</v>
       </c>
@@ -14994,8 +16636,14 @@
       <c r="M273" s="11">
         <v>6630</v>
       </c>
-    </row>
-    <row r="274" spans="2:13" ht="19.8">
+      <c r="O273" s="10">
+        <v>302</v>
+      </c>
+      <c r="P273" s="10">
+        <v>275.39999999999998</v>
+      </c>
+    </row>
+    <row r="274" spans="2:16" ht="19.8">
       <c r="B274" s="12" t="s">
         <v>324</v>
       </c>
@@ -15028,8 +16676,14 @@
       <c r="M274" s="10">
         <v>-67</v>
       </c>
-    </row>
-    <row r="275" spans="2:13" ht="19.8">
+      <c r="O274" s="10">
+        <v>303</v>
+      </c>
+      <c r="P274" s="11">
+        <v>1791.3</v>
+      </c>
+    </row>
+    <row r="275" spans="2:16" ht="19.8">
       <c r="B275" s="12" t="s">
         <v>324</v>
       </c>
@@ -15066,8 +16720,14 @@
       <c r="M275" s="11">
         <v>33600</v>
       </c>
-    </row>
-    <row r="276" spans="2:13">
+      <c r="O275" s="10">
+        <v>299</v>
+      </c>
+      <c r="P275" s="11">
+        <v>1836</v>
+      </c>
+    </row>
+    <row r="276" spans="2:16">
       <c r="B276" s="12" t="s">
         <v>324</v>
       </c>
@@ -15100,8 +16760,14 @@
       <c r="M276" s="10">
         <v>-240</v>
       </c>
-    </row>
-    <row r="277" spans="2:13" ht="19.8">
+      <c r="O276" s="10">
+        <v>300</v>
+      </c>
+      <c r="P276" s="10">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="277" spans="2:16" ht="19.8">
       <c r="B277" s="12" t="s">
         <v>355</v>
       </c>
@@ -15138,8 +16804,14 @@
       <c r="M277" s="11">
         <v>4140</v>
       </c>
-    </row>
-    <row r="278" spans="2:13">
+      <c r="O277" s="10">
+        <v>297</v>
+      </c>
+      <c r="P277" s="11">
+        <v>1299.5999999999999</v>
+      </c>
+    </row>
+    <row r="278" spans="2:16">
       <c r="B278" s="12" t="s">
         <v>355</v>
       </c>
@@ -15172,8 +16844,14 @@
       <c r="M278" s="10">
         <v>-26</v>
       </c>
-    </row>
-    <row r="279" spans="2:13" ht="19.8">
+      <c r="O278" s="10">
+        <v>295</v>
+      </c>
+      <c r="P278" s="11">
+        <v>1368</v>
+      </c>
+    </row>
+    <row r="279" spans="2:16" ht="19.8">
       <c r="B279" s="12" t="s">
         <v>355</v>
       </c>
@@ -15210,8 +16888,14 @@
       <c r="M279" s="11">
         <v>5745</v>
       </c>
-    </row>
-    <row r="280" spans="2:13" ht="19.8">
+      <c r="O279" s="10">
+        <v>296</v>
+      </c>
+      <c r="P279" s="10">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="280" spans="2:16" ht="19.8">
       <c r="B280" s="12" t="s">
         <v>355</v>
       </c>
@@ -15244,8 +16928,14 @@
       <c r="M280" s="10">
         <v>-70.5</v>
       </c>
-    </row>
-    <row r="281" spans="2:13" ht="19.8">
+      <c r="O280" s="10">
+        <v>309</v>
+      </c>
+      <c r="P280" s="11">
+        <v>1764</v>
+      </c>
+    </row>
+    <row r="281" spans="2:16" ht="19.8">
       <c r="B281" s="12" t="s">
         <v>355</v>
       </c>
@@ -15282,8 +16972,14 @@
       <c r="M281" s="11">
         <v>6664</v>
       </c>
-    </row>
-    <row r="282" spans="2:13" ht="19.8">
+      <c r="O281" s="10">
+        <v>415</v>
+      </c>
+      <c r="P281" s="10">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="282" spans="2:16" ht="19.8">
       <c r="B282" s="12" t="s">
         <v>355</v>
       </c>
@@ -15316,8 +17012,14 @@
       <c r="M282" s="10">
         <v>-37.6</v>
       </c>
-    </row>
-    <row r="283" spans="2:13" ht="19.8">
+      <c r="O282" s="10">
+        <v>308</v>
+      </c>
+      <c r="P282" s="11">
+        <v>2310</v>
+      </c>
+    </row>
+    <row r="283" spans="2:16" ht="19.8">
       <c r="B283" s="12" t="s">
         <v>355</v>
       </c>
@@ -15354,8 +17056,14 @@
       <c r="M283" s="10">
         <v>876</v>
       </c>
-    </row>
-    <row r="284" spans="2:13">
+      <c r="O283" s="10">
+        <v>310</v>
+      </c>
+      <c r="P283" s="10">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="284" spans="2:16">
       <c r="B284" s="12" t="s">
         <v>355</v>
       </c>
@@ -15388,8 +17096,14 @@
       <c r="M284" s="10">
         <v>-8.4</v>
       </c>
-    </row>
-    <row r="285" spans="2:13" ht="19.8">
+      <c r="O284" s="10">
+        <v>311</v>
+      </c>
+      <c r="P284" s="10">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="285" spans="2:16" ht="19.8">
       <c r="B285" s="12" t="s">
         <v>355</v>
       </c>
@@ -15426,8 +17140,14 @@
       <c r="M285" s="11">
         <v>2448</v>
       </c>
-    </row>
-    <row r="286" spans="2:13">
+      <c r="O285" s="10">
+        <v>312</v>
+      </c>
+      <c r="P285" s="10">
+        <v>769.5</v>
+      </c>
+    </row>
+    <row r="286" spans="2:16">
       <c r="B286" s="12" t="s">
         <v>355</v>
       </c>
@@ -15460,8 +17180,14 @@
       <c r="M286" s="10">
         <v>-3.2</v>
       </c>
-    </row>
-    <row r="287" spans="2:13" ht="19.8">
+      <c r="O286" s="10">
+        <v>313</v>
+      </c>
+      <c r="P286" s="10">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="287" spans="2:16" ht="19.8">
       <c r="B287" s="12" t="s">
         <v>355</v>
       </c>
@@ -15498,8 +17224,14 @@
       <c r="M287" s="11">
         <v>29240</v>
       </c>
-    </row>
-    <row r="288" spans="2:13" ht="19.8">
+      <c r="O287" s="10">
+        <v>314</v>
+      </c>
+      <c r="P287" s="10">
+        <v>574.5</v>
+      </c>
+    </row>
+    <row r="288" spans="2:16" ht="19.8">
       <c r="B288" s="12" t="s">
         <v>355</v>
       </c>
@@ -15532,8 +17264,14 @@
       <c r="M288" s="10">
         <v>-116</v>
       </c>
-    </row>
-    <row r="289" spans="2:13" ht="19.8">
+      <c r="O288" s="10">
+        <v>316</v>
+      </c>
+      <c r="P288" s="10">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="289" spans="2:16" ht="19.8">
       <c r="B289" s="12" t="s">
         <v>355</v>
       </c>
@@ -15570,8 +17308,14 @@
       <c r="M289" s="11">
         <v>95480</v>
       </c>
-    </row>
-    <row r="290" spans="2:13">
+      <c r="O289" s="10">
+        <v>317</v>
+      </c>
+      <c r="P289" s="10">
+        <v>435.6</v>
+      </c>
+    </row>
+    <row r="290" spans="2:16">
       <c r="B290" s="12" t="s">
         <v>355</v>
       </c>
@@ -15604,8 +17348,14 @@
       <c r="M290" s="10">
         <v>-432</v>
       </c>
-    </row>
-    <row r="291" spans="2:13" ht="19.8">
+      <c r="O290" s="10">
+        <v>318</v>
+      </c>
+      <c r="P290" s="10">
+        <v>116.8</v>
+      </c>
+    </row>
+    <row r="291" spans="2:16" ht="19.8">
       <c r="B291" s="12" t="s">
         <v>355</v>
       </c>
@@ -15642,8 +17392,14 @@
       <c r="M291" s="11">
         <v>19710</v>
       </c>
-    </row>
-    <row r="292" spans="2:13">
+      <c r="O291" s="10">
+        <v>321</v>
+      </c>
+      <c r="P291" s="11">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="292" spans="2:16">
       <c r="B292" s="12" t="s">
         <v>355</v>
       </c>
@@ -15676,8 +17432,14 @@
       <c r="M292" s="10">
         <v>-39</v>
       </c>
-    </row>
-    <row r="293" spans="2:13" ht="19.8">
+      <c r="O292" s="10">
+        <v>324</v>
+      </c>
+      <c r="P292" s="10">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="293" spans="2:16" ht="19.8">
       <c r="B293" s="12" t="s">
         <v>355</v>
       </c>
@@ -15714,8 +17476,14 @@
       <c r="M293" s="11">
         <v>58860</v>
       </c>
-    </row>
-    <row r="294" spans="2:13">
+      <c r="O293" s="10">
+        <v>320</v>
+      </c>
+      <c r="P293" s="11">
+        <v>1620</v>
+      </c>
+    </row>
+    <row r="294" spans="2:16">
       <c r="B294" s="12" t="s">
         <v>355</v>
       </c>
@@ -15748,8 +17516,14 @@
       <c r="M294" s="10">
         <v>-74</v>
       </c>
-    </row>
-    <row r="295" spans="2:13" ht="19.8">
+      <c r="O294" s="10">
+        <v>327</v>
+      </c>
+      <c r="P294" s="11">
+        <v>3150</v>
+      </c>
+    </row>
+    <row r="295" spans="2:16" ht="19.8">
       <c r="B295" s="12" t="s">
         <v>355</v>
       </c>
@@ -15786,8 +17560,14 @@
       <c r="M295" s="11">
         <v>8640</v>
       </c>
-    </row>
-    <row r="296" spans="2:13">
+      <c r="O295" s="10">
+        <v>370</v>
+      </c>
+      <c r="P295" s="11">
+        <v>3420</v>
+      </c>
+    </row>
+    <row r="296" spans="2:16">
       <c r="B296" s="12" t="s">
         <v>355</v>
       </c>
@@ -15820,8 +17600,14 @@
       <c r="M296" s="10">
         <v>-76</v>
       </c>
-    </row>
-    <row r="297" spans="2:13" ht="19.8">
+      <c r="O296" s="10">
+        <v>319</v>
+      </c>
+      <c r="P296" s="10">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="297" spans="2:16" ht="19.8">
       <c r="B297" s="12" t="s">
         <v>355</v>
       </c>
@@ -15858,8 +17644,14 @@
       <c r="M297" s="11">
         <v>21330</v>
       </c>
-    </row>
-    <row r="298" spans="2:13">
+      <c r="O297" s="10">
+        <v>322</v>
+      </c>
+      <c r="P297" s="11">
+        <v>2142</v>
+      </c>
+    </row>
+    <row r="298" spans="2:16">
       <c r="B298" s="12" t="s">
         <v>355</v>
       </c>
@@ -15892,8 +17684,14 @@
       <c r="M298" s="10">
         <v>-97</v>
       </c>
-    </row>
-    <row r="299" spans="2:13" ht="19.8">
+      <c r="O298" s="10">
+        <v>323</v>
+      </c>
+      <c r="P298" s="11">
+        <v>4014</v>
+      </c>
+    </row>
+    <row r="299" spans="2:16" ht="19.8">
       <c r="B299" s="12" t="s">
         <v>380</v>
       </c>
@@ -15930,8 +17728,14 @@
       <c r="M299" s="11">
         <v>2960</v>
       </c>
-    </row>
-    <row r="300" spans="2:13">
+      <c r="O299" s="10">
+        <v>326</v>
+      </c>
+      <c r="P299" s="10">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="300" spans="2:16">
       <c r="B300" s="12" t="s">
         <v>380</v>
       </c>
@@ -15964,8 +17768,14 @@
       <c r="M300" s="10">
         <v>-64</v>
       </c>
-    </row>
-    <row r="301" spans="2:13" ht="19.8">
+      <c r="O300" s="10">
+        <v>328</v>
+      </c>
+      <c r="P300" s="11">
+        <v>4720.8</v>
+      </c>
+    </row>
+    <row r="301" spans="2:16" ht="19.8">
       <c r="B301" s="12" t="s">
         <v>380</v>
       </c>
@@ -16002,8 +17812,14 @@
       <c r="M301" s="11">
         <v>8000</v>
       </c>
-    </row>
-    <row r="302" spans="2:13" ht="19.8">
+      <c r="O301" s="10">
+        <v>329</v>
+      </c>
+      <c r="P301" s="11">
+        <v>1895.6</v>
+      </c>
+    </row>
+    <row r="302" spans="2:16" ht="19.8">
       <c r="B302" s="12" t="s">
         <v>380</v>
       </c>
@@ -16040,8 +17856,14 @@
       <c r="M302" s="11">
         <v>1416</v>
       </c>
-    </row>
-    <row r="303" spans="2:13" ht="19.8">
+      <c r="O302" s="10">
+        <v>330</v>
+      </c>
+      <c r="P302" s="10">
+        <v>368.2</v>
+      </c>
+    </row>
+    <row r="303" spans="2:16" ht="19.8">
       <c r="B303" s="12" t="s">
         <v>380</v>
       </c>
@@ -16075,7 +17897,7 @@
         <v>-74.400000000000006</v>
       </c>
     </row>
-    <row r="304" spans="2:13" ht="19.8">
+    <row r="304" spans="2:16" ht="19.8">
       <c r="B304" s="12" t="s">
         <v>380</v>
       </c>
@@ -16112,8 +17934,14 @@
       <c r="M304" s="11">
         <v>2720</v>
       </c>
-    </row>
-    <row r="305" spans="2:13" ht="19.8">
+      <c r="O304" s="10">
+        <v>331</v>
+      </c>
+      <c r="P304" s="11">
+        <v>5786.1</v>
+      </c>
+    </row>
+    <row r="305" spans="2:16" ht="19.8">
       <c r="B305" s="12" t="s">
         <v>380</v>
       </c>
@@ -16146,8 +17974,14 @@
       <c r="M305" s="10">
         <v>-48</v>
       </c>
-    </row>
-    <row r="306" spans="2:13" ht="19.8">
+      <c r="O305" s="10">
+        <v>334</v>
+      </c>
+      <c r="P305" s="11">
+        <v>3232</v>
+      </c>
+    </row>
+    <row r="306" spans="2:16" ht="19.8">
       <c r="B306" s="12" t="s">
         <v>380</v>
       </c>
@@ -16184,8 +18018,14 @@
       <c r="M306" s="11">
         <v>19380</v>
       </c>
-    </row>
-    <row r="307" spans="2:13" ht="19.8">
+      <c r="O306" s="10">
+        <v>335</v>
+      </c>
+      <c r="P306" s="11">
+        <v>2574</v>
+      </c>
+    </row>
+    <row r="307" spans="2:16" ht="19.8">
       <c r="B307" s="12" t="s">
         <v>380</v>
       </c>
@@ -16218,8 +18058,14 @@
       <c r="M307" s="10">
         <v>-42</v>
       </c>
-    </row>
-    <row r="308" spans="2:13" ht="19.8">
+      <c r="O307" s="10">
+        <v>336</v>
+      </c>
+      <c r="P307" s="11">
+        <v>1512</v>
+      </c>
+    </row>
+    <row r="308" spans="2:16" ht="19.8">
       <c r="B308" s="12" t="s">
         <v>390</v>
       </c>
@@ -16256,8 +18102,14 @@
       <c r="M308" s="11">
         <v>12096</v>
       </c>
-    </row>
-    <row r="309" spans="2:13" ht="19.8">
+      <c r="O308" s="10">
+        <v>337</v>
+      </c>
+      <c r="P308" s="11">
+        <v>4742.5</v>
+      </c>
+    </row>
+    <row r="309" spans="2:16" ht="19.8">
       <c r="B309" s="12" t="s">
         <v>390</v>
       </c>
@@ -16294,8 +18146,14 @@
       <c r="M309" s="11">
         <v>5175</v>
       </c>
-    </row>
-    <row r="310" spans="2:13">
+      <c r="O309" s="10">
+        <v>338</v>
+      </c>
+      <c r="P309" s="11">
+        <v>1382.5</v>
+      </c>
+    </row>
+    <row r="310" spans="2:16">
       <c r="B310" s="12" t="s">
         <v>390</v>
       </c>
@@ -16328,8 +18186,14 @@
       <c r="M310" s="10">
         <v>-43.9</v>
       </c>
-    </row>
-    <row r="311" spans="2:13" ht="19.8">
+      <c r="O310" s="10">
+        <v>325</v>
+      </c>
+      <c r="P310" s="11">
+        <v>1112</v>
+      </c>
+    </row>
+    <row r="311" spans="2:16" ht="19.8">
       <c r="B311" s="12" t="s">
         <v>394</v>
       </c>
@@ -16366,8 +18230,14 @@
       <c r="M311" s="11">
         <v>3392</v>
       </c>
-    </row>
-    <row r="312" spans="2:13">
+      <c r="O311" s="10">
+        <v>332</v>
+      </c>
+      <c r="P311" s="10">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="312" spans="2:16">
       <c r="B312" s="12" t="s">
         <v>394</v>
       </c>
@@ -16400,8 +18270,14 @@
       <c r="M312" s="10">
         <v>-22.4</v>
       </c>
-    </row>
-    <row r="313" spans="2:13" ht="19.8">
+      <c r="O312" s="10">
+        <v>333</v>
+      </c>
+      <c r="P312" s="10">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="313" spans="2:16" ht="19.8">
       <c r="B313" s="12" t="s">
         <v>394</v>
       </c>
@@ -16438,8 +18314,14 @@
       <c r="M313" s="11">
         <v>19040</v>
       </c>
-    </row>
-    <row r="314" spans="2:13">
+      <c r="O313" s="10">
+        <v>339</v>
+      </c>
+      <c r="P313" s="10">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="314" spans="2:16">
       <c r="B314" s="12" t="s">
         <v>394</v>
       </c>
@@ -16472,8 +18354,14 @@
       <c r="M314" s="10">
         <v>-88</v>
       </c>
-    </row>
-    <row r="315" spans="2:13" ht="19.8">
+      <c r="O314" s="10">
+        <v>340</v>
+      </c>
+      <c r="P314" s="10">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="315" spans="2:16" ht="19.8">
       <c r="B315" s="12" t="s">
         <v>394</v>
       </c>
@@ -16510,8 +18398,14 @@
       <c r="M315" s="11">
         <v>11220</v>
       </c>
-    </row>
-    <row r="316" spans="2:13">
+      <c r="O315" s="10">
+        <v>341</v>
+      </c>
+      <c r="P315" s="10">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="316" spans="2:16">
       <c r="B316" s="12" t="s">
         <v>394</v>
       </c>
@@ -16544,8 +18438,14 @@
       <c r="M316" s="10">
         <v>-98</v>
       </c>
-    </row>
-    <row r="317" spans="2:13" ht="19.8">
+      <c r="O316" s="10">
+        <v>342</v>
+      </c>
+      <c r="P316" s="10">
+        <v>847</v>
+      </c>
+    </row>
+    <row r="317" spans="2:16" ht="19.8">
       <c r="B317" s="12" t="s">
         <v>394</v>
       </c>
@@ -16582,8 +18482,14 @@
       <c r="M317" s="11">
         <v>23460</v>
       </c>
-    </row>
-    <row r="318" spans="2:13" ht="19.8">
+      <c r="O317" s="10">
+        <v>343</v>
+      </c>
+      <c r="P317" s="10">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="318" spans="2:16" ht="19.8">
       <c r="B318" s="12" t="s">
         <v>394</v>
       </c>
@@ -16616,8 +18522,14 @@
       <c r="M318" s="10">
         <v>-114</v>
       </c>
-    </row>
-    <row r="319" spans="2:13" ht="19.8">
+      <c r="O318" s="10">
+        <v>344</v>
+      </c>
+      <c r="P318" s="11">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="319" spans="2:16" ht="19.8">
       <c r="B319" s="12" t="s">
         <v>394</v>
       </c>
@@ -16654,8 +18566,14 @@
       <c r="M319" s="11">
         <v>20910</v>
       </c>
-    </row>
-    <row r="320" spans="2:13" ht="19.8">
+      <c r="O319" s="10">
+        <v>346</v>
+      </c>
+      <c r="P319" s="11">
+        <v>1001.6</v>
+      </c>
+    </row>
+    <row r="320" spans="2:16" ht="19.8">
       <c r="B320" s="12" t="s">
         <v>394</v>
       </c>
@@ -16688,8 +18606,14 @@
       <c r="M320" s="10">
         <v>-19</v>
       </c>
-    </row>
-    <row r="321" spans="2:13" ht="19.8">
+      <c r="O320" s="10">
+        <v>347</v>
+      </c>
+      <c r="P320" s="11">
+        <v>1273.4000000000001</v>
+      </c>
+    </row>
+    <row r="321" spans="2:16" ht="19.8">
       <c r="B321" s="12" t="s">
         <v>394</v>
       </c>
@@ -16726,8 +18650,14 @@
       <c r="M321" s="11">
         <v>44280</v>
       </c>
-    </row>
-    <row r="322" spans="2:13">
+      <c r="O321" s="10">
+        <v>356</v>
+      </c>
+      <c r="P321" s="11">
+        <v>2952</v>
+      </c>
+    </row>
+    <row r="322" spans="2:16">
       <c r="B322" s="12" t="s">
         <v>394</v>
       </c>
@@ -16760,8 +18690,14 @@
       <c r="M322" s="10">
         <v>-52</v>
       </c>
-    </row>
-    <row r="323" spans="2:13" ht="19.8">
+      <c r="O322" s="10">
+        <v>357</v>
+      </c>
+      <c r="P322" s="10">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="323" spans="2:16" ht="19.8">
       <c r="B323" s="12" t="s">
         <v>394</v>
       </c>
@@ -16798,8 +18734,14 @@
       <c r="M323" s="11">
         <v>5400</v>
       </c>
-    </row>
-    <row r="324" spans="2:13">
+      <c r="O323" s="10">
+        <v>380</v>
+      </c>
+      <c r="P323" s="11">
+        <v>3857</v>
+      </c>
+    </row>
+    <row r="324" spans="2:16">
       <c r="B324" s="12" t="s">
         <v>394</v>
       </c>
@@ -16832,8 +18774,14 @@
       <c r="M324" s="10">
         <v>-60</v>
       </c>
-    </row>
-    <row r="325" spans="2:13" ht="19.8">
+      <c r="O324" s="10">
+        <v>381</v>
+      </c>
+      <c r="P324" s="11">
+        <v>2109</v>
+      </c>
+    </row>
+    <row r="325" spans="2:16" ht="19.8">
       <c r="B325" s="12" t="s">
         <v>409</v>
       </c>
@@ -16870,8 +18818,14 @@
       <c r="M325" s="11">
         <v>6720</v>
       </c>
-    </row>
-    <row r="326" spans="2:13">
+      <c r="O325" s="10">
+        <v>382</v>
+      </c>
+      <c r="P325" s="11">
+        <v>3327</v>
+      </c>
+    </row>
+    <row r="326" spans="2:16">
       <c r="B326" s="12" t="s">
         <v>409</v>
       </c>
@@ -16904,8 +18858,14 @@
       <c r="M326" s="10">
         <v>-84</v>
       </c>
-    </row>
-    <row r="327" spans="2:13" ht="19.8">
+      <c r="O326" s="10">
+        <v>383</v>
+      </c>
+      <c r="P326" s="11">
+        <v>1159</v>
+      </c>
+    </row>
+    <row r="327" spans="2:16" ht="19.8">
       <c r="B327" s="12" t="s">
         <v>409</v>
       </c>
@@ -16942,8 +18902,14 @@
       <c r="M327" s="11">
         <v>14537</v>
       </c>
-    </row>
-    <row r="328" spans="2:13">
+      <c r="O327" s="10">
+        <v>345</v>
+      </c>
+      <c r="P327" s="11">
+        <v>1823</v>
+      </c>
+    </row>
+    <row r="328" spans="2:16">
       <c r="B328" s="12" t="s">
         <v>409</v>
       </c>
@@ -16976,8 +18942,14 @@
       <c r="M328" s="10">
         <v>-83.3</v>
       </c>
-    </row>
-    <row r="329" spans="2:13" ht="19.8">
+      <c r="O328" s="10">
+        <v>363</v>
+      </c>
+      <c r="P328" s="10">
+        <v>173.6</v>
+      </c>
+    </row>
+    <row r="329" spans="2:16" ht="19.8">
       <c r="B329" s="12" t="s">
         <v>409</v>
       </c>
@@ -17014,8 +18986,14 @@
       <c r="M329" s="11">
         <v>7260</v>
       </c>
-    </row>
-    <row r="330" spans="2:13">
+      <c r="O329" s="10">
+        <v>364</v>
+      </c>
+      <c r="P329" s="10">
+        <v>990</v>
+      </c>
+    </row>
+    <row r="330" spans="2:16">
       <c r="B330" s="12" t="s">
         <v>409</v>
       </c>
@@ -17048,8 +19026,14 @@
       <c r="M330" s="10">
         <v>-34</v>
       </c>
-    </row>
-    <row r="331" spans="2:13" ht="19.8">
+      <c r="O330" s="10">
+        <v>366</v>
+      </c>
+      <c r="P330" s="11">
+        <v>2934</v>
+      </c>
+    </row>
+    <row r="331" spans="2:16" ht="19.8">
       <c r="B331" s="12" t="s">
         <v>409</v>
       </c>
@@ -17086,8 +19070,14 @@
       <c r="M331" s="11">
         <v>9112</v>
       </c>
-    </row>
-    <row r="332" spans="2:13">
+      <c r="O331" s="10">
+        <v>367</v>
+      </c>
+      <c r="P331" s="11">
+        <v>3062.5</v>
+      </c>
+    </row>
+    <row r="332" spans="2:16">
       <c r="B332" s="12" t="s">
         <v>409</v>
       </c>
@@ -17120,8 +19110,14 @@
       <c r="M332" s="10">
         <v>-201</v>
       </c>
-    </row>
-    <row r="333" spans="2:13" ht="19.8">
+      <c r="O332" s="10">
+        <v>375</v>
+      </c>
+      <c r="P332" s="10">
+        <v>304.39999999999998</v>
+      </c>
+    </row>
+    <row r="333" spans="2:16" ht="19.8">
       <c r="B333" s="12" t="s">
         <v>409</v>
       </c>
@@ -17158,8 +19154,14 @@
       <c r="M333" s="11">
         <v>9036</v>
       </c>
-    </row>
-    <row r="334" spans="2:13">
+      <c r="O333" s="10">
+        <v>376</v>
+      </c>
+      <c r="P333" s="10">
+        <v>685.1</v>
+      </c>
+    </row>
+    <row r="334" spans="2:16">
       <c r="B334" s="12" t="s">
         <v>409</v>
       </c>
@@ -17192,8 +19194,14 @@
       <c r="M334" s="10">
         <v>-32.4</v>
       </c>
-    </row>
-    <row r="335" spans="2:13" ht="19.8">
+      <c r="O334" s="10">
+        <v>379</v>
+      </c>
+      <c r="P334" s="11">
+        <v>3327</v>
+      </c>
+    </row>
+    <row r="335" spans="2:16" ht="19.8">
       <c r="B335" s="12" t="s">
         <v>409</v>
       </c>
@@ -17230,8 +19238,14 @@
       <c r="M335" s="11">
         <v>5580</v>
       </c>
-    </row>
-    <row r="336" spans="2:13" ht="19.8">
+      <c r="O335" s="10">
+        <v>393</v>
+      </c>
+      <c r="P335" s="11">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="336" spans="2:16" ht="19.8">
       <c r="B336" s="12" t="s">
         <v>409</v>
       </c>
@@ -17264,8 +19278,14 @@
       <c r="M336" s="10">
         <v>-22</v>
       </c>
-    </row>
-    <row r="337" spans="2:13" ht="19.8">
+      <c r="O336" s="10">
+        <v>406</v>
+      </c>
+      <c r="P336" s="11">
+        <v>3595.2</v>
+      </c>
+    </row>
+    <row r="337" spans="2:16" ht="19.8">
       <c r="B337" s="12" t="s">
         <v>409</v>
       </c>
@@ -17302,8 +19322,14 @@
       <c r="M337" s="11">
         <v>7380</v>
       </c>
-    </row>
-    <row r="338" spans="2:13" ht="19.8">
+      <c r="O337" s="10">
+        <v>407</v>
+      </c>
+      <c r="P337" s="10">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="338" spans="2:16" ht="19.8">
       <c r="B338" s="12" t="s">
         <v>409</v>
       </c>
@@ -17336,8 +19362,14 @@
       <c r="M338" s="10">
         <v>-42</v>
       </c>
-    </row>
-    <row r="339" spans="2:13" ht="19.8">
+      <c r="O338" s="10">
+        <v>408</v>
+      </c>
+      <c r="P338" s="11">
+        <v>2880</v>
+      </c>
+    </row>
+    <row r="339" spans="2:16" ht="19.8">
       <c r="B339" s="12" t="s">
         <v>409</v>
       </c>
@@ -17374,8 +19406,14 @@
       <c r="M339" s="11">
         <v>8892</v>
       </c>
-    </row>
-    <row r="340" spans="2:13" ht="19.8">
+      <c r="O339" s="10">
+        <v>409</v>
+      </c>
+      <c r="P339" s="11">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="340" spans="2:16" ht="19.8">
       <c r="B340" s="12" t="s">
         <v>409</v>
       </c>
@@ -17408,8 +19446,14 @@
       <c r="M340" s="10">
         <v>-32.799999999999997</v>
       </c>
-    </row>
-    <row r="341" spans="2:13" ht="19.8">
+      <c r="O340" s="10">
+        <v>362</v>
+      </c>
+      <c r="P340" s="10">
+        <v>930</v>
+      </c>
+    </row>
+    <row r="341" spans="2:16" ht="19.8">
       <c r="B341" s="12" t="s">
         <v>409</v>
       </c>
@@ -17447,7 +19491,7 @@
         <v>3510</v>
       </c>
     </row>
-    <row r="342" spans="2:13" ht="19.8">
+    <row r="342" spans="2:16" ht="19.8">
       <c r="B342" s="12" t="s">
         <v>409</v>
       </c>
@@ -17480,8 +19524,14 @@
       <c r="M342" s="10">
         <v>-59</v>
       </c>
-    </row>
-    <row r="343" spans="2:13" ht="19.8">
+      <c r="O342" s="10">
+        <v>368</v>
+      </c>
+      <c r="P342" s="10">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="343" spans="2:16" ht="19.8">
       <c r="B343" s="12" t="s">
         <v>428</v>
       </c>
@@ -17518,8 +19568,14 @@
       <c r="M343" s="11">
         <v>3875</v>
       </c>
-    </row>
-    <row r="344" spans="2:13">
+      <c r="O343" s="10">
+        <v>369</v>
+      </c>
+      <c r="P343" s="10">
+        <v>810</v>
+      </c>
+    </row>
+    <row r="344" spans="2:16">
       <c r="B344" s="12" t="s">
         <v>428</v>
       </c>
@@ -17552,8 +19608,14 @@
       <c r="M344" s="10">
         <v>-87.5</v>
       </c>
-    </row>
-    <row r="345" spans="2:13" ht="19.8">
+      <c r="O344" s="10">
+        <v>371</v>
+      </c>
+      <c r="P344" s="10">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="345" spans="2:16" ht="19.8">
       <c r="B345" s="12" t="s">
         <v>428</v>
       </c>
@@ -17590,8 +19652,14 @@
       <c r="M345" s="11">
         <v>46540</v>
       </c>
-    </row>
-    <row r="346" spans="2:13">
+      <c r="O345" s="10">
+        <v>372</v>
+      </c>
+      <c r="P345" s="10">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="346" spans="2:16">
       <c r="B346" s="12" t="s">
         <v>428</v>
       </c>
@@ -17624,8 +19692,14 @@
       <c r="M346" s="10">
         <v>-86</v>
       </c>
-    </row>
-    <row r="347" spans="2:13" ht="19.8">
+      <c r="O346" s="10">
+        <v>373</v>
+      </c>
+      <c r="P346" s="10">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="347" spans="2:16" ht="19.8">
       <c r="B347" s="12" t="s">
         <v>433</v>
       </c>
@@ -17662,8 +19736,14 @@
       <c r="M347" s="11">
         <v>13056</v>
       </c>
-    </row>
-    <row r="348" spans="2:13" ht="19.8">
+      <c r="O347" s="10">
+        <v>374</v>
+      </c>
+      <c r="P347" s="10">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="348" spans="2:16" ht="19.8">
       <c r="B348" s="12" t="s">
         <v>433</v>
       </c>
@@ -17696,8 +19776,14 @@
       <c r="M348" s="10">
         <v>-106</v>
       </c>
-    </row>
-    <row r="349" spans="2:13" ht="19.8">
+      <c r="O348" s="10">
+        <v>377</v>
+      </c>
+      <c r="P348" s="10">
+        <v>512.5</v>
+      </c>
+    </row>
+    <row r="349" spans="2:16" ht="19.8">
       <c r="B349" s="12" t="s">
         <v>437</v>
       </c>
@@ -17734,8 +19820,14 @@
       <c r="M349" s="11">
         <v>17920</v>
       </c>
-    </row>
-    <row r="350" spans="2:13" ht="19.8">
+      <c r="O349" s="10">
+        <v>378</v>
+      </c>
+      <c r="P349" s="11">
+        <v>2010.6</v>
+      </c>
+    </row>
+    <row r="350" spans="2:16" ht="19.8">
       <c r="B350" s="12" t="s">
         <v>437</v>
       </c>
@@ -17768,8 +19860,14 @@
       <c r="M350" s="10">
         <v>-128</v>
       </c>
-    </row>
-    <row r="351" spans="2:13" ht="19.8">
+      <c r="O350" s="10">
+        <v>403</v>
+      </c>
+      <c r="P350" s="10">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="351" spans="2:16" ht="19.8">
       <c r="B351" s="12" t="s">
         <v>437</v>
       </c>
@@ -17806,8 +19904,14 @@
       <c r="M351" s="11">
         <v>6300</v>
       </c>
-    </row>
-    <row r="352" spans="2:13" ht="19.8">
+      <c r="O351" s="10">
+        <v>404</v>
+      </c>
+      <c r="P351" s="10">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="352" spans="2:16" ht="19.8">
       <c r="B352" s="12" t="s">
         <v>437</v>
       </c>
@@ -17840,8 +19944,14 @@
       <c r="M352" s="10">
         <v>-70</v>
       </c>
-    </row>
-    <row r="353" spans="2:13" ht="19.8">
+      <c r="O352" s="10">
+        <v>413</v>
+      </c>
+      <c r="P352" s="10">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="353" spans="2:16" ht="19.8">
       <c r="B353" s="12" t="s">
         <v>437</v>
       </c>
@@ -17878,8 +19988,14 @@
       <c r="M353" s="10">
         <v>360</v>
       </c>
-    </row>
-    <row r="354" spans="2:13" ht="19.8">
+      <c r="O353" s="10">
+        <v>414</v>
+      </c>
+      <c r="P353" s="10">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="354" spans="2:16" ht="19.8">
       <c r="B354" s="12" t="s">
         <v>437</v>
       </c>
@@ -17912,8 +20028,14 @@
       <c r="M354" s="10">
         <v>-24</v>
       </c>
-    </row>
-    <row r="355" spans="2:13" ht="19.8">
+      <c r="O354" s="10">
+        <v>416</v>
+      </c>
+      <c r="P354" s="11">
+        <v>2970</v>
+      </c>
+    </row>
+    <row r="355" spans="2:16" ht="19.8">
       <c r="B355" s="12" t="s">
         <v>437</v>
       </c>
@@ -17950,8 +20072,14 @@
       <c r="M355" s="11">
         <v>17355</v>
       </c>
-    </row>
-    <row r="356" spans="2:13" ht="19.8">
+      <c r="O355" s="10">
+        <v>417</v>
+      </c>
+      <c r="P355" s="10">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="356" spans="2:16" ht="19.8">
       <c r="B356" s="12" t="s">
         <v>437</v>
       </c>
@@ -17984,8 +20112,14 @@
       <c r="M356" s="10">
         <v>-19.5</v>
       </c>
-    </row>
-    <row r="357" spans="2:13" ht="19.8">
+      <c r="O356" s="10">
+        <v>394</v>
+      </c>
+      <c r="P356" s="10">
+        <v>258.60000000000002</v>
+      </c>
+    </row>
+    <row r="357" spans="2:16" ht="19.8">
       <c r="B357" s="12" t="s">
         <v>437</v>
       </c>
@@ -18022,8 +20156,14 @@
       <c r="M357" s="11">
         <v>22410</v>
       </c>
-    </row>
-    <row r="358" spans="2:13">
+      <c r="O357" s="10">
+        <v>395</v>
+      </c>
+      <c r="P357" s="10">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="358" spans="2:16">
       <c r="B358" s="12" t="s">
         <v>437</v>
       </c>
@@ -18056,8 +20196,14 @@
       <c r="M358" s="10">
         <v>-69</v>
       </c>
-    </row>
-    <row r="359" spans="2:13" ht="19.8">
+      <c r="O358" s="10">
+        <v>396</v>
+      </c>
+      <c r="P358" s="10">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="359" spans="2:16" ht="19.8">
       <c r="B359" s="5">
         <v>44936</v>
       </c>
@@ -18094,8 +20240,14 @@
       <c r="M359" s="11">
         <v>48240</v>
       </c>
-    </row>
-    <row r="360" spans="2:13" ht="19.8">
+      <c r="O359" s="10">
+        <v>397</v>
+      </c>
+      <c r="P359" s="11">
+        <v>8702</v>
+      </c>
+    </row>
+    <row r="360" spans="2:16" ht="19.8">
       <c r="B360" s="5">
         <v>44936</v>
       </c>
@@ -18128,8 +20280,14 @@
       <c r="M360" s="10">
         <v>-16</v>
       </c>
-    </row>
-    <row r="361" spans="2:13" ht="19.8">
+      <c r="O360" s="10">
+        <v>398</v>
+      </c>
+      <c r="P360" s="11">
+        <v>1680</v>
+      </c>
+    </row>
+    <row r="361" spans="2:16" ht="19.8">
       <c r="B361" s="5">
         <v>45179</v>
       </c>
@@ -18166,8 +20324,14 @@
       <c r="M361" s="11">
         <v>8840</v>
       </c>
-    </row>
-    <row r="362" spans="2:13">
+      <c r="O361" s="10">
+        <v>399</v>
+      </c>
+      <c r="P361" s="11">
+        <v>2594</v>
+      </c>
+    </row>
+    <row r="362" spans="2:16">
       <c r="B362" s="5">
         <v>45179</v>
       </c>
@@ -18200,8 +20364,14 @@
       <c r="M362" s="10">
         <v>-56</v>
       </c>
-    </row>
-    <row r="363" spans="2:13" ht="19.8">
+      <c r="O362" s="10">
+        <v>484</v>
+      </c>
+      <c r="P362" s="10">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="363" spans="2:16" ht="19.8">
       <c r="B363" s="5">
         <v>45179</v>
       </c>
@@ -18238,8 +20408,14 @@
       <c r="M363" s="11">
         <v>4030</v>
       </c>
-    </row>
-    <row r="364" spans="2:13" ht="19.8">
+      <c r="O363" s="10">
+        <v>453</v>
+      </c>
+      <c r="P363" s="11">
+        <v>4628</v>
+      </c>
+    </row>
+    <row r="364" spans="2:16" ht="19.8">
       <c r="B364" s="5">
         <v>45179</v>
       </c>
@@ -18276,8 +20452,14 @@
       <c r="M364" s="10">
         <v>850</v>
       </c>
-    </row>
-    <row r="365" spans="2:13">
+      <c r="O364" s="10">
+        <v>454</v>
+      </c>
+      <c r="P364" s="11">
+        <v>2338.5</v>
+      </c>
+    </row>
+    <row r="365" spans="2:16">
       <c r="B365" s="5">
         <v>45179</v>
       </c>
@@ -18310,8 +20492,14 @@
       <c r="M365" s="10">
         <v>-92</v>
       </c>
-    </row>
-    <row r="366" spans="2:13" ht="19.8">
+      <c r="O365" s="10">
+        <v>455</v>
+      </c>
+      <c r="P365" s="10">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="366" spans="2:16" ht="19.8">
       <c r="B366" s="12" t="s">
         <v>456</v>
       </c>
@@ -18348,8 +20536,14 @@
       <c r="M366" s="11">
         <v>3510</v>
       </c>
-    </row>
-    <row r="367" spans="2:13" ht="19.8">
+      <c r="O366" s="10">
+        <v>405</v>
+      </c>
+      <c r="P366" s="10">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="367" spans="2:16" ht="19.8">
       <c r="B367" s="12" t="s">
         <v>456</v>
       </c>
@@ -18382,8 +20576,14 @@
       <c r="M367" s="10">
         <v>-59</v>
       </c>
-    </row>
-    <row r="368" spans="2:13" ht="19.8">
+      <c r="O367" s="10">
+        <v>411</v>
+      </c>
+      <c r="P367" s="11">
+        <v>1063</v>
+      </c>
+    </row>
+    <row r="368" spans="2:16" ht="19.8">
       <c r="B368" s="12" t="s">
         <v>456</v>
       </c>
@@ -18420,8 +20620,14 @@
       <c r="M368" s="11">
         <v>19435</v>
       </c>
-    </row>
-    <row r="369" spans="2:13" ht="19.8">
+      <c r="O368" s="10">
+        <v>410</v>
+      </c>
+      <c r="P368" s="10">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="369" spans="2:16" ht="19.8">
       <c r="B369" s="12" t="s">
         <v>456</v>
       </c>
@@ -18454,8 +20660,14 @@
       <c r="M369" s="10">
         <v>-91.5</v>
       </c>
-    </row>
-    <row r="370" spans="2:13" ht="19.8">
+      <c r="O369" s="10">
+        <v>412</v>
+      </c>
+      <c r="P369" s="11">
+        <v>1113</v>
+      </c>
+    </row>
+    <row r="370" spans="2:16" ht="19.8">
       <c r="B370" s="12" t="s">
         <v>461</v>
       </c>
@@ -18492,8 +20704,14 @@
       <c r="M370" s="11">
         <v>23520</v>
       </c>
-    </row>
-    <row r="371" spans="2:13">
+      <c r="O370" s="10">
+        <v>419</v>
+      </c>
+      <c r="P370" s="10">
+        <v>604.5</v>
+      </c>
+    </row>
+    <row r="371" spans="2:16">
       <c r="B371" s="12" t="s">
         <v>461</v>
       </c>
@@ -18526,8 +20744,14 @@
       <c r="M371" s="10">
         <v>-168</v>
       </c>
-    </row>
-    <row r="372" spans="2:13" ht="19.8">
+      <c r="O371" s="10">
+        <v>421</v>
+      </c>
+      <c r="P371" s="10">
+        <v>878</v>
+      </c>
+    </row>
+    <row r="372" spans="2:16" ht="19.8">
       <c r="B372" s="12" t="s">
         <v>461</v>
       </c>
@@ -18564,8 +20788,14 @@
       <c r="M372" s="11">
         <v>130200</v>
       </c>
-    </row>
-    <row r="373" spans="2:13">
+      <c r="O372" s="10">
+        <v>422</v>
+      </c>
+      <c r="P372" s="10">
+        <v>864.7</v>
+      </c>
+    </row>
+    <row r="373" spans="2:16">
       <c r="B373" s="12" t="s">
         <v>461</v>
       </c>
@@ -18598,8 +20828,14 @@
       <c r="M373" s="10">
         <v>-180</v>
       </c>
-    </row>
-    <row r="374" spans="2:13" ht="19.8">
+      <c r="O373" s="10">
+        <v>423</v>
+      </c>
+      <c r="P373" s="10">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="374" spans="2:16" ht="19.8">
       <c r="B374" s="12" t="s">
         <v>461</v>
       </c>
@@ -18636,8 +20872,14 @@
       <c r="M374" s="11">
         <v>60760</v>
       </c>
-    </row>
-    <row r="375" spans="2:13">
+      <c r="O374" s="10">
+        <v>425</v>
+      </c>
+      <c r="P374" s="10">
+        <v>31.5</v>
+      </c>
+    </row>
+    <row r="375" spans="2:16">
       <c r="B375" s="12" t="s">
         <v>461</v>
       </c>
@@ -18670,8 +20912,14 @@
       <c r="M375" s="10">
         <v>-184</v>
       </c>
-    </row>
-    <row r="376" spans="2:13" ht="19.8">
+      <c r="O375" s="10">
+        <v>426</v>
+      </c>
+      <c r="P375" s="10">
+        <v>444.6</v>
+      </c>
+    </row>
+    <row r="376" spans="2:16" ht="19.8">
       <c r="B376" s="12" t="s">
         <v>461</v>
       </c>
@@ -18708,8 +20956,14 @@
       <c r="M376" s="11">
         <v>11700</v>
       </c>
-    </row>
-    <row r="377" spans="2:13">
+      <c r="O376" s="10">
+        <v>427</v>
+      </c>
+      <c r="P376" s="10">
+        <v>848</v>
+      </c>
+    </row>
+    <row r="377" spans="2:16">
       <c r="B377" s="12" t="s">
         <v>461</v>
       </c>
@@ -18742,8 +20996,14 @@
       <c r="M377" s="10">
         <v>-30</v>
       </c>
-    </row>
-    <row r="378" spans="2:13" ht="19.8">
+      <c r="O377" s="10">
+        <v>428</v>
+      </c>
+      <c r="P377" s="11">
+        <v>2695</v>
+      </c>
+    </row>
+    <row r="378" spans="2:16" ht="19.8">
       <c r="B378" s="12" t="s">
         <v>461</v>
       </c>
@@ -18780,8 +21040,14 @@
       <c r="M378" s="11">
         <v>8992</v>
       </c>
-    </row>
-    <row r="379" spans="2:13">
+      <c r="O378" s="10">
+        <v>429</v>
+      </c>
+      <c r="P378" s="10">
+        <v>770</v>
+      </c>
+    </row>
+    <row r="379" spans="2:16">
       <c r="B379" s="12" t="s">
         <v>461</v>
       </c>
@@ -18814,8 +21080,14 @@
       <c r="M379" s="11">
         <v>-3042.4</v>
       </c>
-    </row>
-    <row r="380" spans="2:13" ht="19.8">
+      <c r="O379" s="10">
+        <v>431</v>
+      </c>
+      <c r="P379" s="10">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="380" spans="2:16" ht="19.8">
       <c r="B380" s="12" t="s">
         <v>461</v>
       </c>
@@ -18852,8 +21124,14 @@
       <c r="M380" s="11">
         <v>4928</v>
       </c>
-    </row>
-    <row r="381" spans="2:13">
+      <c r="O380" s="10">
+        <v>446</v>
+      </c>
+      <c r="P380" s="10">
+        <v>323.2</v>
+      </c>
+    </row>
+    <row r="381" spans="2:16">
       <c r="B381" s="12" t="s">
         <v>461</v>
       </c>
@@ -18886,8 +21164,14 @@
       <c r="M381" s="10">
         <v>-81.599999999999994</v>
       </c>
-    </row>
-    <row r="382" spans="2:13" ht="19.8">
+      <c r="O381" s="10">
+        <v>424</v>
+      </c>
+      <c r="P381" s="10">
+        <v>910</v>
+      </c>
+    </row>
+    <row r="382" spans="2:16" ht="19.8">
       <c r="B382" s="12" t="s">
         <v>461</v>
       </c>
@@ -18924,8 +21208,14 @@
       <c r="M382" s="11">
         <v>3264</v>
       </c>
-    </row>
-    <row r="383" spans="2:13">
+      <c r="O382" s="10">
+        <v>418</v>
+      </c>
+      <c r="P382" s="10">
+        <v>895</v>
+      </c>
+    </row>
+    <row r="383" spans="2:16">
       <c r="B383" s="12" t="s">
         <v>461</v>
       </c>
@@ -18958,8 +21248,14 @@
       <c r="M383" s="10">
         <v>-100.8</v>
       </c>
-    </row>
-    <row r="384" spans="2:13" ht="19.8">
+      <c r="O383" s="10">
+        <v>420</v>
+      </c>
+      <c r="P383" s="10">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="384" spans="2:16" ht="19.8">
       <c r="B384" s="12" t="s">
         <v>461</v>
       </c>
@@ -18996,8 +21292,14 @@
       <c r="M384" s="11">
         <v>12000</v>
       </c>
-    </row>
-    <row r="385" spans="2:13" ht="19.8">
+      <c r="O384" s="10">
+        <v>432</v>
+      </c>
+      <c r="P384" s="11">
+        <v>1316.9</v>
+      </c>
+    </row>
+    <row r="385" spans="2:16" ht="19.8">
       <c r="B385" s="12" t="s">
         <v>461</v>
       </c>
@@ -19034,8 +21336,14 @@
       <c r="M385" s="11">
         <v>6000</v>
       </c>
-    </row>
-    <row r="386" spans="2:13" ht="19.8">
+      <c r="O385" s="10">
+        <v>433</v>
+      </c>
+      <c r="P385" s="11">
+        <v>2484</v>
+      </c>
+    </row>
+    <row r="386" spans="2:16" ht="19.8">
       <c r="B386" s="12" t="s">
         <v>461</v>
       </c>
@@ -19072,8 +21380,14 @@
       <c r="M386" s="11">
         <v>9000</v>
       </c>
-    </row>
-    <row r="387" spans="2:13" ht="19.8">
+      <c r="O386" s="10">
+        <v>434</v>
+      </c>
+      <c r="P386" s="10">
+        <v>846</v>
+      </c>
+    </row>
+    <row r="387" spans="2:16" ht="19.8">
       <c r="B387" s="12" t="s">
         <v>461</v>
       </c>
@@ -19110,8 +21424,14 @@
       <c r="M387" s="11">
         <v>8000</v>
       </c>
-    </row>
-    <row r="388" spans="2:13" ht="19.8">
+      <c r="O387" s="10">
+        <v>435</v>
+      </c>
+      <c r="P387" s="11">
+        <v>1578</v>
+      </c>
+    </row>
+    <row r="388" spans="2:16" ht="19.8">
       <c r="B388" s="12" t="s">
         <v>461</v>
       </c>
@@ -19148,8 +21468,14 @@
       <c r="M388" s="11">
         <v>9000</v>
       </c>
-    </row>
-    <row r="389" spans="2:13" ht="19.8">
+      <c r="O388" s="10">
+        <v>436</v>
+      </c>
+      <c r="P388" s="11">
+        <v>1980</v>
+      </c>
+    </row>
+    <row r="389" spans="2:16" ht="19.8">
       <c r="B389" s="12" t="s">
         <v>461</v>
       </c>
@@ -19186,8 +21512,14 @@
       <c r="M389" s="11">
         <v>9000</v>
       </c>
-    </row>
-    <row r="390" spans="2:13" ht="19.8">
+      <c r="O389" s="10">
+        <v>442</v>
+      </c>
+      <c r="P389" s="11">
+        <v>2362.5</v>
+      </c>
+    </row>
+    <row r="390" spans="2:16" ht="19.8">
       <c r="B390" s="12" t="s">
         <v>461</v>
       </c>
@@ -19224,8 +21556,14 @@
       <c r="M390" s="11">
         <v>1500</v>
       </c>
-    </row>
-    <row r="391" spans="2:13" ht="19.8">
+      <c r="O390" s="10">
+        <v>445</v>
+      </c>
+      <c r="P390" s="10">
+        <v>834.1</v>
+      </c>
+    </row>
+    <row r="391" spans="2:16" ht="19.8">
       <c r="B391" s="12" t="s">
         <v>461</v>
       </c>
@@ -19262,8 +21600,14 @@
       <c r="M391" s="10">
         <v>115</v>
       </c>
-    </row>
-    <row r="392" spans="2:13" ht="19.8">
+      <c r="O391" s="10">
+        <v>456</v>
+      </c>
+      <c r="P391" s="10">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="392" spans="2:16" ht="19.8">
       <c r="B392" s="12" t="s">
         <v>461</v>
       </c>
@@ -19296,8 +21640,14 @@
       <c r="M392" s="10">
         <v>-53.5</v>
       </c>
-    </row>
-    <row r="393" spans="2:13" ht="19.8">
+      <c r="O392" s="10">
+        <v>457</v>
+      </c>
+      <c r="P392" s="10">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="393" spans="2:16" ht="19.8">
       <c r="B393" s="12" t="s">
         <v>461</v>
       </c>
@@ -19334,8 +21684,14 @@
       <c r="M393" s="11">
         <v>6320</v>
       </c>
-    </row>
-    <row r="394" spans="2:13" ht="19.8">
+      <c r="O393" s="10">
+        <v>458</v>
+      </c>
+      <c r="P393" s="10">
+        <v>146.5</v>
+      </c>
+    </row>
+    <row r="394" spans="2:16" ht="19.8">
       <c r="B394" s="12" t="s">
         <v>461</v>
       </c>
@@ -19372,8 +21728,14 @@
       <c r="M394" s="11">
         <v>1245</v>
       </c>
-    </row>
-    <row r="395" spans="2:13" ht="19.8">
+      <c r="O394" s="10">
+        <v>459</v>
+      </c>
+      <c r="P394" s="10">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="395" spans="2:16" ht="19.8">
       <c r="B395" s="12" t="s">
         <v>461</v>
       </c>
@@ -19406,8 +21768,14 @@
       <c r="M395" s="10">
         <v>-8.5</v>
       </c>
-    </row>
-    <row r="396" spans="2:13" ht="19.8">
+      <c r="O395" s="10">
+        <v>460</v>
+      </c>
+      <c r="P395" s="10">
+        <v>385.5</v>
+      </c>
+    </row>
+    <row r="396" spans="2:16" ht="19.8">
       <c r="B396" s="12" t="s">
         <v>461</v>
       </c>
@@ -19444,8 +21812,14 @@
       <c r="M396" s="11">
         <v>3510</v>
       </c>
-    </row>
-    <row r="397" spans="2:13" ht="19.8">
+      <c r="O396" s="10">
+        <v>437</v>
+      </c>
+      <c r="P396" s="10">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="397" spans="2:16" ht="19.8">
       <c r="B397" s="12" t="s">
         <v>461</v>
       </c>
@@ -19482,8 +21856,14 @@
       <c r="M397" s="10">
         <v>720</v>
       </c>
-    </row>
-    <row r="398" spans="2:13" ht="19.8">
+      <c r="O397" s="10">
+        <v>438</v>
+      </c>
+      <c r="P397" s="11">
+        <v>1740</v>
+      </c>
+    </row>
+    <row r="398" spans="2:16" ht="19.8">
       <c r="B398" s="12" t="s">
         <v>461</v>
       </c>
@@ -19516,8 +21896,14 @@
       <c r="M398" s="10">
         <v>-7</v>
       </c>
-    </row>
-    <row r="399" spans="2:13" ht="19.8">
+      <c r="O398" s="10">
+        <v>439</v>
+      </c>
+      <c r="P398" s="10">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="399" spans="2:16" ht="19.8">
       <c r="B399" s="12" t="s">
         <v>461</v>
       </c>
@@ -19554,8 +21940,14 @@
       <c r="M399" s="11">
         <v>3328</v>
       </c>
-    </row>
-    <row r="400" spans="2:13" ht="19.8">
+      <c r="O399" s="10">
+        <v>440</v>
+      </c>
+      <c r="P399" s="10">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="400" spans="2:16" ht="19.8">
       <c r="B400" s="12" t="s">
         <v>461</v>
       </c>
@@ -19588,8 +21980,14 @@
       <c r="M400" s="10">
         <v>-95.2</v>
       </c>
-    </row>
-    <row r="401" spans="2:13" ht="19.8">
+      <c r="O400" s="10">
+        <v>441</v>
+      </c>
+      <c r="P400" s="11">
+        <v>1165.0999999999999</v>
+      </c>
+    </row>
+    <row r="401" spans="2:16" ht="19.8">
       <c r="B401" s="12" t="s">
         <v>461</v>
       </c>
@@ -19626,8 +22024,14 @@
       <c r="M401" s="11">
         <v>4208</v>
       </c>
-    </row>
-    <row r="402" spans="2:13" ht="19.8">
+      <c r="O401" s="10">
+        <v>444</v>
+      </c>
+      <c r="P401" s="10">
+        <v>237.6</v>
+      </c>
+    </row>
+    <row r="402" spans="2:16" ht="19.8">
       <c r="B402" s="12" t="s">
         <v>461</v>
       </c>
@@ -19660,8 +22064,14 @@
       <c r="M402" s="10">
         <v>-87.2</v>
       </c>
-    </row>
-    <row r="403" spans="2:13" ht="19.8">
+      <c r="O402" s="10">
+        <v>449</v>
+      </c>
+      <c r="P402" s="11">
+        <v>1044</v>
+      </c>
+    </row>
+    <row r="403" spans="2:16" ht="19.8">
       <c r="B403" s="12" t="s">
         <v>495</v>
       </c>
@@ -19698,8 +22108,14 @@
       <c r="M403" s="11">
         <v>56700</v>
       </c>
-    </row>
-    <row r="404" spans="2:13">
+      <c r="O403" s="10">
+        <v>450</v>
+      </c>
+      <c r="P403" s="11">
+        <v>2430</v>
+      </c>
+    </row>
+    <row r="404" spans="2:16">
       <c r="B404" s="12" t="s">
         <v>495</v>
       </c>
@@ -19732,8 +22148,14 @@
       <c r="M404" s="10">
         <v>-30</v>
       </c>
-    </row>
-    <row r="405" spans="2:13" ht="19.8">
+      <c r="O404" s="10">
+        <v>451</v>
+      </c>
+      <c r="P404" s="10">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="405" spans="2:16" ht="19.8">
       <c r="B405" s="12" t="s">
         <v>495</v>
       </c>
@@ -19770,8 +22192,14 @@
       <c r="M405" s="11">
         <v>1470</v>
       </c>
-    </row>
-    <row r="406" spans="2:13" ht="19.8">
+      <c r="O405" s="10">
+        <v>443</v>
+      </c>
+      <c r="P405" s="10">
+        <v>822.5</v>
+      </c>
+    </row>
+    <row r="406" spans="2:16" ht="19.8">
       <c r="B406" s="12" t="s">
         <v>495</v>
       </c>
@@ -19808,8 +22236,14 @@
       <c r="M406" s="10">
         <v>500</v>
       </c>
-    </row>
-    <row r="407" spans="2:13">
+      <c r="O406" s="10">
+        <v>447</v>
+      </c>
+      <c r="P406" s="10">
+        <v>100.5</v>
+      </c>
+    </row>
+    <row r="407" spans="2:16">
       <c r="B407" s="12" t="s">
         <v>495</v>
       </c>
@@ -19842,8 +22276,14 @@
       <c r="M407" s="10">
         <v>-73</v>
       </c>
-    </row>
-    <row r="408" spans="2:13" ht="19.8">
+      <c r="O407" s="10">
+        <v>452</v>
+      </c>
+      <c r="P407" s="10">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="408" spans="2:16" ht="19.8">
       <c r="B408" s="12" t="s">
         <v>495</v>
       </c>
@@ -19880,8 +22320,14 @@
       <c r="M408" s="11">
         <v>16200</v>
       </c>
-    </row>
-    <row r="409" spans="2:13" ht="19.8">
+      <c r="O408" s="10">
+        <v>448</v>
+      </c>
+      <c r="P408" s="11">
+        <v>9000</v>
+      </c>
+    </row>
+    <row r="409" spans="2:16" ht="19.8">
       <c r="B409" s="12" t="s">
         <v>495</v>
       </c>
@@ -19918,8 +22364,14 @@
       <c r="M409" s="11">
         <v>3830</v>
       </c>
-    </row>
-    <row r="410" spans="2:13" ht="19.8">
+      <c r="O409" s="10">
+        <v>468</v>
+      </c>
+      <c r="P409" s="11">
+        <v>1780</v>
+      </c>
+    </row>
+    <row r="410" spans="2:16" ht="19.8">
       <c r="B410" s="12" t="s">
         <v>495</v>
       </c>
@@ -19952,8 +22404,14 @@
       <c r="M410" s="10">
         <v>-27</v>
       </c>
-    </row>
-    <row r="411" spans="2:13" ht="19.8">
+      <c r="O410" s="10">
+        <v>493</v>
+      </c>
+      <c r="P410" s="10">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="411" spans="2:16" ht="19.8">
       <c r="B411" s="12" t="s">
         <v>495</v>
       </c>
@@ -19990,8 +22448,14 @@
       <c r="M411" s="11">
         <v>15000</v>
       </c>
-    </row>
-    <row r="412" spans="2:13" ht="19.8">
+      <c r="O411" s="10">
+        <v>462</v>
+      </c>
+      <c r="P411" s="10">
+        <v>770</v>
+      </c>
+    </row>
+    <row r="412" spans="2:16" ht="19.8">
       <c r="B412" s="12" t="s">
         <v>495</v>
       </c>
@@ -20028,8 +22492,14 @@
       <c r="M412" s="11">
         <v>30000</v>
       </c>
-    </row>
-    <row r="413" spans="2:13" ht="19.8">
+      <c r="O412" s="10">
+        <v>463</v>
+      </c>
+      <c r="P412" s="11">
+        <v>1190</v>
+      </c>
+    </row>
+    <row r="413" spans="2:16" ht="19.8">
       <c r="B413" s="12" t="s">
         <v>505</v>
       </c>
@@ -20066,8 +22536,14 @@
       <c r="M413" s="11">
         <v>10790</v>
       </c>
-    </row>
-    <row r="414" spans="2:13" ht="19.8">
+      <c r="O413" s="10">
+        <v>464</v>
+      </c>
+      <c r="P413" s="11">
+        <v>1386</v>
+      </c>
+    </row>
+    <row r="414" spans="2:16" ht="19.8">
       <c r="B414" s="12" t="s">
         <v>505</v>
       </c>
@@ -20100,8 +22576,14 @@
       <c r="M414" s="10">
         <v>-11</v>
       </c>
-    </row>
-    <row r="415" spans="2:13" ht="19.8">
+      <c r="O414" s="10">
+        <v>465</v>
+      </c>
+      <c r="P414" s="11">
+        <v>1674</v>
+      </c>
+    </row>
+    <row r="415" spans="2:16" ht="19.8">
       <c r="B415" s="12" t="s">
         <v>505</v>
       </c>
@@ -20138,8 +22620,14 @@
       <c r="M415" s="11">
         <v>19440</v>
       </c>
-    </row>
-    <row r="416" spans="2:13">
+      <c r="O415" s="10">
+        <v>466</v>
+      </c>
+      <c r="P415" s="11">
+        <v>1740</v>
+      </c>
+    </row>
+    <row r="416" spans="2:16">
       <c r="B416" s="12" t="s">
         <v>505</v>
       </c>
@@ -20172,8 +22660,14 @@
       <c r="M416" s="10">
         <v>-196</v>
       </c>
-    </row>
-    <row r="417" spans="2:13" ht="19.8">
+      <c r="O416" s="10">
+        <v>467</v>
+      </c>
+      <c r="P416" s="10">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="417" spans="2:16" ht="19.8">
       <c r="B417" s="12" t="s">
         <v>505</v>
       </c>
@@ -20210,8 +22704,14 @@
       <c r="M417" s="11">
         <v>21190</v>
       </c>
-    </row>
-    <row r="418" spans="2:13" ht="19.8">
+      <c r="O417" s="10">
+        <v>469</v>
+      </c>
+      <c r="P417" s="10">
+        <v>90.8</v>
+      </c>
+    </row>
+    <row r="418" spans="2:16" ht="19.8">
       <c r="B418" s="12" t="s">
         <v>505</v>
       </c>
@@ -20248,8 +22748,14 @@
       <c r="M418" s="11">
         <v>3472</v>
       </c>
-    </row>
-    <row r="419" spans="2:13">
+      <c r="O418" s="10">
+        <v>476</v>
+      </c>
+      <c r="P418" s="11">
+        <v>2951.3</v>
+      </c>
+    </row>
+    <row r="419" spans="2:16">
       <c r="B419" s="12" t="s">
         <v>505</v>
       </c>
@@ -20282,8 +22788,14 @@
       <c r="M419" s="11">
         <v>-1095.8</v>
       </c>
-    </row>
-    <row r="420" spans="2:13" ht="19.8">
+      <c r="O419" s="10">
+        <v>479</v>
+      </c>
+      <c r="P419" s="11">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="420" spans="2:16" ht="19.8">
       <c r="B420" s="12" t="s">
         <v>505</v>
       </c>
@@ -20320,8 +22832,14 @@
       <c r="M420" s="11">
         <v>4865</v>
       </c>
-    </row>
-    <row r="421" spans="2:13">
+      <c r="O420" s="10">
+        <v>480</v>
+      </c>
+      <c r="P420" s="10">
+        <v>712.4</v>
+      </c>
+    </row>
+    <row r="421" spans="2:16">
       <c r="B421" s="12" t="s">
         <v>505</v>
       </c>
@@ -20354,8 +22872,14 @@
       <c r="M421" s="10">
         <v>-78.5</v>
       </c>
-    </row>
-    <row r="422" spans="2:13" ht="19.8">
+      <c r="O421" s="10">
+        <v>481</v>
+      </c>
+      <c r="P421" s="11">
+        <v>1913.4</v>
+      </c>
+    </row>
+    <row r="422" spans="2:16" ht="19.8">
       <c r="B422" s="12" t="s">
         <v>505</v>
       </c>
@@ -20392,8 +22916,14 @@
       <c r="M422" s="11">
         <v>4888</v>
       </c>
-    </row>
-    <row r="423" spans="2:13">
+      <c r="O422" s="10">
+        <v>482</v>
+      </c>
+      <c r="P422" s="11">
+        <v>1548</v>
+      </c>
+    </row>
+    <row r="423" spans="2:16">
       <c r="B423" s="12" t="s">
         <v>505</v>
       </c>
@@ -20426,8 +22956,14 @@
       <c r="M423" s="10">
         <v>-99.2</v>
       </c>
-    </row>
-    <row r="424" spans="2:13" ht="19.8">
+      <c r="O423" s="10">
+        <v>483</v>
+      </c>
+      <c r="P423" s="11">
+        <v>3703.9</v>
+      </c>
+    </row>
+    <row r="424" spans="2:16" ht="19.8">
       <c r="B424" s="12" t="s">
         <v>505</v>
       </c>
@@ -20464,8 +23000,14 @@
       <c r="M424" s="11">
         <v>24310</v>
       </c>
-    </row>
-    <row r="425" spans="2:13" ht="19.8">
+      <c r="O424" s="10">
+        <v>485</v>
+      </c>
+      <c r="P424" s="10">
+        <v>915</v>
+      </c>
+    </row>
+    <row r="425" spans="2:16" ht="19.8">
       <c r="B425" s="12" t="s">
         <v>505</v>
       </c>
@@ -20502,8 +23044,14 @@
       <c r="M425" s="11">
         <v>5325</v>
       </c>
-    </row>
-    <row r="426" spans="2:13">
+      <c r="O425" s="10">
+        <v>486</v>
+      </c>
+      <c r="P425" s="11">
+        <v>1906.2</v>
+      </c>
+    </row>
+    <row r="426" spans="2:16">
       <c r="B426" s="12" t="s">
         <v>505</v>
       </c>
@@ -20536,8 +23084,14 @@
       <c r="M426" s="10">
         <v>-171</v>
       </c>
-    </row>
-    <row r="427" spans="2:13" ht="19.8">
+      <c r="O426" s="10">
+        <v>487</v>
+      </c>
+      <c r="P426" s="11">
+        <v>7236</v>
+      </c>
+    </row>
+    <row r="427" spans="2:16" ht="19.8">
       <c r="B427" s="12" t="s">
         <v>505</v>
       </c>
@@ -20574,8 +23128,14 @@
       <c r="M427" s="11">
         <v>2980</v>
       </c>
-    </row>
-    <row r="428" spans="2:13">
+      <c r="O427" s="10">
+        <v>488</v>
+      </c>
+      <c r="P427" s="11">
+        <v>2700</v>
+      </c>
+    </row>
+    <row r="428" spans="2:16">
       <c r="B428" s="12" t="s">
         <v>505</v>
       </c>
@@ -20608,8 +23168,14 @@
       <c r="M428" s="10">
         <v>-182</v>
       </c>
-    </row>
-    <row r="429" spans="2:13" ht="19.8">
+      <c r="O428" s="10">
+        <v>489</v>
+      </c>
+      <c r="P428" s="10">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="429" spans="2:16" ht="19.8">
       <c r="B429" s="12" t="s">
         <v>505</v>
       </c>
@@ -20646,8 +23212,14 @@
       <c r="M429" s="11">
         <v>3624</v>
       </c>
-    </row>
-    <row r="430" spans="2:13">
+      <c r="O429" s="10">
+        <v>490</v>
+      </c>
+      <c r="P429" s="10">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="430" spans="2:16">
       <c r="B430" s="12" t="s">
         <v>505</v>
       </c>
@@ -20680,8 +23252,14 @@
       <c r="M430" s="10">
         <v>-61.6</v>
       </c>
-    </row>
-    <row r="431" spans="2:13" ht="19.8">
+      <c r="O430" s="10">
+        <v>491</v>
+      </c>
+      <c r="P430" s="10">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="431" spans="2:16" ht="19.8">
       <c r="B431" s="12" t="s">
         <v>505</v>
       </c>
@@ -20718,8 +23296,14 @@
       <c r="M431" s="11">
         <v>5115</v>
       </c>
-    </row>
-    <row r="432" spans="2:13">
+      <c r="O431" s="10">
+        <v>492</v>
+      </c>
+      <c r="P431" s="11">
+        <v>2957.5</v>
+      </c>
+    </row>
+    <row r="432" spans="2:16">
       <c r="B432" s="12" t="s">
         <v>505</v>
       </c>
@@ -20752,8 +23336,14 @@
       <c r="M432" s="10">
         <v>-103.5</v>
       </c>
-    </row>
-    <row r="433" spans="2:13" ht="19.8">
+      <c r="O432" s="10">
+        <v>495</v>
+      </c>
+      <c r="P432" s="11">
+        <v>4184.8</v>
+      </c>
+    </row>
+    <row r="433" spans="2:16" ht="19.8">
       <c r="B433" s="12" t="s">
         <v>505</v>
       </c>
@@ -20790,8 +23380,14 @@
       <c r="M433" s="11">
         <v>17798</v>
       </c>
-    </row>
-    <row r="434" spans="2:13">
+      <c r="O433" s="10">
+        <v>497</v>
+      </c>
+      <c r="P433" s="10">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="434" spans="2:16">
       <c r="B434" s="12" t="s">
         <v>505</v>
       </c>
@@ -20824,8 +23420,14 @@
       <c r="M434" s="10">
         <v>-18.2</v>
       </c>
-    </row>
-    <row r="435" spans="2:13" ht="19.8">
+      <c r="O434" s="10">
+        <v>500</v>
+      </c>
+      <c r="P434" s="11">
+        <v>2592</v>
+      </c>
+    </row>
+    <row r="435" spans="2:16" ht="19.8">
       <c r="B435" s="12" t="s">
         <v>505</v>
       </c>
@@ -20862,8 +23464,14 @@
       <c r="M435" s="11">
         <v>1200</v>
       </c>
-    </row>
-    <row r="436" spans="2:13">
+      <c r="O435" s="10">
+        <v>494</v>
+      </c>
+      <c r="P435" s="11">
+        <v>1103.2</v>
+      </c>
+    </row>
+    <row r="436" spans="2:16">
       <c r="B436" s="12" t="s">
         <v>505</v>
       </c>
@@ -20896,8 +23504,14 @@
       <c r="M436" s="10">
         <v>-80</v>
       </c>
-    </row>
-    <row r="437" spans="2:13" ht="19.8">
+      <c r="O436" s="10">
+        <v>496</v>
+      </c>
+      <c r="P436" s="10">
+        <v>420.8</v>
+      </c>
+    </row>
+    <row r="437" spans="2:16" ht="19.8">
       <c r="B437" s="12" t="s">
         <v>505</v>
       </c>
@@ -20934,8 +23548,14 @@
       <c r="M437" s="11">
         <v>10304</v>
       </c>
-    </row>
-    <row r="438" spans="2:13" ht="19.8">
+      <c r="O437" s="10">
+        <v>498</v>
+      </c>
+      <c r="P437" s="11">
+        <v>1357.5</v>
+      </c>
+    </row>
+    <row r="438" spans="2:16" ht="19.8">
       <c r="B438" s="12" t="s">
         <v>505</v>
       </c>
@@ -20968,8 +23588,14 @@
       <c r="M438" s="10">
         <v>-173.6</v>
       </c>
-    </row>
-    <row r="439" spans="2:13" ht="19.8">
+      <c r="O438" s="10">
+        <v>499</v>
+      </c>
+      <c r="P438" s="11">
+        <v>2232</v>
+      </c>
+    </row>
+    <row r="439" spans="2:16" ht="19.8">
       <c r="B439" s="12" t="s">
         <v>505</v>
       </c>
@@ -21006,8 +23632,14 @@
       <c r="M439" s="11">
         <v>8632</v>
       </c>
-    </row>
-    <row r="440" spans="2:13" ht="19.8">
+      <c r="O439" s="10">
+        <v>501</v>
+      </c>
+      <c r="P439" s="10">
+        <v>911.3</v>
+      </c>
+    </row>
+    <row r="440" spans="2:16" ht="19.8">
       <c r="B440" s="12" t="s">
         <v>505</v>
       </c>
@@ -21040,8 +23672,14 @@
       <c r="M440" s="10">
         <v>-68.8</v>
       </c>
-    </row>
-    <row r="441" spans="2:13" ht="19.8">
+      <c r="O440" s="10">
+        <v>502</v>
+      </c>
+      <c r="P440" s="10">
+        <v>370.4</v>
+      </c>
+    </row>
+    <row r="441" spans="2:16" ht="19.8">
       <c r="B441" s="12" t="s">
         <v>505</v>
       </c>
@@ -21078,8 +23716,14 @@
       <c r="M441" s="11">
         <v>12948</v>
       </c>
-    </row>
-    <row r="442" spans="2:13">
+      <c r="O441" s="10">
+        <v>503</v>
+      </c>
+      <c r="P441" s="10">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="442" spans="2:16">
       <c r="B442" s="12" t="s">
         <v>505</v>
       </c>
@@ -21112,8 +23756,14 @@
       <c r="M442" s="10">
         <v>-153.19999999999999</v>
       </c>
-    </row>
-    <row r="443" spans="2:13" ht="19.8">
+      <c r="O442" s="10">
+        <v>504</v>
+      </c>
+      <c r="P442" s="10">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="443" spans="2:16" ht="19.8">
       <c r="B443" s="12" t="s">
         <v>505</v>
       </c>
@@ -21150,8 +23800,14 @@
       <c r="M443" s="11">
         <v>13968</v>
       </c>
-    </row>
-    <row r="444" spans="2:13">
+      <c r="O443" s="10">
+        <v>505</v>
+      </c>
+      <c r="P443" s="11">
+        <v>2030</v>
+      </c>
+    </row>
+    <row r="444" spans="2:16">
       <c r="B444" s="12" t="s">
         <v>505</v>
       </c>
@@ -21184,8 +23840,14 @@
       <c r="M444" s="10">
         <v>-71.2</v>
       </c>
-    </row>
-    <row r="445" spans="2:13" ht="19.8">
+      <c r="O444" s="10">
+        <v>506</v>
+      </c>
+      <c r="P444" s="10">
+        <v>556.20000000000005</v>
+      </c>
+    </row>
+    <row r="445" spans="2:16" ht="19.8">
       <c r="B445" s="12" t="s">
         <v>505</v>
       </c>
@@ -21222,8 +23884,14 @@
       <c r="M445" s="11">
         <v>12500</v>
       </c>
-    </row>
-    <row r="446" spans="2:13" ht="19.8">
+      <c r="O445" s="10">
+        <v>507</v>
+      </c>
+      <c r="P445" s="10">
+        <v>523.5</v>
+      </c>
+    </row>
+    <row r="446" spans="2:16" ht="19.8">
       <c r="B446" s="12" t="s">
         <v>505</v>
       </c>
@@ -21256,8 +23924,14 @@
       <c r="M446" s="10">
         <v>-50</v>
       </c>
-    </row>
-    <row r="447" spans="2:13" ht="19.8">
+      <c r="O446" s="10">
+        <v>509</v>
+      </c>
+      <c r="P446" s="10">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="447" spans="2:16" ht="19.8">
       <c r="B447" s="5">
         <v>45444</v>
       </c>
@@ -21294,8 +23968,14 @@
       <c r="M447" s="11">
         <v>25020</v>
       </c>
-    </row>
-    <row r="448" spans="2:13" ht="19.8">
+      <c r="O447" s="10">
+        <v>510</v>
+      </c>
+      <c r="P447" s="11">
+        <v>3600</v>
+      </c>
+    </row>
+    <row r="448" spans="2:16" ht="19.8">
       <c r="B448" s="5">
         <v>45444</v>
       </c>
@@ -21332,8 +24012,14 @@
       <c r="M448" s="11">
         <v>11080</v>
       </c>
-    </row>
-    <row r="449" spans="2:13" ht="19.8">
+      <c r="O448" s="10">
+        <v>511</v>
+      </c>
+      <c r="P448" s="11">
+        <v>1636</v>
+      </c>
+    </row>
+    <row r="449" spans="2:16" ht="19.8">
       <c r="B449" s="5">
         <v>45444</v>
       </c>
@@ -21366,8 +24052,14 @@
       <c r="M449" s="10">
         <v>-90</v>
       </c>
-    </row>
-    <row r="450" spans="2:13" ht="19.8">
+      <c r="O449" s="10">
+        <v>513</v>
+      </c>
+      <c r="P449" s="11">
+        <v>1026.4000000000001</v>
+      </c>
+    </row>
+    <row r="450" spans="2:16" ht="19.8">
       <c r="B450" s="12" t="s">
         <v>544</v>
       </c>
@@ -21404,8 +24096,14 @@
       <c r="M450" s="11">
         <v>6292</v>
       </c>
-    </row>
-    <row r="451" spans="2:13" ht="19.8">
+      <c r="O450" s="10">
+        <v>514</v>
+      </c>
+      <c r="P450" s="10">
+        <v>957</v>
+      </c>
+    </row>
+    <row r="451" spans="2:16" ht="19.8">
       <c r="B451" s="12" t="s">
         <v>544</v>
       </c>
@@ -21438,8 +24136,14 @@
       <c r="M451" s="10">
         <v>-63</v>
       </c>
-    </row>
-    <row r="452" spans="2:13" ht="19.8">
+      <c r="O451" s="10">
+        <v>512</v>
+      </c>
+      <c r="P451" s="10">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="452" spans="2:16" ht="19.8">
       <c r="B452" s="12" t="s">
         <v>547</v>
       </c>
@@ -21476,8 +24180,14 @@
       <c r="M452" s="11">
         <v>11150</v>
       </c>
-    </row>
-    <row r="453" spans="2:13">
+      <c r="O452" s="10">
+        <v>576</v>
+      </c>
+      <c r="P452" s="10">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="453" spans="2:16">
       <c r="B453" s="12" t="s">
         <v>547</v>
       </c>
@@ -21510,8 +24220,14 @@
       <c r="M453" s="10">
         <v>-35</v>
       </c>
-    </row>
-    <row r="454" spans="2:13" ht="19.8">
+      <c r="O453" s="10">
+        <v>518</v>
+      </c>
+      <c r="P453" s="11">
+        <v>6175</v>
+      </c>
+    </row>
+    <row r="454" spans="2:16" ht="19.8">
       <c r="B454" s="12" t="s">
         <v>547</v>
       </c>
@@ -21548,8 +24264,14 @@
       <c r="M454" s="11">
         <v>10110</v>
       </c>
-    </row>
-    <row r="455" spans="2:13">
+      <c r="O454" s="10">
+        <v>521</v>
+      </c>
+      <c r="P454" s="10">
+        <v>763.8</v>
+      </c>
+    </row>
+    <row r="455" spans="2:16">
       <c r="B455" s="12" t="s">
         <v>547</v>
       </c>
@@ -21582,8 +24304,14 @@
       <c r="M455" s="10">
         <v>-99</v>
       </c>
-    </row>
-    <row r="456" spans="2:13" ht="19.8">
+      <c r="O455" s="10">
+        <v>522</v>
+      </c>
+      <c r="P455" s="11">
+        <v>1818.2</v>
+      </c>
+    </row>
+    <row r="456" spans="2:16" ht="19.8">
       <c r="B456" s="12" t="s">
         <v>547</v>
       </c>
@@ -21620,8 +24348,14 @@
       <c r="M456" s="11">
         <v>21656</v>
       </c>
-    </row>
-    <row r="457" spans="2:13">
+      <c r="O456" s="10">
+        <v>523</v>
+      </c>
+      <c r="P456" s="11">
+        <v>5580</v>
+      </c>
+    </row>
+    <row r="457" spans="2:16">
       <c r="B457" s="12" t="s">
         <v>547</v>
       </c>
@@ -21654,8 +24388,14 @@
       <c r="M457" s="10">
         <v>-190.4</v>
       </c>
-    </row>
-    <row r="458" spans="2:13" ht="19.8">
+      <c r="O457" s="10">
+        <v>534</v>
+      </c>
+      <c r="P457" s="11">
+        <v>5529</v>
+      </c>
+    </row>
+    <row r="458" spans="2:16" ht="19.8">
       <c r="B458" s="12" t="s">
         <v>547</v>
       </c>
@@ -21692,8 +24432,14 @@
       <c r="M458" s="11">
         <v>-9650</v>
       </c>
-    </row>
-    <row r="459" spans="2:13" ht="19.8">
+      <c r="O458" s="10">
+        <v>516</v>
+      </c>
+      <c r="P458" s="11">
+        <v>1332</v>
+      </c>
+    </row>
+    <row r="459" spans="2:16" ht="19.8">
       <c r="B459" s="12" t="s">
         <v>547</v>
       </c>
@@ -21730,8 +24476,14 @@
       <c r="M459" s="11">
         <v>23100</v>
       </c>
-    </row>
-    <row r="460" spans="2:13">
+      <c r="O459" s="10">
+        <v>517</v>
+      </c>
+      <c r="P459" s="11">
+        <v>3366</v>
+      </c>
+    </row>
+    <row r="460" spans="2:16">
       <c r="B460" s="12" t="s">
         <v>547</v>
       </c>
@@ -21764,8 +24516,14 @@
       <c r="M460" s="10">
         <v>-190</v>
       </c>
-    </row>
-    <row r="461" spans="2:13" ht="19.8">
+      <c r="O460" s="10">
+        <v>547</v>
+      </c>
+      <c r="P460" s="10">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="461" spans="2:16" ht="19.8">
       <c r="B461" s="12" t="s">
         <v>547</v>
       </c>
@@ -21802,8 +24560,14 @@
       <c r="M461" s="11">
         <v>-6180</v>
       </c>
-    </row>
-    <row r="462" spans="2:13" ht="19.8">
+      <c r="O461" s="10">
+        <v>519</v>
+      </c>
+      <c r="P461" s="11">
+        <v>1192.7</v>
+      </c>
+    </row>
+    <row r="462" spans="2:16" ht="19.8">
       <c r="B462" s="12" t="s">
         <v>547</v>
       </c>
@@ -21840,8 +24604,14 @@
       <c r="M462" s="11">
         <v>21740</v>
       </c>
-    </row>
-    <row r="463" spans="2:13">
+      <c r="O462" s="10">
+        <v>520</v>
+      </c>
+      <c r="P462" s="10">
+        <v>844.6</v>
+      </c>
+    </row>
+    <row r="463" spans="2:16">
       <c r="B463" s="12" t="s">
         <v>547</v>
       </c>
@@ -21874,8 +24644,14 @@
       <c r="M463" s="10">
         <v>-166</v>
       </c>
-    </row>
-    <row r="464" spans="2:13" ht="19.8">
+      <c r="O463" s="10">
+        <v>524</v>
+      </c>
+      <c r="P463" s="11">
+        <v>2580</v>
+      </c>
+    </row>
+    <row r="464" spans="2:16" ht="19.8">
       <c r="B464" s="12" t="s">
         <v>547</v>
       </c>
@@ -21912,8 +24688,14 @@
       <c r="M464" s="11">
         <v>-9700</v>
       </c>
-    </row>
-    <row r="465" spans="2:13" ht="19.8">
+      <c r="O464" s="10">
+        <v>525</v>
+      </c>
+      <c r="P464" s="11">
+        <v>1445</v>
+      </c>
+    </row>
+    <row r="465" spans="2:16" ht="19.8">
       <c r="B465" s="12" t="s">
         <v>547</v>
       </c>
@@ -21950,8 +24732,14 @@
       <c r="M465" s="11">
         <v>3850</v>
       </c>
-    </row>
-    <row r="466" spans="2:13">
+      <c r="O465" s="10">
+        <v>526</v>
+      </c>
+      <c r="P465" s="10">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="466" spans="2:16">
       <c r="B466" s="12" t="s">
         <v>547</v>
       </c>
@@ -21984,8 +24772,14 @@
       <c r="M466" s="10">
         <v>-65</v>
       </c>
-    </row>
-    <row r="467" spans="2:13" ht="19.8">
+      <c r="O466" s="10">
+        <v>527</v>
+      </c>
+      <c r="P466" s="11">
+        <v>3298</v>
+      </c>
+    </row>
+    <row r="467" spans="2:16" ht="19.8">
       <c r="B467" s="12" t="s">
         <v>547</v>
       </c>
@@ -22022,8 +24816,14 @@
       <c r="M467" s="11">
         <v>2120</v>
       </c>
-    </row>
-    <row r="468" spans="2:13">
+      <c r="O467" s="10">
+        <v>528</v>
+      </c>
+      <c r="P467" s="11">
+        <v>4140</v>
+      </c>
+    </row>
+    <row r="468" spans="2:16">
       <c r="B468" s="12" t="s">
         <v>547</v>
       </c>
@@ -22056,8 +24856,14 @@
       <c r="M468" s="10">
         <v>-8</v>
       </c>
-    </row>
-    <row r="469" spans="2:13" ht="19.8">
+      <c r="O468" s="10">
+        <v>529</v>
+      </c>
+      <c r="P468" s="10">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="469" spans="2:16" ht="19.8">
       <c r="B469" s="12" t="s">
         <v>547</v>
       </c>
@@ -22094,8 +24900,14 @@
       <c r="M469" s="11">
         <v>6188</v>
       </c>
-    </row>
-    <row r="470" spans="2:13" ht="19.8">
+      <c r="O469" s="10">
+        <v>530</v>
+      </c>
+      <c r="P469" s="11">
+        <v>2322</v>
+      </c>
+    </row>
+    <row r="470" spans="2:16" ht="19.8">
       <c r="B470" s="12" t="s">
         <v>547</v>
       </c>
@@ -22128,8 +24940,14 @@
       <c r="M470" s="10">
         <v>-69.2</v>
       </c>
-    </row>
-    <row r="471" spans="2:13" ht="19.8">
+      <c r="O470" s="10">
+        <v>531</v>
+      </c>
+      <c r="P470" s="10">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="471" spans="2:16" ht="19.8">
       <c r="B471" s="12" t="s">
         <v>547</v>
       </c>
@@ -22166,8 +24984,14 @@
       <c r="M471" s="11">
         <v>10456</v>
       </c>
-    </row>
-    <row r="472" spans="2:13" ht="19.8">
+      <c r="O471" s="10">
+        <v>532</v>
+      </c>
+      <c r="P471" s="11">
+        <v>2849</v>
+      </c>
+    </row>
+    <row r="472" spans="2:16" ht="19.8">
       <c r="B472" s="12" t="s">
         <v>547</v>
       </c>
@@ -22200,8 +25024,14 @@
       <c r="M472" s="10">
         <v>-110.4</v>
       </c>
-    </row>
-    <row r="473" spans="2:13" ht="19.8">
+      <c r="O472" s="10">
+        <v>533</v>
+      </c>
+      <c r="P472" s="11">
+        <v>2618.1999999999998</v>
+      </c>
+    </row>
+    <row r="473" spans="2:16" ht="19.8">
       <c r="B473" s="12" t="s">
         <v>547</v>
       </c>
@@ -22238,8 +25068,14 @@
       <c r="M473" s="11">
         <v>3870</v>
       </c>
-    </row>
-    <row r="474" spans="2:13" ht="19.8">
+      <c r="O473" s="10">
+        <v>535</v>
+      </c>
+      <c r="P473" s="10">
+        <v>905.6</v>
+      </c>
+    </row>
+    <row r="474" spans="2:16" ht="19.8">
       <c r="B474" s="12" t="s">
         <v>547</v>
       </c>
@@ -22272,8 +25108,14 @@
       <c r="M474" s="10">
         <v>-83</v>
       </c>
-    </row>
-    <row r="475" spans="2:13" ht="19.8">
+      <c r="O474" s="10">
+        <v>543</v>
+      </c>
+      <c r="P474" s="11">
+        <v>4471.8999999999996</v>
+      </c>
+    </row>
+    <row r="475" spans="2:16" ht="19.8">
       <c r="B475" s="12" t="s">
         <v>547</v>
       </c>
@@ -22310,8 +25152,14 @@
       <c r="M475" s="11">
         <v>5265</v>
       </c>
-    </row>
-    <row r="476" spans="2:13" ht="19.8">
+      <c r="O475" s="10">
+        <v>546</v>
+      </c>
+      <c r="P475" s="10">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="476" spans="2:16" ht="19.8">
       <c r="B476" s="12" t="s">
         <v>547</v>
       </c>
@@ -22348,8 +25196,14 @@
       <c r="M476" s="11">
         <v>7635</v>
       </c>
-    </row>
-    <row r="477" spans="2:13" ht="19.8">
+      <c r="O476" s="10">
+        <v>548</v>
+      </c>
+      <c r="P476" s="10">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="477" spans="2:16" ht="19.8">
       <c r="B477" s="12" t="s">
         <v>547</v>
       </c>
@@ -22382,8 +25236,14 @@
       <c r="M477" s="10">
         <v>-110</v>
       </c>
-    </row>
-    <row r="478" spans="2:13" ht="19.8">
+      <c r="O477" s="10">
+        <v>549</v>
+      </c>
+      <c r="P477" s="11">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="478" spans="2:16" ht="19.8">
       <c r="B478" s="12" t="s">
         <v>547</v>
       </c>
@@ -22420,8 +25280,14 @@
       <c r="M478" s="11">
         <v>12390</v>
       </c>
-    </row>
-    <row r="479" spans="2:13" ht="19.8">
+      <c r="O478" s="10">
+        <v>646</v>
+      </c>
+      <c r="P478" s="11">
+        <v>5175</v>
+      </c>
+    </row>
+    <row r="479" spans="2:16" ht="19.8">
       <c r="B479" s="12" t="s">
         <v>547</v>
       </c>
@@ -22454,8 +25320,14 @@
       <c r="M479" s="10">
         <v>-151</v>
       </c>
-    </row>
-    <row r="480" spans="2:13" ht="19.8">
+      <c r="O479" s="10">
+        <v>647</v>
+      </c>
+      <c r="P479" s="11">
+        <v>1185</v>
+      </c>
+    </row>
+    <row r="480" spans="2:16" ht="19.8">
       <c r="B480" s="12" t="s">
         <v>547</v>
       </c>
@@ -22492,8 +25364,14 @@
       <c r="M480" s="11">
         <v>9350</v>
       </c>
-    </row>
-    <row r="481" spans="2:13" ht="19.8">
+      <c r="O480" s="10">
+        <v>648</v>
+      </c>
+      <c r="P480" s="11">
+        <v>1617</v>
+      </c>
+    </row>
+    <row r="481" spans="2:16" ht="19.8">
       <c r="B481" s="12" t="s">
         <v>547</v>
       </c>
@@ -22526,8 +25404,14 @@
       <c r="M481" s="10">
         <v>-129.5</v>
       </c>
-    </row>
-    <row r="482" spans="2:13" ht="19.8">
+      <c r="O481" s="10">
+        <v>536</v>
+      </c>
+      <c r="P481" s="10">
+        <v>649.6</v>
+      </c>
+    </row>
+    <row r="482" spans="2:16" ht="19.8">
       <c r="B482" s="12" t="s">
         <v>547</v>
       </c>
@@ -22564,8 +25448,14 @@
       <c r="M482" s="11">
         <v>2800</v>
       </c>
-    </row>
-    <row r="483" spans="2:13" ht="19.8">
+      <c r="O482" s="10">
+        <v>537</v>
+      </c>
+      <c r="P482" s="11">
+        <v>1530</v>
+      </c>
+    </row>
+    <row r="483" spans="2:16" ht="19.8">
       <c r="B483" s="12" t="s">
         <v>547</v>
       </c>
@@ -22598,8 +25488,14 @@
       <c r="M483" s="10">
         <v>-3.2</v>
       </c>
-    </row>
-    <row r="484" spans="2:13" ht="19.8">
+      <c r="O483" s="10">
+        <v>540</v>
+      </c>
+      <c r="P483" s="11">
+        <v>2109</v>
+      </c>
+    </row>
+    <row r="484" spans="2:16" ht="19.8">
       <c r="B484" s="12" t="s">
         <v>547</v>
       </c>
@@ -22636,8 +25532,14 @@
       <c r="M484" s="11">
         <v>1909</v>
       </c>
-    </row>
-    <row r="485" spans="2:13" ht="19.8">
+      <c r="O484" s="10">
+        <v>541</v>
+      </c>
+      <c r="P484" s="10">
+        <v>882</v>
+      </c>
+    </row>
+    <row r="485" spans="2:16" ht="19.8">
       <c r="B485" s="12" t="s">
         <v>547</v>
       </c>
@@ -22670,8 +25572,14 @@
       <c r="M485" s="10">
         <v>-77.099999999999994</v>
       </c>
-    </row>
-    <row r="486" spans="2:13" ht="19.8">
+      <c r="O485" s="10">
+        <v>542</v>
+      </c>
+      <c r="P485" s="10">
+        <v>810</v>
+      </c>
+    </row>
+    <row r="486" spans="2:16" ht="19.8">
       <c r="B486" s="12" t="s">
         <v>547</v>
       </c>
@@ -22708,8 +25616,14 @@
       <c r="M486" s="11">
         <v>1736</v>
       </c>
-    </row>
-    <row r="487" spans="2:13" ht="19.8">
+      <c r="O486" s="10">
+        <v>544</v>
+      </c>
+      <c r="P486" s="10">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="487" spans="2:16" ht="19.8">
       <c r="B487" s="12" t="s">
         <v>547</v>
       </c>
@@ -22742,8 +25656,14 @@
       <c r="M487" s="10">
         <v>-100.6</v>
       </c>
-    </row>
-    <row r="488" spans="2:13" ht="19.8">
+      <c r="O487" s="10">
+        <v>545</v>
+      </c>
+      <c r="P487" s="10">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="488" spans="2:16" ht="19.8">
       <c r="B488" s="12" t="s">
         <v>547</v>
       </c>
@@ -22780,8 +25700,14 @@
       <c r="M488" s="11">
         <v>1445</v>
       </c>
-    </row>
-    <row r="489" spans="2:13" ht="19.8">
+      <c r="O488" s="10">
+        <v>538</v>
+      </c>
+      <c r="P488" s="11">
+        <v>1478.4</v>
+      </c>
+    </row>
+    <row r="489" spans="2:16" ht="19.8">
       <c r="B489" s="12" t="s">
         <v>547</v>
       </c>
@@ -22814,8 +25740,14 @@
       <c r="M489" s="10">
         <v>-57.3</v>
       </c>
-    </row>
-    <row r="490" spans="2:13" ht="19.8">
+      <c r="O489" s="10">
+        <v>539</v>
+      </c>
+      <c r="P489" s="10">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="490" spans="2:16" ht="19.8">
       <c r="B490" s="12" t="s">
         <v>547</v>
       </c>
@@ -22852,8 +25784,14 @@
       <c r="M490" s="11">
         <v>9943</v>
       </c>
-    </row>
-    <row r="491" spans="2:13" ht="19.8">
+      <c r="O490" s="10">
+        <v>557</v>
+      </c>
+      <c r="P490" s="11">
+        <v>5418</v>
+      </c>
+    </row>
+    <row r="491" spans="2:16" ht="19.8">
       <c r="B491" s="12" t="s">
         <v>547</v>
       </c>
@@ -22886,8 +25824,14 @@
       <c r="M491" s="10">
         <v>-166</v>
       </c>
-    </row>
-    <row r="492" spans="2:13" ht="19.8">
+      <c r="O491" s="10">
+        <v>560</v>
+      </c>
+      <c r="P491" s="10">
+        <v>267.5</v>
+      </c>
+    </row>
+    <row r="492" spans="2:16" ht="19.8">
       <c r="B492" s="12" t="s">
         <v>547</v>
       </c>
@@ -22924,8 +25868,14 @@
       <c r="M492" s="11">
         <v>7140</v>
       </c>
-    </row>
-    <row r="493" spans="2:13" ht="19.8">
+      <c r="O492" s="10">
+        <v>561</v>
+      </c>
+      <c r="P492" s="10">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="493" spans="2:16" ht="19.8">
       <c r="B493" s="12" t="s">
         <v>547</v>
       </c>
@@ -22958,8 +25908,14 @@
       <c r="M493" s="10">
         <v>-160</v>
       </c>
-    </row>
-    <row r="494" spans="2:13" ht="19.8">
+      <c r="O493" s="10">
+        <v>566</v>
+      </c>
+      <c r="P493" s="11">
+        <v>3959</v>
+      </c>
+    </row>
+    <row r="494" spans="2:16" ht="19.8">
       <c r="B494" s="12" t="s">
         <v>547</v>
       </c>
@@ -22996,8 +25952,14 @@
       <c r="M494" s="11">
         <v>6693</v>
       </c>
-    </row>
-    <row r="495" spans="2:13" ht="19.8">
+      <c r="O494" s="10">
+        <v>567</v>
+      </c>
+      <c r="P494" s="11">
+        <v>1979.5</v>
+      </c>
+    </row>
+    <row r="495" spans="2:16" ht="19.8">
       <c r="B495" s="12" t="s">
         <v>547</v>
       </c>
@@ -23030,8 +25992,14 @@
       <c r="M495" s="10">
         <v>-155.5</v>
       </c>
-    </row>
-    <row r="496" spans="2:13" ht="19.8">
+      <c r="O495" s="10">
+        <v>568</v>
+      </c>
+      <c r="P495" s="11">
+        <v>4736</v>
+      </c>
+    </row>
+    <row r="496" spans="2:16" ht="19.8">
       <c r="B496" s="12" t="s">
         <v>547</v>
       </c>
@@ -23068,8 +26036,14 @@
       <c r="M496" s="11">
         <v>7492.8</v>
       </c>
-    </row>
-    <row r="497" spans="2:13" ht="19.8">
+      <c r="O496" s="10">
+        <v>569</v>
+      </c>
+      <c r="P496" s="11">
+        <v>1411.7</v>
+      </c>
+    </row>
+    <row r="497" spans="2:16" ht="19.8">
       <c r="B497" s="12" t="s">
         <v>547</v>
       </c>
@@ -23102,8 +26076,14 @@
       <c r="M497" s="10">
         <v>-29.2</v>
       </c>
-    </row>
-    <row r="498" spans="2:13" ht="19.8">
+      <c r="O497" s="10">
+        <v>570</v>
+      </c>
+      <c r="P497" s="10">
+        <v>868.3</v>
+      </c>
+    </row>
+    <row r="498" spans="2:16" ht="19.8">
       <c r="B498" s="12" t="s">
         <v>547</v>
       </c>
@@ -23140,8 +26120,14 @@
       <c r="M498" s="11">
         <v>8752</v>
       </c>
-    </row>
-    <row r="499" spans="2:13" ht="19.8">
+      <c r="O498" s="10">
+        <v>571</v>
+      </c>
+      <c r="P498" s="10">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="499" spans="2:16" ht="19.8">
       <c r="B499" s="12" t="s">
         <v>547</v>
       </c>
@@ -23174,8 +26160,14 @@
       <c r="M499" s="10">
         <v>-18.399999999999999</v>
       </c>
-    </row>
-    <row r="500" spans="2:13" ht="19.8">
+      <c r="O499" s="10">
+        <v>550</v>
+      </c>
+      <c r="P499" s="11">
+        <v>1912.4</v>
+      </c>
+    </row>
+    <row r="500" spans="2:16" ht="19.8">
       <c r="B500" s="12" t="s">
         <v>547</v>
       </c>
@@ -23212,8 +26204,14 @@
       <c r="M500" s="10">
         <v>652</v>
       </c>
-    </row>
-    <row r="501" spans="2:13" ht="19.8">
+      <c r="O500" s="10">
+        <v>551</v>
+      </c>
+      <c r="P500" s="10">
+        <v>297.5</v>
+      </c>
+    </row>
+    <row r="501" spans="2:16" ht="19.8">
       <c r="B501" s="12" t="s">
         <v>547</v>
       </c>
@@ -23246,8 +26244,14 @@
       <c r="M501" s="10">
         <v>-86.9</v>
       </c>
-    </row>
-    <row r="502" spans="2:13" ht="19.8">
+      <c r="O501" s="10">
+        <v>552</v>
+      </c>
+      <c r="P501" s="10">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="502" spans="2:16" ht="19.8">
       <c r="B502" s="12" t="s">
         <v>547</v>
       </c>
@@ -23284,8 +26288,14 @@
       <c r="M502" s="10">
         <v>676</v>
       </c>
-    </row>
-    <row r="503" spans="2:13" ht="19.8">
+      <c r="O502" s="10">
+        <v>553</v>
+      </c>
+      <c r="P502" s="11">
+        <v>1324.4</v>
+      </c>
+    </row>
+    <row r="503" spans="2:16" ht="19.8">
       <c r="B503" s="12" t="s">
         <v>547</v>
       </c>
@@ -23318,8 +26328,14 @@
       <c r="M503" s="10">
         <v>-71.599999999999994</v>
       </c>
-    </row>
-    <row r="504" spans="2:13" ht="19.8">
+      <c r="O503" s="10">
+        <v>554</v>
+      </c>
+      <c r="P503" s="11">
+        <v>2358.4</v>
+      </c>
+    </row>
+    <row r="504" spans="2:16" ht="19.8">
       <c r="B504" s="12" t="s">
         <v>547</v>
       </c>
@@ -23356,8 +26372,14 @@
       <c r="M504" s="11">
         <v>2150</v>
       </c>
-    </row>
-    <row r="505" spans="2:13" ht="19.8">
+      <c r="O504" s="10">
+        <v>555</v>
+      </c>
+      <c r="P504" s="11">
+        <v>2070</v>
+      </c>
+    </row>
+    <row r="505" spans="2:16" ht="19.8">
       <c r="B505" s="12" t="s">
         <v>547</v>
       </c>
@@ -23390,8 +26412,14 @@
       <c r="M505" s="10">
         <v>-45</v>
       </c>
-    </row>
-    <row r="506" spans="2:13" ht="19.8">
+      <c r="O505" s="10">
+        <v>556</v>
+      </c>
+      <c r="P505" s="11">
+        <v>4028</v>
+      </c>
+    </row>
+    <row r="506" spans="2:16" ht="19.8">
       <c r="B506" s="12" t="s">
         <v>547</v>
       </c>
@@ -23428,8 +26456,14 @@
       <c r="M506" s="11">
         <v>9010</v>
       </c>
-    </row>
-    <row r="507" spans="2:13" ht="19.8">
+      <c r="O506" s="10">
+        <v>565</v>
+      </c>
+      <c r="P506" s="11">
+        <v>4301</v>
+      </c>
+    </row>
+    <row r="507" spans="2:16" ht="19.8">
       <c r="B507" s="12" t="s">
         <v>547</v>
       </c>
@@ -23462,8 +26496,14 @@
       <c r="M507" s="10">
         <v>-9</v>
       </c>
-    </row>
-    <row r="508" spans="2:13" ht="19.8">
+      <c r="O507" s="10">
+        <v>575</v>
+      </c>
+      <c r="P507" s="10">
+        <v>186.2</v>
+      </c>
+    </row>
+    <row r="508" spans="2:16" ht="19.8">
       <c r="B508" s="12" t="s">
         <v>547</v>
       </c>
@@ -23500,8 +26540,14 @@
       <c r="M508" s="11">
         <v>8670</v>
       </c>
-    </row>
-    <row r="509" spans="2:13" ht="19.8">
+      <c r="O508" s="10">
+        <v>558</v>
+      </c>
+      <c r="P508" s="10">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="509" spans="2:16" ht="19.8">
       <c r="B509" s="12" t="s">
         <v>547</v>
       </c>
@@ -23534,8 +26580,14 @@
       <c r="M509" s="10">
         <v>-103</v>
       </c>
-    </row>
-    <row r="510" spans="2:13" ht="19.8">
+      <c r="O509" s="10">
+        <v>559</v>
+      </c>
+      <c r="P509" s="11">
+        <v>2770</v>
+      </c>
+    </row>
+    <row r="510" spans="2:16" ht="19.8">
       <c r="B510" s="12" t="s">
         <v>547</v>
       </c>
@@ -23572,8 +26624,14 @@
       <c r="M510" s="11">
         <v>16740</v>
       </c>
-    </row>
-    <row r="511" spans="2:13">
+      <c r="O510" s="10">
+        <v>572</v>
+      </c>
+      <c r="P510" s="10">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="511" spans="2:16">
       <c r="B511" s="12" t="s">
         <v>547</v>
       </c>
@@ -23606,8 +26664,14 @@
       <c r="M511" s="10">
         <v>-66</v>
       </c>
-    </row>
-    <row r="512" spans="2:13" ht="19.8">
+      <c r="O511" s="10">
+        <v>562</v>
+      </c>
+      <c r="P511" s="11">
+        <v>1912.4</v>
+      </c>
+    </row>
+    <row r="512" spans="2:16" ht="19.8">
       <c r="B512" s="12" t="s">
         <v>547</v>
       </c>
@@ -23644,8 +26708,14 @@
       <c r="M512" s="11">
         <v>58050</v>
       </c>
-    </row>
-    <row r="513" spans="2:13">
+      <c r="O512" s="10">
+        <v>563</v>
+      </c>
+      <c r="P512" s="11">
+        <v>1718.4</v>
+      </c>
+    </row>
+    <row r="513" spans="2:16">
       <c r="B513" s="12" t="s">
         <v>547</v>
       </c>
@@ -23678,8 +26748,14 @@
       <c r="M513" s="10">
         <v>-245</v>
       </c>
-    </row>
-    <row r="514" spans="2:13" ht="19.8">
+      <c r="O513" s="10">
+        <v>564</v>
+      </c>
+      <c r="P513" s="11">
+        <v>1718.4</v>
+      </c>
+    </row>
+    <row r="514" spans="2:16" ht="19.8">
       <c r="B514" s="12" t="s">
         <v>547</v>
       </c>
@@ -23716,8 +26792,14 @@
       <c r="M514" s="10">
         <v>490</v>
       </c>
-    </row>
-    <row r="515" spans="2:13" ht="19.8">
+      <c r="O514" s="10">
+        <v>579</v>
+      </c>
+      <c r="P514" s="10">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="515" spans="2:16" ht="19.8">
       <c r="B515" s="12" t="s">
         <v>547</v>
       </c>
@@ -23750,8 +26832,14 @@
       <c r="M515" s="10">
         <v>-41</v>
       </c>
-    </row>
-    <row r="516" spans="2:13" ht="19.8">
+      <c r="O515" s="10">
+        <v>581</v>
+      </c>
+      <c r="P515" s="10">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="516" spans="2:16" ht="19.8">
       <c r="B516" s="12" t="s">
         <v>547</v>
       </c>
@@ -23788,8 +26876,14 @@
       <c r="M516" s="10">
         <v>670</v>
       </c>
-    </row>
-    <row r="517" spans="2:13" ht="19.8">
+      <c r="O516" s="10">
+        <v>582</v>
+      </c>
+      <c r="P516" s="10">
+        <v>249.3</v>
+      </c>
+    </row>
+    <row r="517" spans="2:16" ht="19.8">
       <c r="B517" s="12" t="s">
         <v>547</v>
       </c>
@@ -23822,8 +26916,14 @@
       <c r="M517" s="10">
         <v>-3</v>
       </c>
-    </row>
-    <row r="518" spans="2:13" ht="19.8">
+      <c r="O517" s="10">
+        <v>583</v>
+      </c>
+      <c r="P517" s="10">
+        <v>323.39999999999998</v>
+      </c>
+    </row>
+    <row r="518" spans="2:16" ht="19.8">
       <c r="B518" s="12" t="s">
         <v>547</v>
       </c>
@@ -23860,8 +26960,14 @@
       <c r="M518" s="11">
         <v>4816</v>
       </c>
-    </row>
-    <row r="519" spans="2:13" ht="19.8">
+      <c r="O518" s="10">
+        <v>589</v>
+      </c>
+      <c r="P518" s="10">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="519" spans="2:16" ht="19.8">
       <c r="B519" s="12" t="s">
         <v>547</v>
       </c>
@@ -23894,8 +27000,14 @@
       <c r="M519" s="10">
         <v>-134.4</v>
       </c>
-    </row>
-    <row r="520" spans="2:13" ht="19.8">
+      <c r="O519" s="10">
+        <v>590</v>
+      </c>
+      <c r="P519" s="10">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="520" spans="2:16" ht="19.8">
       <c r="B520" s="12" t="s">
         <v>547</v>
       </c>
@@ -23932,8 +27044,14 @@
       <c r="M520" s="11">
         <v>21483</v>
       </c>
-    </row>
-    <row r="521" spans="2:13">
+      <c r="O520" s="10">
+        <v>591</v>
+      </c>
+      <c r="P520" s="10">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="521" spans="2:16">
       <c r="B521" s="12" t="s">
         <v>547</v>
       </c>
@@ -23966,8 +27084,14 @@
       <c r="M521" s="10">
         <v>-134.69999999999999</v>
       </c>
-    </row>
-    <row r="522" spans="2:13" ht="19.8">
+      <c r="O521" s="10">
+        <v>592</v>
+      </c>
+      <c r="P521" s="10">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="522" spans="2:16" ht="19.8">
       <c r="B522" s="12" t="s">
         <v>547</v>
       </c>
@@ -24004,8 +27128,14 @@
       <c r="M522" s="11">
         <v>14580</v>
       </c>
-    </row>
-    <row r="523" spans="2:13" ht="19.8">
+      <c r="O522" s="10">
+        <v>597</v>
+      </c>
+      <c r="P522" s="10">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="523" spans="2:16" ht="19.8">
       <c r="B523" s="12" t="s">
         <v>547</v>
       </c>
@@ -24038,8 +27168,14 @@
       <c r="M523" s="10">
         <v>-122</v>
       </c>
-    </row>
-    <row r="524" spans="2:13" ht="19.8">
+      <c r="O523" s="10">
+        <v>573</v>
+      </c>
+      <c r="P523" s="10">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="524" spans="2:16" ht="19.8">
       <c r="B524" s="12" t="s">
         <v>547</v>
       </c>
@@ -24076,8 +27212,14 @@
       <c r="M524" s="11">
         <v>16920</v>
       </c>
-    </row>
-    <row r="525" spans="2:13" ht="19.8">
+      <c r="O524" s="10">
+        <v>574</v>
+      </c>
+      <c r="P524" s="10">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="525" spans="2:16" ht="19.8">
       <c r="B525" s="12" t="s">
         <v>547</v>
       </c>
@@ -24110,8 +27252,14 @@
       <c r="M525" s="10">
         <v>-128</v>
       </c>
-    </row>
-    <row r="526" spans="2:13" ht="19.8">
+      <c r="O525" s="10">
+        <v>580</v>
+      </c>
+      <c r="P525" s="10">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="526" spans="2:16" ht="19.8">
       <c r="B526" s="12" t="s">
         <v>547</v>
       </c>
@@ -24148,8 +27296,14 @@
       <c r="M526" s="11">
         <v>27900</v>
       </c>
-    </row>
-    <row r="527" spans="2:13" ht="19.8">
+      <c r="O526" s="10">
+        <v>593</v>
+      </c>
+      <c r="P526" s="10">
+        <v>915</v>
+      </c>
+    </row>
+    <row r="527" spans="2:16" ht="19.8">
       <c r="B527" s="12" t="s">
         <v>547</v>
       </c>
@@ -24182,8 +27336,14 @@
       <c r="M527" s="10">
         <v>-110</v>
       </c>
-    </row>
-    <row r="528" spans="2:13" ht="19.8">
+      <c r="O527" s="10">
+        <v>598</v>
+      </c>
+      <c r="P527" s="11">
+        <v>5040</v>
+      </c>
+    </row>
+    <row r="528" spans="2:16" ht="19.8">
       <c r="B528" s="12" t="s">
         <v>627</v>
       </c>
@@ -24220,8 +27380,14 @@
       <c r="M528" s="11">
         <v>1890</v>
       </c>
-    </row>
-    <row r="529" spans="2:13" ht="19.8">
+      <c r="O528" s="10">
+        <v>599</v>
+      </c>
+      <c r="P528" s="11">
+        <v>2679</v>
+      </c>
+    </row>
+    <row r="529" spans="2:16" ht="19.8">
       <c r="B529" s="12" t="s">
         <v>627</v>
       </c>
@@ -24258,8 +27424,14 @@
       <c r="M529" s="11">
         <v>7036</v>
       </c>
-    </row>
-    <row r="530" spans="2:13">
+      <c r="O529" s="10">
+        <v>600</v>
+      </c>
+      <c r="P529" s="11">
+        <v>1868.5</v>
+      </c>
+    </row>
+    <row r="530" spans="2:16">
       <c r="B530" s="12" t="s">
         <v>627</v>
       </c>
@@ -24292,8 +27464,14 @@
       <c r="M530" s="10">
         <v>-132.4</v>
       </c>
-    </row>
-    <row r="531" spans="2:13" ht="19.8">
+      <c r="O530" s="10">
+        <v>577</v>
+      </c>
+      <c r="P530" s="10">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="531" spans="2:16" ht="19.8">
       <c r="B531" s="12" t="s">
         <v>627</v>
       </c>
@@ -24330,8 +27508,14 @@
       <c r="M531" s="11">
         <v>6000</v>
       </c>
-    </row>
-    <row r="532" spans="2:13" ht="19.8">
+      <c r="O531" s="10">
+        <v>595</v>
+      </c>
+      <c r="P531" s="11">
+        <v>1796</v>
+      </c>
+    </row>
+    <row r="532" spans="2:16" ht="19.8">
       <c r="B532" s="12" t="s">
         <v>627</v>
       </c>
@@ -24368,8 +27552,14 @@
       <c r="M532" s="11">
         <v>8019</v>
       </c>
-    </row>
-    <row r="533" spans="2:13" ht="19.8">
+      <c r="O532" s="10">
+        <v>601</v>
+      </c>
+      <c r="P532" s="10">
+        <v>842</v>
+      </c>
+    </row>
+    <row r="533" spans="2:16" ht="19.8">
       <c r="B533" s="12" t="s">
         <v>627</v>
       </c>
@@ -24402,8 +27592,14 @@
       <c r="M533" s="10">
         <v>-117.1</v>
       </c>
-    </row>
-    <row r="534" spans="2:13" ht="19.8">
+      <c r="O533" s="10">
+        <v>602</v>
+      </c>
+      <c r="P533" s="10">
+        <v>842</v>
+      </c>
+    </row>
+    <row r="534" spans="2:16" ht="19.8">
       <c r="B534" s="12" t="s">
         <v>627</v>
       </c>
@@ -24440,8 +27636,14 @@
       <c r="M534" s="11">
         <v>7202</v>
       </c>
-    </row>
-    <row r="535" spans="2:13" ht="19.8">
+      <c r="O534" s="10">
+        <v>603</v>
+      </c>
+      <c r="P534" s="10">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="535" spans="2:16" ht="19.8">
       <c r="B535" s="12" t="s">
         <v>627</v>
       </c>
@@ -24474,8 +27676,14 @@
       <c r="M535" s="10">
         <v>-82</v>
       </c>
-    </row>
-    <row r="536" spans="2:13" ht="19.8">
+      <c r="O535" s="10">
+        <v>604</v>
+      </c>
+      <c r="P535" s="10">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="536" spans="2:16" ht="19.8">
       <c r="B536" s="12" t="s">
         <v>627</v>
       </c>
@@ -24512,8 +27720,14 @@
       <c r="M536" s="11">
         <v>16920</v>
       </c>
-    </row>
-    <row r="537" spans="2:13" ht="19.8">
+      <c r="O536" s="10">
+        <v>605</v>
+      </c>
+      <c r="P536" s="10">
+        <v>503.2</v>
+      </c>
+    </row>
+    <row r="537" spans="2:16" ht="19.8">
       <c r="B537" s="12" t="s">
         <v>627</v>
       </c>
@@ -24546,8 +27760,14 @@
       <c r="M537" s="10">
         <v>-128</v>
       </c>
-    </row>
-    <row r="538" spans="2:13" ht="19.8">
+      <c r="O537" s="10">
+        <v>606</v>
+      </c>
+      <c r="P537" s="10">
+        <v>363.7</v>
+      </c>
+    </row>
+    <row r="538" spans="2:16" ht="19.8">
       <c r="B538" s="12" t="s">
         <v>627</v>
       </c>
@@ -24584,8 +27804,14 @@
       <c r="M538" s="11">
         <v>2450</v>
       </c>
-    </row>
-    <row r="539" spans="2:13">
+      <c r="O538" s="10">
+        <v>607</v>
+      </c>
+      <c r="P538" s="11">
+        <v>1406.1</v>
+      </c>
+    </row>
+    <row r="539" spans="2:16">
       <c r="B539" s="12" t="s">
         <v>627</v>
       </c>
@@ -24618,8 +27844,14 @@
       <c r="M539" s="10">
         <v>-5</v>
       </c>
-    </row>
-    <row r="540" spans="2:13" ht="19.8">
+      <c r="O539" s="10">
+        <v>608</v>
+      </c>
+      <c r="P539" s="11">
+        <v>2790</v>
+      </c>
+    </row>
+    <row r="540" spans="2:16" ht="19.8">
       <c r="B540" s="5">
         <v>45567</v>
       </c>
@@ -24656,8 +27888,14 @@
       <c r="M540" s="11">
         <v>10496</v>
       </c>
-    </row>
-    <row r="541" spans="2:13" ht="19.8">
+      <c r="O540" s="10">
+        <v>610</v>
+      </c>
+      <c r="P540" s="10">
+        <v>392.4</v>
+      </c>
+    </row>
+    <row r="541" spans="2:16" ht="19.8">
       <c r="B541" s="5">
         <v>45567</v>
       </c>
@@ -24690,8 +27928,14 @@
       <c r="M541" s="10">
         <v>-96.4</v>
       </c>
-    </row>
-    <row r="542" spans="2:13" ht="19.8">
+      <c r="O541" s="10">
+        <v>611</v>
+      </c>
+      <c r="P541" s="10">
+        <v>376.6</v>
+      </c>
+    </row>
+    <row r="542" spans="2:16" ht="19.8">
       <c r="B542" s="12" t="s">
         <v>645</v>
       </c>
@@ -24728,8 +27972,14 @@
       <c r="M542" s="11">
         <v>23350</v>
       </c>
-    </row>
-    <row r="543" spans="2:13" ht="19.8">
+      <c r="O542" s="10">
+        <v>612</v>
+      </c>
+      <c r="P542" s="10">
+        <v>377.8</v>
+      </c>
+    </row>
+    <row r="543" spans="2:16" ht="19.8">
       <c r="B543" s="12" t="s">
         <v>645</v>
       </c>
@@ -24762,8 +28012,14 @@
       <c r="M543" s="10">
         <v>-115</v>
       </c>
-    </row>
-    <row r="544" spans="2:13" ht="19.8">
+      <c r="O543" s="10">
+        <v>613</v>
+      </c>
+      <c r="P543" s="10">
+        <v>191.5</v>
+      </c>
+    </row>
+    <row r="544" spans="2:16" ht="19.8">
       <c r="B544" s="12" t="s">
         <v>648</v>
       </c>
@@ -24800,8 +28056,14 @@
       <c r="M544" s="11">
         <v>4992</v>
       </c>
-    </row>
-    <row r="545" spans="2:13">
+      <c r="O544" s="10">
+        <v>614</v>
+      </c>
+      <c r="P544" s="10">
+        <v>893.4</v>
+      </c>
+    </row>
+    <row r="545" spans="2:16">
       <c r="B545" s="12" t="s">
         <v>648</v>
       </c>
@@ -24834,8 +28096,14 @@
       <c r="M545" s="10">
         <v>-92.8</v>
       </c>
-    </row>
-    <row r="546" spans="2:13" ht="19.8">
+      <c r="O545" s="10">
+        <v>615</v>
+      </c>
+      <c r="P545" s="10">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="546" spans="2:16" ht="19.8">
       <c r="B546" s="12" t="s">
         <v>648</v>
       </c>
@@ -24872,8 +28140,14 @@
       <c r="M546" s="11">
         <v>19916</v>
       </c>
-    </row>
-    <row r="547" spans="2:13">
+      <c r="O546" s="10">
+        <v>619</v>
+      </c>
+      <c r="P546" s="11">
+        <v>5436</v>
+      </c>
+    </row>
+    <row r="547" spans="2:16">
       <c r="B547" s="12" t="s">
         <v>648</v>
       </c>
@@ -24906,8 +28180,14 @@
       <c r="M547" s="10">
         <v>-124.4</v>
       </c>
-    </row>
-    <row r="548" spans="2:13" ht="19.8">
+      <c r="O547" s="10">
+        <v>620</v>
+      </c>
+      <c r="P547" s="10">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="548" spans="2:16" ht="19.8">
       <c r="B548" s="12" t="s">
         <v>648</v>
       </c>
@@ -24944,8 +28224,14 @@
       <c r="M548" s="11">
         <v>21021</v>
       </c>
-    </row>
-    <row r="549" spans="2:13">
+      <c r="O548" s="10">
+        <v>621</v>
+      </c>
+      <c r="P548" s="10">
+        <v>256.8</v>
+      </c>
+    </row>
+    <row r="549" spans="2:16">
       <c r="B549" s="12" t="s">
         <v>648</v>
       </c>
@@ -24978,8 +28264,14 @@
       <c r="M549" s="10">
         <v>-118.9</v>
       </c>
-    </row>
-    <row r="550" spans="2:13" ht="19.8">
+      <c r="O549" s="10">
+        <v>623</v>
+      </c>
+      <c r="P549" s="10">
+        <v>501.2</v>
+      </c>
+    </row>
+    <row r="550" spans="2:16" ht="19.8">
       <c r="B550" s="12" t="s">
         <v>648</v>
       </c>
@@ -25016,8 +28308,14 @@
       <c r="M550" s="11">
         <v>6165</v>
       </c>
-    </row>
-    <row r="551" spans="2:13" ht="19.8">
+      <c r="O550" s="10">
+        <v>624</v>
+      </c>
+      <c r="P550" s="11">
+        <v>1792.8</v>
+      </c>
+    </row>
+    <row r="551" spans="2:16" ht="19.8">
       <c r="B551" s="12" t="s">
         <v>648</v>
       </c>
@@ -25054,8 +28352,14 @@
       <c r="M551" s="11">
         <v>1998</v>
       </c>
-    </row>
-    <row r="552" spans="2:13" ht="19.8">
+      <c r="O551" s="10">
+        <v>625</v>
+      </c>
+      <c r="P551" s="11">
+        <v>1234.8</v>
+      </c>
+    </row>
+    <row r="552" spans="2:16" ht="19.8">
       <c r="B552" s="12" t="s">
         <v>648</v>
       </c>
@@ -25088,8 +28392,14 @@
       <c r="M552" s="10">
         <v>-146.69999999999999</v>
       </c>
-    </row>
-    <row r="553" spans="2:13" ht="19.8">
+      <c r="O552" s="10">
+        <v>629</v>
+      </c>
+      <c r="P552" s="11">
+        <v>3244.8</v>
+      </c>
+    </row>
+    <row r="553" spans="2:16" ht="19.8">
       <c r="B553" s="12" t="s">
         <v>648</v>
       </c>
@@ -25126,8 +28436,14 @@
       <c r="M553" s="11">
         <v>4815</v>
       </c>
-    </row>
-    <row r="554" spans="2:13" ht="19.8">
+      <c r="O553" s="10">
+        <v>632</v>
+      </c>
+      <c r="P553" s="11">
+        <v>2460.5</v>
+      </c>
+    </row>
+    <row r="554" spans="2:16" ht="19.8">
       <c r="B554" s="12" t="s">
         <v>648</v>
       </c>
@@ -25164,8 +28480,14 @@
       <c r="M554" s="11">
         <v>1314</v>
       </c>
-    </row>
-    <row r="555" spans="2:13" ht="19.8">
+      <c r="O554" s="10">
+        <v>633</v>
+      </c>
+      <c r="P554" s="11">
+        <v>3718.5</v>
+      </c>
+    </row>
+    <row r="555" spans="2:16" ht="19.8">
       <c r="B555" s="12" t="s">
         <v>648</v>
       </c>
@@ -25198,8 +28520,14 @@
       <c r="M555" s="10">
         <v>-16.100000000000001</v>
       </c>
-    </row>
-    <row r="556" spans="2:13" ht="19.8">
+      <c r="O555" s="10">
+        <v>638</v>
+      </c>
+      <c r="P555" s="11">
+        <v>1558</v>
+      </c>
+    </row>
+    <row r="556" spans="2:16" ht="19.8">
       <c r="B556" s="12" t="s">
         <v>648</v>
       </c>
@@ -25236,8 +28564,14 @@
       <c r="M556" s="11">
         <v>7015</v>
       </c>
-    </row>
-    <row r="557" spans="2:13">
+      <c r="O556" s="10">
+        <v>616</v>
+      </c>
+      <c r="P556" s="11">
+        <v>4176</v>
+      </c>
+    </row>
+    <row r="557" spans="2:16">
       <c r="B557" s="12" t="s">
         <v>648</v>
       </c>
@@ -25270,8 +28604,14 @@
       <c r="M557" s="10">
         <v>-13.5</v>
       </c>
-    </row>
-    <row r="558" spans="2:13" ht="19.8">
+      <c r="O557" s="10">
+        <v>618</v>
+      </c>
+      <c r="P557" s="11">
+        <v>1172</v>
+      </c>
+    </row>
+    <row r="558" spans="2:16" ht="19.8">
       <c r="B558" s="12" t="s">
         <v>648</v>
       </c>
@@ -25308,8 +28648,14 @@
       <c r="M558" s="11">
         <v>3910</v>
       </c>
-    </row>
-    <row r="559" spans="2:13">
+      <c r="O558" s="10">
+        <v>622</v>
+      </c>
+      <c r="P558" s="11">
+        <v>1418.1</v>
+      </c>
+    </row>
+    <row r="559" spans="2:16">
       <c r="B559" s="12" t="s">
         <v>648</v>
       </c>
@@ -25342,8 +28688,14 @@
       <c r="M559" s="10">
         <v>-119</v>
       </c>
-    </row>
-    <row r="560" spans="2:13" ht="19.8">
+      <c r="O559" s="10">
+        <v>626</v>
+      </c>
+      <c r="P559" s="10">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="560" spans="2:16" ht="19.8">
       <c r="B560" s="12" t="s">
         <v>648</v>
       </c>
@@ -25380,8 +28732,14 @@
       <c r="M560" s="11">
         <v>6440</v>
       </c>
-    </row>
-    <row r="561" spans="2:13" ht="19.8">
+      <c r="O560" s="10">
+        <v>627</v>
+      </c>
+      <c r="P560" s="10">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="561" spans="2:16" ht="19.8">
       <c r="B561" s="12" t="s">
         <v>648</v>
       </c>
@@ -25414,8 +28772,14 @@
       <c r="M561" s="10">
         <v>-96</v>
       </c>
-    </row>
-    <row r="562" spans="2:13" ht="19.8">
+      <c r="O561" s="10">
+        <v>630</v>
+      </c>
+      <c r="P561" s="10">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="562" spans="2:16" ht="19.8">
       <c r="B562" s="12" t="s">
         <v>648</v>
       </c>
@@ -25452,8 +28816,14 @@
       <c r="M562" s="11">
         <v>3978</v>
       </c>
-    </row>
-    <row r="563" spans="2:13" ht="19.8">
+      <c r="O562" s="10">
+        <v>634</v>
+      </c>
+      <c r="P562" s="10">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="563" spans="2:16" ht="19.8">
       <c r="B563" s="12" t="s">
         <v>648</v>
       </c>
@@ -25486,8 +28856,14 @@
       <c r="M563" s="10">
         <v>-80.2</v>
       </c>
-    </row>
-    <row r="564" spans="2:13" ht="19.8">
+      <c r="O563" s="10">
+        <v>635</v>
+      </c>
+      <c r="P563" s="10">
+        <v>617.5</v>
+      </c>
+    </row>
+    <row r="564" spans="2:16" ht="19.8">
       <c r="B564" s="12" t="s">
         <v>648</v>
       </c>
@@ -25524,8 +28900,14 @@
       <c r="M564" s="11">
         <v>6643</v>
       </c>
-    </row>
-    <row r="565" spans="2:13" ht="19.8">
+      <c r="O564" s="10">
+        <v>636</v>
+      </c>
+      <c r="P564" s="10">
+        <v>769.8</v>
+      </c>
+    </row>
+    <row r="565" spans="2:16" ht="19.8">
       <c r="B565" s="12" t="s">
         <v>648</v>
       </c>
@@ -25558,8 +28940,14 @@
       <c r="M565" s="10">
         <v>-78.7</v>
       </c>
-    </row>
-    <row r="566" spans="2:13" ht="19.8">
+      <c r="O565" s="10">
+        <v>637</v>
+      </c>
+      <c r="P565" s="11">
+        <v>2288</v>
+      </c>
+    </row>
+    <row r="566" spans="2:16" ht="19.8">
       <c r="B566" s="12" t="s">
         <v>672</v>
       </c>
@@ -25596,8 +28984,14 @@
       <c r="M566" s="11">
         <v>38160</v>
       </c>
-    </row>
-    <row r="567" spans="2:13" ht="19.8">
+      <c r="O566" s="10">
+        <v>639</v>
+      </c>
+      <c r="P566" s="11">
+        <v>9975</v>
+      </c>
+    </row>
+    <row r="567" spans="2:16" ht="19.8">
       <c r="B567" s="12" t="s">
         <v>672</v>
       </c>
@@ -25630,8 +29024,14 @@
       <c r="M567" s="10">
         <v>-144</v>
       </c>
-    </row>
-    <row r="568" spans="2:13" ht="19.8">
+      <c r="O567" s="10">
+        <v>640</v>
+      </c>
+      <c r="P567" s="11">
+        <v>4028</v>
+      </c>
+    </row>
+    <row r="568" spans="2:16" ht="19.8">
       <c r="B568" s="12" t="s">
         <v>672</v>
       </c>
@@ -25668,8 +29068,14 @@
       <c r="M568" s="11">
         <v>10740</v>
       </c>
-    </row>
-    <row r="569" spans="2:13" ht="19.8">
+      <c r="O568" s="10">
+        <v>641</v>
+      </c>
+      <c r="P568" s="11">
+        <v>2603</v>
+      </c>
+    </row>
+    <row r="569" spans="2:16" ht="19.8">
       <c r="B569" s="12" t="s">
         <v>672</v>
       </c>
@@ -25702,8 +29108,14 @@
       <c r="M569" s="10">
         <v>-66</v>
       </c>
-    </row>
-    <row r="570" spans="2:13" ht="19.8">
+      <c r="O569" s="10">
+        <v>642</v>
+      </c>
+      <c r="P569" s="11">
+        <v>2907</v>
+      </c>
+    </row>
+    <row r="570" spans="2:16" ht="19.8">
       <c r="B570" s="12" t="s">
         <v>672</v>
       </c>
@@ -25740,8 +29152,14 @@
       <c r="M570" s="11">
         <v>13850</v>
       </c>
-    </row>
-    <row r="571" spans="2:13" ht="19.8">
+      <c r="O570" s="10">
+        <v>644</v>
+      </c>
+      <c r="P570" s="11">
+        <v>3600</v>
+      </c>
+    </row>
+    <row r="571" spans="2:16" ht="19.8">
       <c r="B571" s="12" t="s">
         <v>672</v>
       </c>
@@ -25774,8 +29192,14 @@
       <c r="M571" s="10">
         <v>-165</v>
       </c>
-    </row>
-    <row r="572" spans="2:13" ht="19.8">
+      <c r="O571" s="10">
+        <v>653</v>
+      </c>
+      <c r="P571" s="10">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="572" spans="2:16" ht="19.8">
       <c r="B572" s="12" t="s">
         <v>672</v>
       </c>
@@ -25812,8 +29236,14 @@
       <c r="M572" s="11">
         <v>3270</v>
       </c>
-    </row>
-    <row r="573" spans="2:13" ht="19.8">
+      <c r="O572" s="10">
+        <v>628</v>
+      </c>
+      <c r="P572" s="10">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="573" spans="2:16" ht="19.8">
       <c r="B573" s="12" t="s">
         <v>672</v>
       </c>
@@ -25846,8 +29276,14 @@
       <c r="M573" s="10">
         <v>-143</v>
       </c>
-    </row>
-    <row r="574" spans="2:13" ht="19.8">
+      <c r="O573" s="10">
+        <v>631</v>
+      </c>
+      <c r="P573" s="10">
+        <v>462.5</v>
+      </c>
+    </row>
+    <row r="574" spans="2:16" ht="19.8">
       <c r="B574" s="12" t="s">
         <v>672</v>
       </c>
@@ -25884,8 +29320,14 @@
       <c r="M574" s="11">
         <v>6240</v>
       </c>
-    </row>
-    <row r="575" spans="2:13" ht="19.8">
+      <c r="O574" s="10">
+        <v>643</v>
+      </c>
+      <c r="P574" s="10">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="575" spans="2:16" ht="19.8">
       <c r="B575" s="12" t="s">
         <v>672</v>
       </c>
@@ -25922,8 +29364,14 @@
       <c r="M575" s="11">
         <v>6240</v>
       </c>
-    </row>
-    <row r="576" spans="2:13">
+      <c r="O575" s="10">
+        <v>652</v>
+      </c>
+      <c r="P575" s="11">
+        <v>8913</v>
+      </c>
+    </row>
+    <row r="576" spans="2:16">
       <c r="B576" s="12" t="s">
         <v>672</v>
       </c>
@@ -52284,6 +55732,9 @@
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="O1:O302 O304:O340 O342:O1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>